--- a/templates/GS official Template.xlsx
+++ b/templates/GS official Template.xlsx
@@ -975,7 +975,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1425,6 +1425,90 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="5" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="5" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" applyNumberFormat="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="18" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6864,11 +6948,11 @@
         <f>'[1]TERM 1'!K18</f>
         <v/>
       </c>
-      <c r="L16" s="44" t="str">
+      <c r="L16" s="121" t="str">
         <f>'[1]TERM 1'!L18</f>
         <v/>
       </c>
-      <c r="M16" s="45" t="str">
+      <c r="M16" s="122" t="str">
         <f>'[1]TERM 1'!M18</f>
         <v/>
       </c>
@@ -6879,34 +6963,34 @@
         <f>'[1]TERM 1'!Q18</f>
         <v/>
       </c>
-      <c r="R16" s="44" t="str">
+      <c r="R16" s="121" t="str">
         <f>'[1]TERM 1'!R18</f>
         <v/>
       </c>
-      <c r="S16" s="47" t="str">
+      <c r="S16" s="123" t="str">
         <f>'[1]TERM 1'!S18</f>
         <v/>
       </c>
       <c r="T16" s="40"/>
       <c r="U16" s="41"/>
       <c r="V16" s="42"/>
-      <c r="W16" s="44" t="str">
+      <c r="W16" s="121" t="str">
         <f>'[1]TERM 1'!W18</f>
         <v/>
       </c>
-      <c r="X16" s="45" t="str">
+      <c r="X16" s="122" t="str">
         <f>'[1]TERM 1'!X18</f>
         <v/>
       </c>
-      <c r="Y16" s="48" t="str">
+      <c r="Y16" s="124" t="str">
         <f>'[1]TERM 1'!Y18</f>
         <v/>
       </c>
-      <c r="Z16" s="44" t="str">
+      <c r="Z16" s="121" t="str">
         <f>'[1]TERM 1'!Z18</f>
         <v/>
       </c>
-      <c r="AA16" s="47" t="str">
+      <c r="AA16" s="123" t="str">
         <f>'[1]TERM 1'!AA18</f>
         <v/>
       </c>
@@ -6940,11 +7024,11 @@
         <f>'[1]TERM 1'!K19</f>
         <v/>
       </c>
-      <c r="L17" s="58" t="str">
+      <c r="L17" s="125" t="str">
         <f>'[1]TERM 1'!L19</f>
         <v/>
       </c>
-      <c r="M17" s="59" t="str">
+      <c r="M17" s="126" t="str">
         <f>'[1]TERM 1'!M19</f>
         <v/>
       </c>
@@ -6955,34 +7039,34 @@
         <f>'[1]TERM 1'!Q19</f>
         <v/>
       </c>
-      <c r="R17" s="58" t="str">
+      <c r="R17" s="125" t="str">
         <f>'[1]TERM 1'!R19</f>
         <v/>
       </c>
-      <c r="S17" s="61" t="str">
+      <c r="S17" s="127" t="str">
         <f>'[1]TERM 1'!S19</f>
         <v/>
       </c>
       <c r="T17" s="62"/>
       <c r="U17" s="55"/>
       <c r="V17" s="56"/>
-      <c r="W17" s="58" t="str">
+      <c r="W17" s="125" t="str">
         <f>'[1]TERM 1'!W19</f>
         <v/>
       </c>
-      <c r="X17" s="59" t="str">
+      <c r="X17" s="126" t="str">
         <f>'[1]TERM 1'!X19</f>
         <v/>
       </c>
-      <c r="Y17" s="63" t="str">
+      <c r="Y17" s="128" t="str">
         <f>'[1]TERM 1'!Y19</f>
         <v/>
       </c>
-      <c r="Z17" s="58" t="str">
+      <c r="Z17" s="125" t="str">
         <f>'[1]TERM 1'!Z19</f>
         <v/>
       </c>
-      <c r="AA17" s="61" t="str">
+      <c r="AA17" s="127" t="str">
         <f>'[1]TERM 1'!AA19</f>
         <v/>
       </c>
@@ -7016,11 +7100,11 @@
         <f>'[1]TERM 1'!K20</f>
         <v/>
       </c>
-      <c r="L18" s="58" t="str">
+      <c r="L18" s="125" t="str">
         <f>'[1]TERM 1'!L20</f>
         <v/>
       </c>
-      <c r="M18" s="59" t="str">
+      <c r="M18" s="126" t="str">
         <f>'[1]TERM 1'!M20</f>
         <v/>
       </c>
@@ -7031,34 +7115,34 @@
         <f>'[1]TERM 1'!Q20</f>
         <v/>
       </c>
-      <c r="R18" s="58" t="str">
+      <c r="R18" s="125" t="str">
         <f>'[1]TERM 1'!R20</f>
         <v/>
       </c>
-      <c r="S18" s="61" t="str">
+      <c r="S18" s="127" t="str">
         <f>'[1]TERM 1'!S20</f>
         <v/>
       </c>
       <c r="T18" s="62"/>
       <c r="U18" s="55"/>
       <c r="V18" s="56"/>
-      <c r="W18" s="58" t="str">
+      <c r="W18" s="125" t="str">
         <f>'[1]TERM 1'!W20</f>
         <v/>
       </c>
-      <c r="X18" s="59" t="str">
+      <c r="X18" s="126" t="str">
         <f>'[1]TERM 1'!X20</f>
         <v/>
       </c>
-      <c r="Y18" s="63" t="str">
+      <c r="Y18" s="128" t="str">
         <f>'[1]TERM 1'!Y20</f>
         <v/>
       </c>
-      <c r="Z18" s="58" t="str">
+      <c r="Z18" s="125" t="str">
         <f>'[1]TERM 1'!Z20</f>
         <v/>
       </c>
-      <c r="AA18" s="61" t="str">
+      <c r="AA18" s="127" t="str">
         <f>'[1]TERM 1'!AA20</f>
         <v/>
       </c>
@@ -7092,11 +7176,11 @@
         <f>'[1]TERM 1'!K21</f>
         <v/>
       </c>
-      <c r="L19" s="58" t="str">
+      <c r="L19" s="125" t="str">
         <f>'[1]TERM 1'!L21</f>
         <v/>
       </c>
-      <c r="M19" s="59" t="str">
+      <c r="M19" s="126" t="str">
         <f>'[1]TERM 1'!M21</f>
         <v/>
       </c>
@@ -7107,34 +7191,34 @@
         <f>'[1]TERM 1'!Q21</f>
         <v/>
       </c>
-      <c r="R19" s="58" t="str">
+      <c r="R19" s="125" t="str">
         <f>'[1]TERM 1'!R21</f>
         <v/>
       </c>
-      <c r="S19" s="61" t="str">
+      <c r="S19" s="127" t="str">
         <f>'[1]TERM 1'!S21</f>
         <v/>
       </c>
       <c r="T19" s="62"/>
       <c r="U19" s="55"/>
       <c r="V19" s="56"/>
-      <c r="W19" s="58" t="str">
+      <c r="W19" s="125" t="str">
         <f>'[1]TERM 1'!W21</f>
         <v/>
       </c>
-      <c r="X19" s="59" t="str">
+      <c r="X19" s="126" t="str">
         <f>'[1]TERM 1'!X21</f>
         <v/>
       </c>
-      <c r="Y19" s="63" t="str">
+      <c r="Y19" s="128" t="str">
         <f>'[1]TERM 1'!Y21</f>
         <v/>
       </c>
-      <c r="Z19" s="58" t="str">
+      <c r="Z19" s="125" t="str">
         <f>'[1]TERM 1'!Z21</f>
         <v/>
       </c>
-      <c r="AA19" s="61" t="str">
+      <c r="AA19" s="127" t="str">
         <f>'[1]TERM 1'!AA21</f>
         <v/>
       </c>
@@ -7168,11 +7252,11 @@
         <f>'[1]TERM 1'!K22</f>
         <v/>
       </c>
-      <c r="L20" s="58" t="str">
+      <c r="L20" s="125" t="str">
         <f>'[1]TERM 1'!L22</f>
         <v/>
       </c>
-      <c r="M20" s="59" t="str">
+      <c r="M20" s="126" t="str">
         <f>'[1]TERM 1'!M22</f>
         <v/>
       </c>
@@ -7183,34 +7267,34 @@
         <f>'[1]TERM 1'!Q22</f>
         <v/>
       </c>
-      <c r="R20" s="58" t="str">
+      <c r="R20" s="125" t="str">
         <f>'[1]TERM 1'!R22</f>
         <v/>
       </c>
-      <c r="S20" s="61" t="str">
+      <c r="S20" s="127" t="str">
         <f>'[1]TERM 1'!S22</f>
         <v/>
       </c>
       <c r="T20" s="62"/>
       <c r="U20" s="55"/>
       <c r="V20" s="56"/>
-      <c r="W20" s="58" t="str">
+      <c r="W20" s="125" t="str">
         <f>'[1]TERM 1'!W22</f>
         <v/>
       </c>
-      <c r="X20" s="59" t="str">
+      <c r="X20" s="126" t="str">
         <f>'[1]TERM 1'!X22</f>
         <v/>
       </c>
-      <c r="Y20" s="63" t="str">
+      <c r="Y20" s="128" t="str">
         <f>'[1]TERM 1'!Y22</f>
         <v/>
       </c>
-      <c r="Z20" s="58" t="str">
+      <c r="Z20" s="125" t="str">
         <f>'[1]TERM 1'!Z22</f>
         <v/>
       </c>
-      <c r="AA20" s="61" t="str">
+      <c r="AA20" s="127" t="str">
         <f>'[1]TERM 1'!AA22</f>
         <v/>
       </c>
@@ -7244,11 +7328,11 @@
         <f>'[1]TERM 1'!K23</f>
         <v/>
       </c>
-      <c r="L21" s="58" t="str">
+      <c r="L21" s="125" t="str">
         <f>'[1]TERM 1'!L23</f>
         <v/>
       </c>
-      <c r="M21" s="59" t="str">
+      <c r="M21" s="126" t="str">
         <f>'[1]TERM 1'!M23</f>
         <v/>
       </c>
@@ -7259,34 +7343,34 @@
         <f>'[1]TERM 1'!Q23</f>
         <v/>
       </c>
-      <c r="R21" s="58" t="str">
+      <c r="R21" s="125" t="str">
         <f>'[1]TERM 1'!R23</f>
         <v/>
       </c>
-      <c r="S21" s="61" t="str">
+      <c r="S21" s="127" t="str">
         <f>'[1]TERM 1'!S23</f>
         <v/>
       </c>
       <c r="T21" s="62"/>
       <c r="U21" s="55"/>
       <c r="V21" s="56"/>
-      <c r="W21" s="58" t="str">
+      <c r="W21" s="125" t="str">
         <f>'[1]TERM 1'!W23</f>
         <v/>
       </c>
-      <c r="X21" s="59" t="str">
+      <c r="X21" s="126" t="str">
         <f>'[1]TERM 1'!X23</f>
         <v/>
       </c>
-      <c r="Y21" s="63" t="str">
+      <c r="Y21" s="128" t="str">
         <f>'[1]TERM 1'!Y23</f>
         <v/>
       </c>
-      <c r="Z21" s="58" t="str">
+      <c r="Z21" s="125" t="str">
         <f>'[1]TERM 1'!Z23</f>
         <v/>
       </c>
-      <c r="AA21" s="61" t="str">
+      <c r="AA21" s="127" t="str">
         <f>'[1]TERM 1'!AA23</f>
         <v/>
       </c>
@@ -7320,11 +7404,11 @@
         <f>'[1]TERM 1'!K24</f>
         <v/>
       </c>
-      <c r="L22" s="58" t="str">
+      <c r="L22" s="125" t="str">
         <f>'[1]TERM 1'!L24</f>
         <v/>
       </c>
-      <c r="M22" s="59" t="str">
+      <c r="M22" s="126" t="str">
         <f>'[1]TERM 1'!M24</f>
         <v/>
       </c>
@@ -7335,34 +7419,34 @@
         <f>'[1]TERM 1'!Q24</f>
         <v/>
       </c>
-      <c r="R22" s="58" t="str">
+      <c r="R22" s="125" t="str">
         <f>'[1]TERM 1'!R24</f>
         <v/>
       </c>
-      <c r="S22" s="61" t="str">
+      <c r="S22" s="127" t="str">
         <f>'[1]TERM 1'!S24</f>
         <v/>
       </c>
       <c r="T22" s="62"/>
       <c r="U22" s="55"/>
       <c r="V22" s="56"/>
-      <c r="W22" s="58" t="str">
+      <c r="W22" s="125" t="str">
         <f>'[1]TERM 1'!W24</f>
         <v/>
       </c>
-      <c r="X22" s="59" t="str">
+      <c r="X22" s="126" t="str">
         <f>'[1]TERM 1'!X24</f>
         <v/>
       </c>
-      <c r="Y22" s="63" t="str">
+      <c r="Y22" s="128" t="str">
         <f>'[1]TERM 1'!Y24</f>
         <v/>
       </c>
-      <c r="Z22" s="58" t="str">
+      <c r="Z22" s="125" t="str">
         <f>'[1]TERM 1'!Z24</f>
         <v/>
       </c>
-      <c r="AA22" s="61" t="str">
+      <c r="AA22" s="127" t="str">
         <f>'[1]TERM 1'!AA24</f>
         <v/>
       </c>
@@ -7396,11 +7480,11 @@
         <f>'[1]TERM 1'!K25</f>
         <v/>
       </c>
-      <c r="L23" s="58" t="str">
+      <c r="L23" s="125" t="str">
         <f>'[1]TERM 1'!L25</f>
         <v/>
       </c>
-      <c r="M23" s="59" t="str">
+      <c r="M23" s="126" t="str">
         <f>'[1]TERM 1'!M25</f>
         <v/>
       </c>
@@ -7411,34 +7495,34 @@
         <f>'[1]TERM 1'!Q25</f>
         <v/>
       </c>
-      <c r="R23" s="58" t="str">
+      <c r="R23" s="125" t="str">
         <f>'[1]TERM 1'!R25</f>
         <v/>
       </c>
-      <c r="S23" s="61" t="str">
+      <c r="S23" s="127" t="str">
         <f>'[1]TERM 1'!S25</f>
         <v/>
       </c>
       <c r="T23" s="62"/>
       <c r="U23" s="55"/>
       <c r="V23" s="56"/>
-      <c r="W23" s="58" t="str">
+      <c r="W23" s="125" t="str">
         <f>'[1]TERM 1'!W25</f>
         <v/>
       </c>
-      <c r="X23" s="59" t="str">
+      <c r="X23" s="126" t="str">
         <f>'[1]TERM 1'!X25</f>
         <v/>
       </c>
-      <c r="Y23" s="63" t="str">
+      <c r="Y23" s="128" t="str">
         <f>'[1]TERM 1'!Y25</f>
         <v/>
       </c>
-      <c r="Z23" s="58" t="str">
+      <c r="Z23" s="125" t="str">
         <f>'[1]TERM 1'!Z25</f>
         <v/>
       </c>
-      <c r="AA23" s="61" t="str">
+      <c r="AA23" s="127" t="str">
         <f>'[1]TERM 1'!AA25</f>
         <v/>
       </c>
@@ -7472,11 +7556,11 @@
         <f>'[1]TERM 1'!K26</f>
         <v/>
       </c>
-      <c r="L24" s="58" t="str">
+      <c r="L24" s="125" t="str">
         <f>'[1]TERM 1'!L26</f>
         <v/>
       </c>
-      <c r="M24" s="59" t="str">
+      <c r="M24" s="126" t="str">
         <f>'[1]TERM 1'!M26</f>
         <v/>
       </c>
@@ -7487,34 +7571,34 @@
         <f>'[1]TERM 1'!Q26</f>
         <v/>
       </c>
-      <c r="R24" s="58" t="str">
+      <c r="R24" s="125" t="str">
         <f>'[1]TERM 1'!R26</f>
         <v/>
       </c>
-      <c r="S24" s="61" t="str">
+      <c r="S24" s="127" t="str">
         <f>'[1]TERM 1'!S26</f>
         <v/>
       </c>
       <c r="T24" s="62"/>
       <c r="U24" s="55"/>
       <c r="V24" s="56"/>
-      <c r="W24" s="58" t="str">
+      <c r="W24" s="125" t="str">
         <f>'[1]TERM 1'!W26</f>
         <v/>
       </c>
-      <c r="X24" s="59" t="str">
+      <c r="X24" s="126" t="str">
         <f>'[1]TERM 1'!X26</f>
         <v/>
       </c>
-      <c r="Y24" s="63" t="str">
+      <c r="Y24" s="128" t="str">
         <f>'[1]TERM 1'!Y26</f>
         <v/>
       </c>
-      <c r="Z24" s="58" t="str">
+      <c r="Z24" s="125" t="str">
         <f>'[1]TERM 1'!Z26</f>
         <v/>
       </c>
-      <c r="AA24" s="61" t="str">
+      <c r="AA24" s="127" t="str">
         <f>'[1]TERM 1'!AA26</f>
         <v/>
       </c>
@@ -7548,11 +7632,11 @@
         <f>'[1]TERM 1'!K27</f>
         <v/>
       </c>
-      <c r="L25" s="58" t="str">
+      <c r="L25" s="125" t="str">
         <f>'[1]TERM 1'!L27</f>
         <v/>
       </c>
-      <c r="M25" s="59" t="str">
+      <c r="M25" s="126" t="str">
         <f>'[1]TERM 1'!M27</f>
         <v/>
       </c>
@@ -7563,34 +7647,34 @@
         <f>'[1]TERM 1'!Q27</f>
         <v/>
       </c>
-      <c r="R25" s="58" t="str">
+      <c r="R25" s="125" t="str">
         <f>'[1]TERM 1'!R27</f>
         <v/>
       </c>
-      <c r="S25" s="61" t="str">
+      <c r="S25" s="127" t="str">
         <f>'[1]TERM 1'!S27</f>
         <v/>
       </c>
       <c r="T25" s="62"/>
       <c r="U25" s="55"/>
       <c r="V25" s="56"/>
-      <c r="W25" s="58" t="str">
+      <c r="W25" s="125" t="str">
         <f>'[1]TERM 1'!W27</f>
         <v/>
       </c>
-      <c r="X25" s="59" t="str">
+      <c r="X25" s="126" t="str">
         <f>'[1]TERM 1'!X27</f>
         <v/>
       </c>
-      <c r="Y25" s="63" t="str">
+      <c r="Y25" s="128" t="str">
         <f>'[1]TERM 1'!Y27</f>
         <v/>
       </c>
-      <c r="Z25" s="58" t="str">
+      <c r="Z25" s="125" t="str">
         <f>'[1]TERM 1'!Z27</f>
         <v/>
       </c>
-      <c r="AA25" s="61" t="str">
+      <c r="AA25" s="127" t="str">
         <f>'[1]TERM 1'!AA27</f>
         <v/>
       </c>
@@ -7624,11 +7708,11 @@
         <f>'[1]TERM 1'!K28</f>
         <v/>
       </c>
-      <c r="L26" s="58" t="str">
+      <c r="L26" s="125" t="str">
         <f>'[1]TERM 1'!L28</f>
         <v/>
       </c>
-      <c r="M26" s="59" t="str">
+      <c r="M26" s="126" t="str">
         <f>'[1]TERM 1'!M28</f>
         <v/>
       </c>
@@ -7639,34 +7723,34 @@
         <f>'[1]TERM 1'!Q28</f>
         <v/>
       </c>
-      <c r="R26" s="58" t="str">
+      <c r="R26" s="125" t="str">
         <f>'[1]TERM 1'!R28</f>
         <v/>
       </c>
-      <c r="S26" s="61" t="str">
+      <c r="S26" s="127" t="str">
         <f>'[1]TERM 1'!S28</f>
         <v/>
       </c>
       <c r="T26" s="62"/>
       <c r="U26" s="55"/>
       <c r="V26" s="56"/>
-      <c r="W26" s="58" t="str">
+      <c r="W26" s="125" t="str">
         <f>'[1]TERM 1'!W28</f>
         <v/>
       </c>
-      <c r="X26" s="59" t="str">
+      <c r="X26" s="126" t="str">
         <f>'[1]TERM 1'!X28</f>
         <v/>
       </c>
-      <c r="Y26" s="63" t="str">
+      <c r="Y26" s="128" t="str">
         <f>'[1]TERM 1'!Y28</f>
         <v/>
       </c>
-      <c r="Z26" s="58" t="str">
+      <c r="Z26" s="125" t="str">
         <f>'[1]TERM 1'!Z28</f>
         <v/>
       </c>
-      <c r="AA26" s="61" t="str">
+      <c r="AA26" s="127" t="str">
         <f>'[1]TERM 1'!AA28</f>
         <v/>
       </c>
@@ -7700,11 +7784,11 @@
         <f>'[1]TERM 1'!K29</f>
         <v/>
       </c>
-      <c r="L27" s="58" t="str">
+      <c r="L27" s="125" t="str">
         <f>'[1]TERM 1'!L29</f>
         <v/>
       </c>
-      <c r="M27" s="59" t="str">
+      <c r="M27" s="126" t="str">
         <f>'[1]TERM 1'!M29</f>
         <v/>
       </c>
@@ -7715,34 +7799,34 @@
         <f>'[1]TERM 1'!Q29</f>
         <v/>
       </c>
-      <c r="R27" s="58" t="str">
+      <c r="R27" s="125" t="str">
         <f>'[1]TERM 1'!R29</f>
         <v/>
       </c>
-      <c r="S27" s="61" t="str">
+      <c r="S27" s="127" t="str">
         <f>'[1]TERM 1'!S29</f>
         <v/>
       </c>
       <c r="T27" s="62"/>
       <c r="U27" s="55"/>
       <c r="V27" s="56"/>
-      <c r="W27" s="58" t="str">
+      <c r="W27" s="125" t="str">
         <f>'[1]TERM 1'!W29</f>
         <v/>
       </c>
-      <c r="X27" s="59" t="str">
+      <c r="X27" s="126" t="str">
         <f>'[1]TERM 1'!X29</f>
         <v/>
       </c>
-      <c r="Y27" s="63" t="str">
+      <c r="Y27" s="128" t="str">
         <f>'[1]TERM 1'!Y29</f>
         <v/>
       </c>
-      <c r="Z27" s="58" t="str">
+      <c r="Z27" s="125" t="str">
         <f>'[1]TERM 1'!Z29</f>
         <v/>
       </c>
-      <c r="AA27" s="61" t="str">
+      <c r="AA27" s="127" t="str">
         <f>'[1]TERM 1'!AA29</f>
         <v/>
       </c>
@@ -7776,11 +7860,11 @@
         <f>'[1]TERM 1'!K30</f>
         <v/>
       </c>
-      <c r="L28" s="58" t="str">
+      <c r="L28" s="125" t="str">
         <f>'[1]TERM 1'!L30</f>
         <v/>
       </c>
-      <c r="M28" s="59" t="str">
+      <c r="M28" s="126" t="str">
         <f>'[1]TERM 1'!M30</f>
         <v/>
       </c>
@@ -7791,34 +7875,34 @@
         <f>'[1]TERM 1'!Q30</f>
         <v/>
       </c>
-      <c r="R28" s="58" t="str">
+      <c r="R28" s="125" t="str">
         <f>'[1]TERM 1'!R30</f>
         <v/>
       </c>
-      <c r="S28" s="61" t="str">
+      <c r="S28" s="127" t="str">
         <f>'[1]TERM 1'!S30</f>
         <v/>
       </c>
       <c r="T28" s="62"/>
       <c r="U28" s="55"/>
       <c r="V28" s="56"/>
-      <c r="W28" s="58" t="str">
+      <c r="W28" s="125" t="str">
         <f>'[1]TERM 1'!W30</f>
         <v/>
       </c>
-      <c r="X28" s="59" t="str">
+      <c r="X28" s="126" t="str">
         <f>'[1]TERM 1'!X30</f>
         <v/>
       </c>
-      <c r="Y28" s="63" t="str">
+      <c r="Y28" s="128" t="str">
         <f>'[1]TERM 1'!Y30</f>
         <v/>
       </c>
-      <c r="Z28" s="58" t="str">
+      <c r="Z28" s="125" t="str">
         <f>'[1]TERM 1'!Z30</f>
         <v/>
       </c>
-      <c r="AA28" s="61" t="str">
+      <c r="AA28" s="127" t="str">
         <f>'[1]TERM 1'!AA30</f>
         <v/>
       </c>
@@ -7852,11 +7936,11 @@
         <f>'[1]TERM 1'!K31</f>
         <v/>
       </c>
-      <c r="L29" s="58" t="str">
+      <c r="L29" s="125" t="str">
         <f>'[1]TERM 1'!L31</f>
         <v/>
       </c>
-      <c r="M29" s="59" t="str">
+      <c r="M29" s="126" t="str">
         <f>'[1]TERM 1'!M31</f>
         <v/>
       </c>
@@ -7867,34 +7951,34 @@
         <f>'[1]TERM 1'!Q31</f>
         <v/>
       </c>
-      <c r="R29" s="58" t="str">
+      <c r="R29" s="125" t="str">
         <f>'[1]TERM 1'!R31</f>
         <v/>
       </c>
-      <c r="S29" s="61" t="str">
+      <c r="S29" s="127" t="str">
         <f>'[1]TERM 1'!S31</f>
         <v/>
       </c>
       <c r="T29" s="62"/>
       <c r="U29" s="55"/>
       <c r="V29" s="56"/>
-      <c r="W29" s="58" t="str">
+      <c r="W29" s="125" t="str">
         <f>'[1]TERM 1'!W31</f>
         <v/>
       </c>
-      <c r="X29" s="59" t="str">
+      <c r="X29" s="126" t="str">
         <f>'[1]TERM 1'!X31</f>
         <v/>
       </c>
-      <c r="Y29" s="63" t="str">
+      <c r="Y29" s="128" t="str">
         <f>'[1]TERM 1'!Y31</f>
         <v/>
       </c>
-      <c r="Z29" s="58" t="str">
+      <c r="Z29" s="125" t="str">
         <f>'[1]TERM 1'!Z31</f>
         <v/>
       </c>
-      <c r="AA29" s="61" t="str">
+      <c r="AA29" s="127" t="str">
         <f>'[1]TERM 1'!AA31</f>
         <v/>
       </c>
@@ -7928,11 +8012,11 @@
         <f>'[1]TERM 1'!K32</f>
         <v/>
       </c>
-      <c r="L30" s="58" t="str">
+      <c r="L30" s="125" t="str">
         <f>'[1]TERM 1'!L32</f>
         <v/>
       </c>
-      <c r="M30" s="59" t="str">
+      <c r="M30" s="126" t="str">
         <f>'[1]TERM 1'!M32</f>
         <v/>
       </c>
@@ -7943,34 +8027,34 @@
         <f>'[1]TERM 1'!Q32</f>
         <v/>
       </c>
-      <c r="R30" s="58" t="str">
+      <c r="R30" s="125" t="str">
         <f>'[1]TERM 1'!R32</f>
         <v/>
       </c>
-      <c r="S30" s="61" t="str">
+      <c r="S30" s="127" t="str">
         <f>'[1]TERM 1'!S32</f>
         <v/>
       </c>
       <c r="T30" s="62"/>
       <c r="U30" s="55"/>
       <c r="V30" s="56"/>
-      <c r="W30" s="58" t="str">
+      <c r="W30" s="125" t="str">
         <f>'[1]TERM 1'!W32</f>
         <v/>
       </c>
-      <c r="X30" s="59" t="str">
+      <c r="X30" s="126" t="str">
         <f>'[1]TERM 1'!X32</f>
         <v/>
       </c>
-      <c r="Y30" s="63" t="str">
+      <c r="Y30" s="128" t="str">
         <f>'[1]TERM 1'!Y32</f>
         <v/>
       </c>
-      <c r="Z30" s="58" t="str">
+      <c r="Z30" s="125" t="str">
         <f>'[1]TERM 1'!Z32</f>
         <v/>
       </c>
-      <c r="AA30" s="61" t="str">
+      <c r="AA30" s="127" t="str">
         <f>'[1]TERM 1'!AA32</f>
         <v/>
       </c>
@@ -8004,11 +8088,11 @@
         <f>'[1]TERM 1'!K33</f>
         <v/>
       </c>
-      <c r="L31" s="58" t="str">
+      <c r="L31" s="125" t="str">
         <f>'[1]TERM 1'!L33</f>
         <v/>
       </c>
-      <c r="M31" s="59" t="str">
+      <c r="M31" s="126" t="str">
         <f>'[1]TERM 1'!M33</f>
         <v/>
       </c>
@@ -8019,34 +8103,34 @@
         <f>'[1]TERM 1'!Q33</f>
         <v/>
       </c>
-      <c r="R31" s="58" t="str">
+      <c r="R31" s="125" t="str">
         <f>'[1]TERM 1'!R33</f>
         <v/>
       </c>
-      <c r="S31" s="61" t="str">
+      <c r="S31" s="127" t="str">
         <f>'[1]TERM 1'!S33</f>
         <v/>
       </c>
       <c r="T31" s="62"/>
       <c r="U31" s="55"/>
       <c r="V31" s="56"/>
-      <c r="W31" s="58" t="str">
+      <c r="W31" s="125" t="str">
         <f>'[1]TERM 1'!W33</f>
         <v/>
       </c>
-      <c r="X31" s="59" t="str">
+      <c r="X31" s="126" t="str">
         <f>'[1]TERM 1'!X33</f>
         <v/>
       </c>
-      <c r="Y31" s="63" t="str">
+      <c r="Y31" s="128" t="str">
         <f>'[1]TERM 1'!Y33</f>
         <v/>
       </c>
-      <c r="Z31" s="58" t="str">
+      <c r="Z31" s="125" t="str">
         <f>'[1]TERM 1'!Z33</f>
         <v/>
       </c>
-      <c r="AA31" s="61" t="str">
+      <c r="AA31" s="127" t="str">
         <f>'[1]TERM 1'!AA33</f>
         <v/>
       </c>
@@ -8080,11 +8164,11 @@
         <f>'[1]TERM 1'!K34</f>
         <v/>
       </c>
-      <c r="L32" s="58" t="str">
+      <c r="L32" s="125" t="str">
         <f>'[1]TERM 1'!L34</f>
         <v/>
       </c>
-      <c r="M32" s="59" t="str">
+      <c r="M32" s="126" t="str">
         <f>'[1]TERM 1'!M34</f>
         <v/>
       </c>
@@ -8095,34 +8179,34 @@
         <f>'[1]TERM 1'!Q34</f>
         <v/>
       </c>
-      <c r="R32" s="58" t="str">
+      <c r="R32" s="125" t="str">
         <f>'[1]TERM 1'!R34</f>
         <v/>
       </c>
-      <c r="S32" s="61" t="str">
+      <c r="S32" s="127" t="str">
         <f>'[1]TERM 1'!S34</f>
         <v/>
       </c>
       <c r="T32" s="62"/>
       <c r="U32" s="55"/>
       <c r="V32" s="56"/>
-      <c r="W32" s="58" t="str">
+      <c r="W32" s="125" t="str">
         <f>'[1]TERM 1'!W34</f>
         <v/>
       </c>
-      <c r="X32" s="59" t="str">
+      <c r="X32" s="126" t="str">
         <f>'[1]TERM 1'!X34</f>
         <v/>
       </c>
-      <c r="Y32" s="63" t="str">
+      <c r="Y32" s="128" t="str">
         <f>'[1]TERM 1'!Y34</f>
         <v/>
       </c>
-      <c r="Z32" s="58" t="str">
+      <c r="Z32" s="125" t="str">
         <f>'[1]TERM 1'!Z34</f>
         <v/>
       </c>
-      <c r="AA32" s="61" t="str">
+      <c r="AA32" s="127" t="str">
         <f>'[1]TERM 1'!AA34</f>
         <v/>
       </c>
@@ -8156,11 +8240,11 @@
         <f>'[1]TERM 1'!K35</f>
         <v/>
       </c>
-      <c r="L33" s="58" t="str">
+      <c r="L33" s="125" t="str">
         <f>'[1]TERM 1'!L35</f>
         <v/>
       </c>
-      <c r="M33" s="59" t="str">
+      <c r="M33" s="126" t="str">
         <f>'[1]TERM 1'!M35</f>
         <v/>
       </c>
@@ -8171,34 +8255,34 @@
         <f>'[1]TERM 1'!Q35</f>
         <v/>
       </c>
-      <c r="R33" s="58" t="str">
+      <c r="R33" s="125" t="str">
         <f>'[1]TERM 1'!R35</f>
         <v/>
       </c>
-      <c r="S33" s="61" t="str">
+      <c r="S33" s="127" t="str">
         <f>'[1]TERM 1'!S35</f>
         <v/>
       </c>
       <c r="T33" s="62"/>
       <c r="U33" s="55"/>
       <c r="V33" s="56"/>
-      <c r="W33" s="58" t="str">
+      <c r="W33" s="125" t="str">
         <f>'[1]TERM 1'!W35</f>
         <v/>
       </c>
-      <c r="X33" s="59" t="str">
+      <c r="X33" s="126" t="str">
         <f>'[1]TERM 1'!X35</f>
         <v/>
       </c>
-      <c r="Y33" s="63" t="str">
+      <c r="Y33" s="128" t="str">
         <f>'[1]TERM 1'!Y35</f>
         <v/>
       </c>
-      <c r="Z33" s="58" t="str">
+      <c r="Z33" s="125" t="str">
         <f>'[1]TERM 1'!Z35</f>
         <v/>
       </c>
-      <c r="AA33" s="61" t="str">
+      <c r="AA33" s="127" t="str">
         <f>'[1]TERM 1'!AA35</f>
         <v/>
       </c>
@@ -8232,11 +8316,11 @@
         <f>'[1]TERM 1'!K36</f>
         <v/>
       </c>
-      <c r="L34" s="58" t="str">
+      <c r="L34" s="125" t="str">
         <f>'[1]TERM 1'!L36</f>
         <v/>
       </c>
-      <c r="M34" s="59" t="str">
+      <c r="M34" s="126" t="str">
         <f>'[1]TERM 1'!M36</f>
         <v/>
       </c>
@@ -8247,34 +8331,34 @@
         <f>'[1]TERM 1'!Q36</f>
         <v/>
       </c>
-      <c r="R34" s="58" t="str">
+      <c r="R34" s="125" t="str">
         <f>'[1]TERM 1'!R36</f>
         <v/>
       </c>
-      <c r="S34" s="61" t="str">
+      <c r="S34" s="127" t="str">
         <f>'[1]TERM 1'!S36</f>
         <v/>
       </c>
       <c r="T34" s="62"/>
       <c r="U34" s="55"/>
       <c r="V34" s="56"/>
-      <c r="W34" s="58" t="str">
+      <c r="W34" s="125" t="str">
         <f>'[1]TERM 1'!W36</f>
         <v/>
       </c>
-      <c r="X34" s="59" t="str">
+      <c r="X34" s="126" t="str">
         <f>'[1]TERM 1'!X36</f>
         <v/>
       </c>
-      <c r="Y34" s="63" t="str">
+      <c r="Y34" s="128" t="str">
         <f>'[1]TERM 1'!Y36</f>
         <v/>
       </c>
-      <c r="Z34" s="58" t="str">
+      <c r="Z34" s="125" t="str">
         <f>'[1]TERM 1'!Z36</f>
         <v/>
       </c>
-      <c r="AA34" s="61" t="str">
+      <c r="AA34" s="127" t="str">
         <f>'[1]TERM 1'!AA36</f>
         <v/>
       </c>
@@ -8308,11 +8392,11 @@
         <f>'[1]TERM 1'!K37</f>
         <v/>
       </c>
-      <c r="L35" s="58" t="str">
+      <c r="L35" s="125" t="str">
         <f>'[1]TERM 1'!L37</f>
         <v/>
       </c>
-      <c r="M35" s="59" t="str">
+      <c r="M35" s="126" t="str">
         <f>'[1]TERM 1'!M37</f>
         <v/>
       </c>
@@ -8323,34 +8407,34 @@
         <f>'[1]TERM 1'!Q37</f>
         <v/>
       </c>
-      <c r="R35" s="58" t="str">
+      <c r="R35" s="125" t="str">
         <f>'[1]TERM 1'!R37</f>
         <v/>
       </c>
-      <c r="S35" s="61" t="str">
+      <c r="S35" s="127" t="str">
         <f>'[1]TERM 1'!S37</f>
         <v/>
       </c>
       <c r="T35" s="62"/>
       <c r="U35" s="55"/>
       <c r="V35" s="56"/>
-      <c r="W35" s="58" t="str">
+      <c r="W35" s="125" t="str">
         <f>'[1]TERM 1'!W37</f>
         <v/>
       </c>
-      <c r="X35" s="59" t="str">
+      <c r="X35" s="126" t="str">
         <f>'[1]TERM 1'!X37</f>
         <v/>
       </c>
-      <c r="Y35" s="63" t="str">
+      <c r="Y35" s="128" t="str">
         <f>'[1]TERM 1'!Y37</f>
         <v/>
       </c>
-      <c r="Z35" s="58" t="str">
+      <c r="Z35" s="125" t="str">
         <f>'[1]TERM 1'!Z37</f>
         <v/>
       </c>
-      <c r="AA35" s="61" t="str">
+      <c r="AA35" s="127" t="str">
         <f>'[1]TERM 1'!AA37</f>
         <v/>
       </c>
@@ -8384,11 +8468,11 @@
         <f>'[1]TERM 1'!K38</f>
         <v/>
       </c>
-      <c r="L36" s="58" t="str">
+      <c r="L36" s="125" t="str">
         <f>'[1]TERM 1'!L38</f>
         <v/>
       </c>
-      <c r="M36" s="59" t="str">
+      <c r="M36" s="126" t="str">
         <f>'[1]TERM 1'!M38</f>
         <v/>
       </c>
@@ -8399,34 +8483,34 @@
         <f>'[1]TERM 1'!Q38</f>
         <v/>
       </c>
-      <c r="R36" s="58" t="str">
+      <c r="R36" s="125" t="str">
         <f>'[1]TERM 1'!R38</f>
         <v/>
       </c>
-      <c r="S36" s="61" t="str">
+      <c r="S36" s="127" t="str">
         <f>'[1]TERM 1'!S38</f>
         <v/>
       </c>
       <c r="T36" s="62"/>
       <c r="U36" s="55"/>
       <c r="V36" s="56"/>
-      <c r="W36" s="58" t="str">
+      <c r="W36" s="125" t="str">
         <f>'[1]TERM 1'!W38</f>
         <v/>
       </c>
-      <c r="X36" s="59" t="str">
+      <c r="X36" s="126" t="str">
         <f>'[1]TERM 1'!X38</f>
         <v/>
       </c>
-      <c r="Y36" s="63" t="str">
+      <c r="Y36" s="128" t="str">
         <f>'[1]TERM 1'!Y38</f>
         <v/>
       </c>
-      <c r="Z36" s="58" t="str">
+      <c r="Z36" s="125" t="str">
         <f>'[1]TERM 1'!Z38</f>
         <v/>
       </c>
-      <c r="AA36" s="61" t="str">
+      <c r="AA36" s="127" t="str">
         <f>'[1]TERM 1'!AA38</f>
         <v/>
       </c>
@@ -8460,11 +8544,11 @@
         <f>'[1]TERM 1'!K39</f>
         <v/>
       </c>
-      <c r="L37" s="58" t="str">
+      <c r="L37" s="125" t="str">
         <f>'[1]TERM 1'!L39</f>
         <v/>
       </c>
-      <c r="M37" s="59" t="str">
+      <c r="M37" s="126" t="str">
         <f>'[1]TERM 1'!M39</f>
         <v/>
       </c>
@@ -8475,34 +8559,34 @@
         <f>'[1]TERM 1'!Q39</f>
         <v/>
       </c>
-      <c r="R37" s="58" t="str">
+      <c r="R37" s="125" t="str">
         <f>'[1]TERM 1'!R39</f>
         <v/>
       </c>
-      <c r="S37" s="61" t="str">
+      <c r="S37" s="127" t="str">
         <f>'[1]TERM 1'!S39</f>
         <v/>
       </c>
       <c r="T37" s="62"/>
       <c r="U37" s="55"/>
       <c r="V37" s="56"/>
-      <c r="W37" s="58" t="str">
+      <c r="W37" s="125" t="str">
         <f>'[1]TERM 1'!W39</f>
         <v/>
       </c>
-      <c r="X37" s="59" t="str">
+      <c r="X37" s="126" t="str">
         <f>'[1]TERM 1'!X39</f>
         <v/>
       </c>
-      <c r="Y37" s="63" t="str">
+      <c r="Y37" s="128" t="str">
         <f>'[1]TERM 1'!Y39</f>
         <v/>
       </c>
-      <c r="Z37" s="58" t="str">
+      <c r="Z37" s="125" t="str">
         <f>'[1]TERM 1'!Z39</f>
         <v/>
       </c>
-      <c r="AA37" s="61" t="str">
+      <c r="AA37" s="127" t="str">
         <f>'[1]TERM 1'!AA39</f>
         <v/>
       </c>
@@ -8536,11 +8620,11 @@
         <f>'[1]TERM 1'!K40</f>
         <v/>
       </c>
-      <c r="L38" s="58" t="str">
+      <c r="L38" s="125" t="str">
         <f>'[1]TERM 1'!L40</f>
         <v/>
       </c>
-      <c r="M38" s="59" t="str">
+      <c r="M38" s="126" t="str">
         <f>'[1]TERM 1'!M40</f>
         <v/>
       </c>
@@ -8551,34 +8635,34 @@
         <f>'[1]TERM 1'!Q40</f>
         <v/>
       </c>
-      <c r="R38" s="58" t="str">
+      <c r="R38" s="125" t="str">
         <f>'[1]TERM 1'!R40</f>
         <v/>
       </c>
-      <c r="S38" s="61" t="str">
+      <c r="S38" s="127" t="str">
         <f>'[1]TERM 1'!S40</f>
         <v/>
       </c>
       <c r="T38" s="62"/>
       <c r="U38" s="55"/>
       <c r="V38" s="56"/>
-      <c r="W38" s="58" t="str">
+      <c r="W38" s="125" t="str">
         <f>'[1]TERM 1'!W40</f>
         <v/>
       </c>
-      <c r="X38" s="59" t="str">
+      <c r="X38" s="126" t="str">
         <f>'[1]TERM 1'!X40</f>
         <v/>
       </c>
-      <c r="Y38" s="63" t="str">
+      <c r="Y38" s="128" t="str">
         <f>'[1]TERM 1'!Y40</f>
         <v/>
       </c>
-      <c r="Z38" s="58" t="str">
+      <c r="Z38" s="125" t="str">
         <f>'[1]TERM 1'!Z40</f>
         <v/>
       </c>
-      <c r="AA38" s="61" t="str">
+      <c r="AA38" s="127" t="str">
         <f>'[1]TERM 1'!AA40</f>
         <v/>
       </c>
@@ -8612,11 +8696,11 @@
         <f>'[1]TERM 1'!K41</f>
         <v/>
       </c>
-      <c r="L39" s="58" t="str">
+      <c r="L39" s="125" t="str">
         <f>'[1]TERM 1'!L41</f>
         <v/>
       </c>
-      <c r="M39" s="59" t="str">
+      <c r="M39" s="126" t="str">
         <f>'[1]TERM 1'!M41</f>
         <v/>
       </c>
@@ -8627,34 +8711,34 @@
         <f>'[1]TERM 1'!Q41</f>
         <v/>
       </c>
-      <c r="R39" s="58" t="str">
+      <c r="R39" s="125" t="str">
         <f>'[1]TERM 1'!R41</f>
         <v/>
       </c>
-      <c r="S39" s="61" t="str">
+      <c r="S39" s="127" t="str">
         <f>'[1]TERM 1'!S41</f>
         <v/>
       </c>
       <c r="T39" s="62"/>
       <c r="U39" s="55"/>
       <c r="V39" s="56"/>
-      <c r="W39" s="58" t="str">
+      <c r="W39" s="125" t="str">
         <f>'[1]TERM 1'!W41</f>
         <v/>
       </c>
-      <c r="X39" s="59" t="str">
+      <c r="X39" s="126" t="str">
         <f>'[1]TERM 1'!X41</f>
         <v/>
       </c>
-      <c r="Y39" s="63" t="str">
+      <c r="Y39" s="128" t="str">
         <f>'[1]TERM 1'!Y41</f>
         <v/>
       </c>
-      <c r="Z39" s="58" t="str">
+      <c r="Z39" s="125" t="str">
         <f>'[1]TERM 1'!Z41</f>
         <v/>
       </c>
-      <c r="AA39" s="61" t="str">
+      <c r="AA39" s="127" t="str">
         <f>'[1]TERM 1'!AA41</f>
         <v/>
       </c>
@@ -8688,11 +8772,11 @@
         <f>'[1]TERM 1'!K42</f>
         <v/>
       </c>
-      <c r="L40" s="58" t="str">
+      <c r="L40" s="125" t="str">
         <f>'[1]TERM 1'!L42</f>
         <v/>
       </c>
-      <c r="M40" s="59" t="str">
+      <c r="M40" s="126" t="str">
         <f>'[1]TERM 1'!M42</f>
         <v/>
       </c>
@@ -8703,34 +8787,34 @@
         <f>'[1]TERM 1'!Q42</f>
         <v/>
       </c>
-      <c r="R40" s="58" t="str">
+      <c r="R40" s="125" t="str">
         <f>'[1]TERM 1'!R42</f>
         <v/>
       </c>
-      <c r="S40" s="61" t="str">
+      <c r="S40" s="127" t="str">
         <f>'[1]TERM 1'!S42</f>
         <v/>
       </c>
       <c r="T40" s="62"/>
       <c r="U40" s="55"/>
       <c r="V40" s="56"/>
-      <c r="W40" s="58" t="str">
+      <c r="W40" s="125" t="str">
         <f>'[1]TERM 1'!W42</f>
         <v/>
       </c>
-      <c r="X40" s="59" t="str">
+      <c r="X40" s="126" t="str">
         <f>'[1]TERM 1'!X42</f>
         <v/>
       </c>
-      <c r="Y40" s="63" t="str">
+      <c r="Y40" s="128" t="str">
         <f>'[1]TERM 1'!Y42</f>
         <v/>
       </c>
-      <c r="Z40" s="58" t="str">
+      <c r="Z40" s="125" t="str">
         <f>'[1]TERM 1'!Z42</f>
         <v/>
       </c>
-      <c r="AA40" s="61" t="str">
+      <c r="AA40" s="127" t="str">
         <f>'[1]TERM 1'!AA42</f>
         <v/>
       </c>
@@ -8764,11 +8848,11 @@
         <f>'[1]TERM 1'!K43</f>
         <v/>
       </c>
-      <c r="L41" s="58" t="str">
+      <c r="L41" s="125" t="str">
         <f>'[1]TERM 1'!L43</f>
         <v/>
       </c>
-      <c r="M41" s="59" t="str">
+      <c r="M41" s="126" t="str">
         <f>'[1]TERM 1'!M43</f>
         <v/>
       </c>
@@ -8779,34 +8863,34 @@
         <f>'[1]TERM 1'!Q43</f>
         <v/>
       </c>
-      <c r="R41" s="58" t="str">
+      <c r="R41" s="125" t="str">
         <f>'[1]TERM 1'!R43</f>
         <v/>
       </c>
-      <c r="S41" s="61" t="str">
+      <c r="S41" s="127" t="str">
         <f>'[1]TERM 1'!S43</f>
         <v/>
       </c>
       <c r="T41" s="62"/>
       <c r="U41" s="55"/>
       <c r="V41" s="56"/>
-      <c r="W41" s="58" t="str">
+      <c r="W41" s="125" t="str">
         <f>'[1]TERM 1'!W43</f>
         <v/>
       </c>
-      <c r="X41" s="59" t="str">
+      <c r="X41" s="126" t="str">
         <f>'[1]TERM 1'!X43</f>
         <v/>
       </c>
-      <c r="Y41" s="63" t="str">
+      <c r="Y41" s="128" t="str">
         <f>'[1]TERM 1'!Y43</f>
         <v/>
       </c>
-      <c r="Z41" s="58" t="str">
+      <c r="Z41" s="125" t="str">
         <f>'[1]TERM 1'!Z43</f>
         <v/>
       </c>
-      <c r="AA41" s="61" t="str">
+      <c r="AA41" s="127" t="str">
         <f>'[1]TERM 1'!AA43</f>
         <v/>
       </c>
@@ -8840,11 +8924,11 @@
         <f>'[1]TERM 1'!K44</f>
         <v/>
       </c>
-      <c r="L42" s="58" t="str">
+      <c r="L42" s="125" t="str">
         <f>'[1]TERM 1'!L44</f>
         <v/>
       </c>
-      <c r="M42" s="59" t="str">
+      <c r="M42" s="126" t="str">
         <f>'[1]TERM 1'!M44</f>
         <v/>
       </c>
@@ -8855,34 +8939,34 @@
         <f>'[1]TERM 1'!Q44</f>
         <v/>
       </c>
-      <c r="R42" s="58" t="str">
+      <c r="R42" s="125" t="str">
         <f>'[1]TERM 1'!R44</f>
         <v/>
       </c>
-      <c r="S42" s="61" t="str">
+      <c r="S42" s="127" t="str">
         <f>'[1]TERM 1'!S44</f>
         <v/>
       </c>
       <c r="T42" s="62"/>
       <c r="U42" s="55"/>
       <c r="V42" s="56"/>
-      <c r="W42" s="58" t="str">
+      <c r="W42" s="125" t="str">
         <f>'[1]TERM 1'!W44</f>
         <v/>
       </c>
-      <c r="X42" s="59" t="str">
+      <c r="X42" s="126" t="str">
         <f>'[1]TERM 1'!X44</f>
         <v/>
       </c>
-      <c r="Y42" s="63" t="str">
+      <c r="Y42" s="128" t="str">
         <f>'[1]TERM 1'!Y44</f>
         <v/>
       </c>
-      <c r="Z42" s="58" t="str">
+      <c r="Z42" s="125" t="str">
         <f>'[1]TERM 1'!Z44</f>
         <v/>
       </c>
-      <c r="AA42" s="61" t="str">
+      <c r="AA42" s="127" t="str">
         <f>'[1]TERM 1'!AA44</f>
         <v/>
       </c>
@@ -8916,11 +9000,11 @@
         <f>'[1]TERM 1'!K45</f>
         <v/>
       </c>
-      <c r="L43" s="58" t="str">
+      <c r="L43" s="125" t="str">
         <f>'[1]TERM 1'!L45</f>
         <v/>
       </c>
-      <c r="M43" s="59" t="str">
+      <c r="M43" s="126" t="str">
         <f>'[1]TERM 1'!M45</f>
         <v/>
       </c>
@@ -8931,34 +9015,34 @@
         <f>'[1]TERM 1'!Q45</f>
         <v/>
       </c>
-      <c r="R43" s="58" t="str">
+      <c r="R43" s="125" t="str">
         <f>'[1]TERM 1'!R45</f>
         <v/>
       </c>
-      <c r="S43" s="61" t="str">
+      <c r="S43" s="127" t="str">
         <f>'[1]TERM 1'!S45</f>
         <v/>
       </c>
       <c r="T43" s="62"/>
       <c r="U43" s="55"/>
       <c r="V43" s="56"/>
-      <c r="W43" s="58" t="str">
+      <c r="W43" s="125" t="str">
         <f>'[1]TERM 1'!W45</f>
         <v/>
       </c>
-      <c r="X43" s="59" t="str">
+      <c r="X43" s="126" t="str">
         <f>'[1]TERM 1'!X45</f>
         <v/>
       </c>
-      <c r="Y43" s="63" t="str">
+      <c r="Y43" s="128" t="str">
         <f>'[1]TERM 1'!Y45</f>
         <v/>
       </c>
-      <c r="Z43" s="58" t="str">
+      <c r="Z43" s="125" t="str">
         <f>'[1]TERM 1'!Z45</f>
         <v/>
       </c>
-      <c r="AA43" s="61" t="str">
+      <c r="AA43" s="127" t="str">
         <f>'[1]TERM 1'!AA45</f>
         <v/>
       </c>
@@ -8992,11 +9076,11 @@
         <f>'[1]TERM 1'!K46</f>
         <v/>
       </c>
-      <c r="L44" s="58" t="str">
+      <c r="L44" s="125" t="str">
         <f>'[1]TERM 1'!L46</f>
         <v/>
       </c>
-      <c r="M44" s="59" t="str">
+      <c r="M44" s="126" t="str">
         <f>'[1]TERM 1'!M46</f>
         <v/>
       </c>
@@ -9007,34 +9091,34 @@
         <f>'[1]TERM 1'!Q46</f>
         <v/>
       </c>
-      <c r="R44" s="58" t="str">
+      <c r="R44" s="125" t="str">
         <f>'[1]TERM 1'!R46</f>
         <v/>
       </c>
-      <c r="S44" s="61" t="str">
+      <c r="S44" s="127" t="str">
         <f>'[1]TERM 1'!S46</f>
         <v/>
       </c>
       <c r="T44" s="62"/>
       <c r="U44" s="55"/>
       <c r="V44" s="56"/>
-      <c r="W44" s="58" t="str">
+      <c r="W44" s="125" t="str">
         <f>'[1]TERM 1'!W46</f>
         <v/>
       </c>
-      <c r="X44" s="59" t="str">
+      <c r="X44" s="126" t="str">
         <f>'[1]TERM 1'!X46</f>
         <v/>
       </c>
-      <c r="Y44" s="63" t="str">
+      <c r="Y44" s="128" t="str">
         <f>'[1]TERM 1'!Y46</f>
         <v/>
       </c>
-      <c r="Z44" s="58" t="str">
+      <c r="Z44" s="125" t="str">
         <f>'[1]TERM 1'!Z46</f>
         <v/>
       </c>
-      <c r="AA44" s="61" t="str">
+      <c r="AA44" s="127" t="str">
         <f>'[1]TERM 1'!AA46</f>
         <v/>
       </c>
@@ -9068,11 +9152,11 @@
         <f>'[1]TERM 1'!K47</f>
         <v/>
       </c>
-      <c r="L45" s="58" t="str">
+      <c r="L45" s="125" t="str">
         <f>'[1]TERM 1'!L47</f>
         <v/>
       </c>
-      <c r="M45" s="59" t="str">
+      <c r="M45" s="126" t="str">
         <f>'[1]TERM 1'!M47</f>
         <v/>
       </c>
@@ -9083,34 +9167,34 @@
         <f>'[1]TERM 1'!Q47</f>
         <v/>
       </c>
-      <c r="R45" s="58" t="str">
+      <c r="R45" s="125" t="str">
         <f>'[1]TERM 1'!R47</f>
         <v/>
       </c>
-      <c r="S45" s="61" t="str">
+      <c r="S45" s="127" t="str">
         <f>'[1]TERM 1'!S47</f>
         <v/>
       </c>
       <c r="T45" s="62"/>
       <c r="U45" s="55"/>
       <c r="V45" s="56"/>
-      <c r="W45" s="58" t="str">
+      <c r="W45" s="125" t="str">
         <f>'[1]TERM 1'!W47</f>
         <v/>
       </c>
-      <c r="X45" s="59" t="str">
+      <c r="X45" s="126" t="str">
         <f>'[1]TERM 1'!X47</f>
         <v/>
       </c>
-      <c r="Y45" s="63" t="str">
+      <c r="Y45" s="128" t="str">
         <f>'[1]TERM 1'!Y47</f>
         <v/>
       </c>
-      <c r="Z45" s="58" t="str">
+      <c r="Z45" s="125" t="str">
         <f>'[1]TERM 1'!Z47</f>
         <v/>
       </c>
-      <c r="AA45" s="61" t="str">
+      <c r="AA45" s="127" t="str">
         <f>'[1]TERM 1'!AA47</f>
         <v/>
       </c>
@@ -9144,11 +9228,11 @@
         <f>'[1]TERM 1'!K48</f>
         <v/>
       </c>
-      <c r="L46" s="58" t="str">
+      <c r="L46" s="125" t="str">
         <f>'[1]TERM 1'!L48</f>
         <v/>
       </c>
-      <c r="M46" s="59" t="str">
+      <c r="M46" s="126" t="str">
         <f>'[1]TERM 1'!M48</f>
         <v/>
       </c>
@@ -9159,34 +9243,34 @@
         <f>'[1]TERM 1'!Q48</f>
         <v/>
       </c>
-      <c r="R46" s="58" t="str">
+      <c r="R46" s="125" t="str">
         <f>'[1]TERM 1'!R48</f>
         <v/>
       </c>
-      <c r="S46" s="61" t="str">
+      <c r="S46" s="127" t="str">
         <f>'[1]TERM 1'!S48</f>
         <v/>
       </c>
       <c r="T46" s="62"/>
       <c r="U46" s="55"/>
       <c r="V46" s="56"/>
-      <c r="W46" s="58" t="str">
+      <c r="W46" s="125" t="str">
         <f>'[1]TERM 1'!W48</f>
         <v/>
       </c>
-      <c r="X46" s="59" t="str">
+      <c r="X46" s="126" t="str">
         <f>'[1]TERM 1'!X48</f>
         <v/>
       </c>
-      <c r="Y46" s="63" t="str">
+      <c r="Y46" s="128" t="str">
         <f>'[1]TERM 1'!Y48</f>
         <v/>
       </c>
-      <c r="Z46" s="58" t="str">
+      <c r="Z46" s="125" t="str">
         <f>'[1]TERM 1'!Z48</f>
         <v/>
       </c>
-      <c r="AA46" s="61" t="str">
+      <c r="AA46" s="127" t="str">
         <f>'[1]TERM 1'!AA48</f>
         <v/>
       </c>
@@ -9220,11 +9304,11 @@
         <f>'[1]TERM 1'!K49</f>
         <v/>
       </c>
-      <c r="L47" s="58" t="str">
+      <c r="L47" s="125" t="str">
         <f>'[1]TERM 1'!L49</f>
         <v/>
       </c>
-      <c r="M47" s="59" t="str">
+      <c r="M47" s="126" t="str">
         <f>'[1]TERM 1'!M49</f>
         <v/>
       </c>
@@ -9235,34 +9319,34 @@
         <f>'[1]TERM 1'!Q49</f>
         <v/>
       </c>
-      <c r="R47" s="58" t="str">
+      <c r="R47" s="125" t="str">
         <f>'[1]TERM 1'!R49</f>
         <v/>
       </c>
-      <c r="S47" s="61" t="str">
+      <c r="S47" s="127" t="str">
         <f>'[1]TERM 1'!S49</f>
         <v/>
       </c>
       <c r="T47" s="62"/>
       <c r="U47" s="55"/>
       <c r="V47" s="56"/>
-      <c r="W47" s="58" t="str">
+      <c r="W47" s="125" t="str">
         <f>'[1]TERM 1'!W49</f>
         <v/>
       </c>
-      <c r="X47" s="59" t="str">
+      <c r="X47" s="126" t="str">
         <f>'[1]TERM 1'!X49</f>
         <v/>
       </c>
-      <c r="Y47" s="63" t="str">
+      <c r="Y47" s="128" t="str">
         <f>'[1]TERM 1'!Y49</f>
         <v/>
       </c>
-      <c r="Z47" s="58" t="str">
+      <c r="Z47" s="125" t="str">
         <f>'[1]TERM 1'!Z49</f>
         <v/>
       </c>
-      <c r="AA47" s="61" t="str">
+      <c r="AA47" s="127" t="str">
         <f>'[1]TERM 1'!AA49</f>
         <v/>
       </c>
@@ -9296,11 +9380,11 @@
         <f>'[1]TERM 1'!K50</f>
         <v/>
       </c>
-      <c r="L48" s="58" t="str">
+      <c r="L48" s="125" t="str">
         <f>'[1]TERM 1'!L50</f>
         <v/>
       </c>
-      <c r="M48" s="59" t="str">
+      <c r="M48" s="126" t="str">
         <f>'[1]TERM 1'!M50</f>
         <v/>
       </c>
@@ -9311,34 +9395,34 @@
         <f>'[1]TERM 1'!Q50</f>
         <v/>
       </c>
-      <c r="R48" s="58" t="str">
+      <c r="R48" s="125" t="str">
         <f>'[1]TERM 1'!R50</f>
         <v/>
       </c>
-      <c r="S48" s="61" t="str">
+      <c r="S48" s="127" t="str">
         <f>'[1]TERM 1'!S50</f>
         <v/>
       </c>
       <c r="T48" s="62"/>
       <c r="U48" s="55"/>
       <c r="V48" s="56"/>
-      <c r="W48" s="58" t="str">
+      <c r="W48" s="125" t="str">
         <f>'[1]TERM 1'!W50</f>
         <v/>
       </c>
-      <c r="X48" s="59" t="str">
+      <c r="X48" s="126" t="str">
         <f>'[1]TERM 1'!X50</f>
         <v/>
       </c>
-      <c r="Y48" s="63" t="str">
+      <c r="Y48" s="128" t="str">
         <f>'[1]TERM 1'!Y50</f>
         <v/>
       </c>
-      <c r="Z48" s="58" t="str">
+      <c r="Z48" s="125" t="str">
         <f>'[1]TERM 1'!Z50</f>
         <v/>
       </c>
-      <c r="AA48" s="61" t="str">
+      <c r="AA48" s="127" t="str">
         <f>'[1]TERM 1'!AA50</f>
         <v/>
       </c>
@@ -9372,11 +9456,11 @@
         <f>'[1]TERM 1'!K51</f>
         <v/>
       </c>
-      <c r="L49" s="58" t="str">
+      <c r="L49" s="125" t="str">
         <f>'[1]TERM 1'!L51</f>
         <v/>
       </c>
-      <c r="M49" s="59" t="str">
+      <c r="M49" s="126" t="str">
         <f>'[1]TERM 1'!M51</f>
         <v/>
       </c>
@@ -9387,34 +9471,34 @@
         <f>'[1]TERM 1'!Q51</f>
         <v/>
       </c>
-      <c r="R49" s="58" t="str">
+      <c r="R49" s="125" t="str">
         <f>'[1]TERM 1'!R51</f>
         <v/>
       </c>
-      <c r="S49" s="61" t="str">
+      <c r="S49" s="127" t="str">
         <f>'[1]TERM 1'!S51</f>
         <v/>
       </c>
       <c r="T49" s="62"/>
       <c r="U49" s="55"/>
       <c r="V49" s="56"/>
-      <c r="W49" s="58" t="str">
+      <c r="W49" s="125" t="str">
         <f>'[1]TERM 1'!W51</f>
         <v/>
       </c>
-      <c r="X49" s="59" t="str">
+      <c r="X49" s="126" t="str">
         <f>'[1]TERM 1'!X51</f>
         <v/>
       </c>
-      <c r="Y49" s="63" t="str">
+      <c r="Y49" s="128" t="str">
         <f>'[1]TERM 1'!Y51</f>
         <v/>
       </c>
-      <c r="Z49" s="58" t="str">
+      <c r="Z49" s="125" t="str">
         <f>'[1]TERM 1'!Z51</f>
         <v/>
       </c>
-      <c r="AA49" s="61" t="str">
+      <c r="AA49" s="127" t="str">
         <f>'[1]TERM 1'!AA51</f>
         <v/>
       </c>
@@ -9448,11 +9532,11 @@
         <f>'[1]TERM 1'!K52</f>
         <v/>
       </c>
-      <c r="L50" s="58" t="str">
+      <c r="L50" s="125" t="str">
         <f>'[1]TERM 1'!L52</f>
         <v/>
       </c>
-      <c r="M50" s="59" t="str">
+      <c r="M50" s="126" t="str">
         <f>'[1]TERM 1'!M52</f>
         <v/>
       </c>
@@ -9463,34 +9547,34 @@
         <f>'[1]TERM 1'!Q52</f>
         <v/>
       </c>
-      <c r="R50" s="58" t="str">
+      <c r="R50" s="125" t="str">
         <f>'[1]TERM 1'!R52</f>
         <v/>
       </c>
-      <c r="S50" s="61" t="str">
+      <c r="S50" s="127" t="str">
         <f>'[1]TERM 1'!S52</f>
         <v/>
       </c>
       <c r="T50" s="62"/>
       <c r="U50" s="55"/>
       <c r="V50" s="56"/>
-      <c r="W50" s="58" t="str">
+      <c r="W50" s="125" t="str">
         <f>'[1]TERM 1'!W52</f>
         <v/>
       </c>
-      <c r="X50" s="59" t="str">
+      <c r="X50" s="126" t="str">
         <f>'[1]TERM 1'!X52</f>
         <v/>
       </c>
-      <c r="Y50" s="63" t="str">
+      <c r="Y50" s="128" t="str">
         <f>'[1]TERM 1'!Y52</f>
         <v/>
       </c>
-      <c r="Z50" s="58" t="str">
+      <c r="Z50" s="125" t="str">
         <f>'[1]TERM 1'!Z52</f>
         <v/>
       </c>
-      <c r="AA50" s="61" t="str">
+      <c r="AA50" s="127" t="str">
         <f>'[1]TERM 1'!AA52</f>
         <v/>
       </c>
@@ -9524,11 +9608,11 @@
         <f>'[1]TERM 1'!K53</f>
         <v/>
       </c>
-      <c r="L51" s="58" t="str">
+      <c r="L51" s="125" t="str">
         <f>'[1]TERM 1'!L53</f>
         <v/>
       </c>
-      <c r="M51" s="59" t="str">
+      <c r="M51" s="126" t="str">
         <f>'[1]TERM 1'!M53</f>
         <v/>
       </c>
@@ -9539,34 +9623,34 @@
         <f>'[1]TERM 1'!Q53</f>
         <v/>
       </c>
-      <c r="R51" s="58" t="str">
+      <c r="R51" s="125" t="str">
         <f>'[1]TERM 1'!R53</f>
         <v/>
       </c>
-      <c r="S51" s="61" t="str">
+      <c r="S51" s="127" t="str">
         <f>'[1]TERM 1'!S53</f>
         <v/>
       </c>
       <c r="T51" s="62"/>
       <c r="U51" s="55"/>
       <c r="V51" s="56"/>
-      <c r="W51" s="58" t="str">
+      <c r="W51" s="125" t="str">
         <f>'[1]TERM 1'!W53</f>
         <v/>
       </c>
-      <c r="X51" s="59" t="str">
+      <c r="X51" s="126" t="str">
         <f>'[1]TERM 1'!X53</f>
         <v/>
       </c>
-      <c r="Y51" s="63" t="str">
+      <c r="Y51" s="128" t="str">
         <f>'[1]TERM 1'!Y53</f>
         <v/>
       </c>
-      <c r="Z51" s="58" t="str">
+      <c r="Z51" s="125" t="str">
         <f>'[1]TERM 1'!Z53</f>
         <v/>
       </c>
-      <c r="AA51" s="61" t="str">
+      <c r="AA51" s="127" t="str">
         <f>'[1]TERM 1'!AA53</f>
         <v/>
       </c>
@@ -9600,11 +9684,11 @@
         <f>'[1]TERM 1'!K54</f>
         <v/>
       </c>
-      <c r="L52" s="58" t="str">
+      <c r="L52" s="125" t="str">
         <f>'[1]TERM 1'!L54</f>
         <v/>
       </c>
-      <c r="M52" s="59" t="str">
+      <c r="M52" s="126" t="str">
         <f>'[1]TERM 1'!M54</f>
         <v/>
       </c>
@@ -9615,34 +9699,34 @@
         <f>'[1]TERM 1'!Q54</f>
         <v/>
       </c>
-      <c r="R52" s="58" t="str">
+      <c r="R52" s="125" t="str">
         <f>'[1]TERM 1'!R54</f>
         <v/>
       </c>
-      <c r="S52" s="61" t="str">
+      <c r="S52" s="127" t="str">
         <f>'[1]TERM 1'!S54</f>
         <v/>
       </c>
       <c r="T52" s="62"/>
       <c r="U52" s="55"/>
       <c r="V52" s="56"/>
-      <c r="W52" s="58" t="str">
+      <c r="W52" s="125" t="str">
         <f>'[1]TERM 1'!W54</f>
         <v/>
       </c>
-      <c r="X52" s="59" t="str">
+      <c r="X52" s="126" t="str">
         <f>'[1]TERM 1'!X54</f>
         <v/>
       </c>
-      <c r="Y52" s="63" t="str">
+      <c r="Y52" s="128" t="str">
         <f>'[1]TERM 1'!Y54</f>
         <v/>
       </c>
-      <c r="Z52" s="58" t="str">
+      <c r="Z52" s="125" t="str">
         <f>'[1]TERM 1'!Z54</f>
         <v/>
       </c>
-      <c r="AA52" s="61" t="str">
+      <c r="AA52" s="127" t="str">
         <f>'[1]TERM 1'!AA54</f>
         <v/>
       </c>
@@ -9676,11 +9760,11 @@
         <f>'[1]TERM 1'!K55</f>
         <v/>
       </c>
-      <c r="L53" s="58" t="str">
+      <c r="L53" s="125" t="str">
         <f>'[1]TERM 1'!L55</f>
         <v/>
       </c>
-      <c r="M53" s="59" t="str">
+      <c r="M53" s="126" t="str">
         <f>'[1]TERM 1'!M55</f>
         <v/>
       </c>
@@ -9691,34 +9775,34 @@
         <f>'[1]TERM 1'!Q55</f>
         <v/>
       </c>
-      <c r="R53" s="58" t="str">
+      <c r="R53" s="125" t="str">
         <f>'[1]TERM 1'!R55</f>
         <v/>
       </c>
-      <c r="S53" s="61" t="str">
+      <c r="S53" s="127" t="str">
         <f>'[1]TERM 1'!S55</f>
         <v/>
       </c>
       <c r="T53" s="62"/>
       <c r="U53" s="55"/>
       <c r="V53" s="56"/>
-      <c r="W53" s="58" t="str">
+      <c r="W53" s="125" t="str">
         <f>'[1]TERM 1'!W55</f>
         <v/>
       </c>
-      <c r="X53" s="59" t="str">
+      <c r="X53" s="126" t="str">
         <f>'[1]TERM 1'!X55</f>
         <v/>
       </c>
-      <c r="Y53" s="63" t="str">
+      <c r="Y53" s="128" t="str">
         <f>'[1]TERM 1'!Y55</f>
         <v/>
       </c>
-      <c r="Z53" s="58" t="str">
+      <c r="Z53" s="125" t="str">
         <f>'[1]TERM 1'!Z55</f>
         <v/>
       </c>
-      <c r="AA53" s="61" t="str">
+      <c r="AA53" s="127" t="str">
         <f>'[1]TERM 1'!AA55</f>
         <v/>
       </c>
@@ -9752,11 +9836,11 @@
         <f>'[1]TERM 1'!K56</f>
         <v/>
       </c>
-      <c r="L54" s="58" t="str">
+      <c r="L54" s="125" t="str">
         <f>'[1]TERM 1'!L56</f>
         <v/>
       </c>
-      <c r="M54" s="59" t="str">
+      <c r="M54" s="126" t="str">
         <f>'[1]TERM 1'!M56</f>
         <v/>
       </c>
@@ -9767,34 +9851,34 @@
         <f>'[1]TERM 1'!Q56</f>
         <v/>
       </c>
-      <c r="R54" s="58" t="str">
+      <c r="R54" s="125" t="str">
         <f>'[1]TERM 1'!R56</f>
         <v/>
       </c>
-      <c r="S54" s="61" t="str">
+      <c r="S54" s="127" t="str">
         <f>'[1]TERM 1'!S56</f>
         <v/>
       </c>
       <c r="T54" s="62"/>
       <c r="U54" s="55"/>
       <c r="V54" s="56"/>
-      <c r="W54" s="58" t="str">
+      <c r="W54" s="125" t="str">
         <f>'[1]TERM 1'!W56</f>
         <v/>
       </c>
-      <c r="X54" s="59" t="str">
+      <c r="X54" s="126" t="str">
         <f>'[1]TERM 1'!X56</f>
         <v/>
       </c>
-      <c r="Y54" s="63" t="str">
+      <c r="Y54" s="128" t="str">
         <f>'[1]TERM 1'!Y56</f>
         <v/>
       </c>
-      <c r="Z54" s="58" t="str">
+      <c r="Z54" s="125" t="str">
         <f>'[1]TERM 1'!Z56</f>
         <v/>
       </c>
-      <c r="AA54" s="61" t="str">
+      <c r="AA54" s="127" t="str">
         <f>'[1]TERM 1'!AA56</f>
         <v/>
       </c>
@@ -9828,11 +9912,11 @@
         <f>'[1]TERM 1'!K57</f>
         <v/>
       </c>
-      <c r="L55" s="58" t="str">
+      <c r="L55" s="125" t="str">
         <f>'[1]TERM 1'!L57</f>
         <v/>
       </c>
-      <c r="M55" s="59" t="str">
+      <c r="M55" s="126" t="str">
         <f>'[1]TERM 1'!M57</f>
         <v/>
       </c>
@@ -9843,34 +9927,34 @@
         <f>'[1]TERM 1'!Q57</f>
         <v/>
       </c>
-      <c r="R55" s="58" t="str">
+      <c r="R55" s="125" t="str">
         <f>'[1]TERM 1'!R57</f>
         <v/>
       </c>
-      <c r="S55" s="61" t="str">
+      <c r="S55" s="127" t="str">
         <f>'[1]TERM 1'!S57</f>
         <v/>
       </c>
       <c r="T55" s="62"/>
       <c r="U55" s="55"/>
       <c r="V55" s="56"/>
-      <c r="W55" s="58" t="str">
+      <c r="W55" s="125" t="str">
         <f>'[1]TERM 1'!W57</f>
         <v/>
       </c>
-      <c r="X55" s="59" t="str">
+      <c r="X55" s="126" t="str">
         <f>'[1]TERM 1'!X57</f>
         <v/>
       </c>
-      <c r="Y55" s="63" t="str">
+      <c r="Y55" s="128" t="str">
         <f>'[1]TERM 1'!Y57</f>
         <v/>
       </c>
-      <c r="Z55" s="58" t="str">
+      <c r="Z55" s="125" t="str">
         <f>'[1]TERM 1'!Z57</f>
         <v/>
       </c>
-      <c r="AA55" s="61" t="str">
+      <c r="AA55" s="127" t="str">
         <f>'[1]TERM 1'!AA57</f>
         <v/>
       </c>
@@ -9904,11 +9988,11 @@
         <f>'[1]TERM 1'!K58</f>
         <v/>
       </c>
-      <c r="L56" s="58" t="str">
+      <c r="L56" s="125" t="str">
         <f>'[1]TERM 1'!L58</f>
         <v/>
       </c>
-      <c r="M56" s="59" t="str">
+      <c r="M56" s="126" t="str">
         <f>'[1]TERM 1'!M58</f>
         <v/>
       </c>
@@ -9919,34 +10003,34 @@
         <f>'[1]TERM 1'!Q58</f>
         <v/>
       </c>
-      <c r="R56" s="58" t="str">
+      <c r="R56" s="125" t="str">
         <f>'[1]TERM 1'!R58</f>
         <v/>
       </c>
-      <c r="S56" s="61" t="str">
+      <c r="S56" s="127" t="str">
         <f>'[1]TERM 1'!S58</f>
         <v/>
       </c>
       <c r="T56" s="62"/>
       <c r="U56" s="55"/>
       <c r="V56" s="56"/>
-      <c r="W56" s="58" t="str">
+      <c r="W56" s="125" t="str">
         <f>'[1]TERM 1'!W58</f>
         <v/>
       </c>
-      <c r="X56" s="59" t="str">
+      <c r="X56" s="126" t="str">
         <f>'[1]TERM 1'!X58</f>
         <v/>
       </c>
-      <c r="Y56" s="63" t="str">
+      <c r="Y56" s="128" t="str">
         <f>'[1]TERM 1'!Y58</f>
         <v/>
       </c>
-      <c r="Z56" s="58" t="str">
+      <c r="Z56" s="125" t="str">
         <f>'[1]TERM 1'!Z58</f>
         <v/>
       </c>
-      <c r="AA56" s="61" t="str">
+      <c r="AA56" s="127" t="str">
         <f>'[1]TERM 1'!AA58</f>
         <v/>
       </c>
@@ -9980,11 +10064,11 @@
         <f>'[1]TERM 1'!K59</f>
         <v/>
       </c>
-      <c r="L57" s="58" t="str">
+      <c r="L57" s="125" t="str">
         <f>'[1]TERM 1'!L59</f>
         <v/>
       </c>
-      <c r="M57" s="59" t="str">
+      <c r="M57" s="126" t="str">
         <f>'[1]TERM 1'!M59</f>
         <v/>
       </c>
@@ -9995,34 +10079,34 @@
         <f>'[1]TERM 1'!Q59</f>
         <v/>
       </c>
-      <c r="R57" s="58" t="str">
+      <c r="R57" s="125" t="str">
         <f>'[1]TERM 1'!R59</f>
         <v/>
       </c>
-      <c r="S57" s="61" t="str">
+      <c r="S57" s="127" t="str">
         <f>'[1]TERM 1'!S59</f>
         <v/>
       </c>
       <c r="T57" s="62"/>
       <c r="U57" s="55"/>
       <c r="V57" s="56"/>
-      <c r="W57" s="58" t="str">
+      <c r="W57" s="125" t="str">
         <f>'[1]TERM 1'!W59</f>
         <v/>
       </c>
-      <c r="X57" s="59" t="str">
+      <c r="X57" s="126" t="str">
         <f>'[1]TERM 1'!X59</f>
         <v/>
       </c>
-      <c r="Y57" s="63" t="str">
+      <c r="Y57" s="128" t="str">
         <f>'[1]TERM 1'!Y59</f>
         <v/>
       </c>
-      <c r="Z57" s="58" t="str">
+      <c r="Z57" s="125" t="str">
         <f>'[1]TERM 1'!Z59</f>
         <v/>
       </c>
-      <c r="AA57" s="61" t="str">
+      <c r="AA57" s="127" t="str">
         <f>'[1]TERM 1'!AA59</f>
         <v/>
       </c>
@@ -10056,11 +10140,11 @@
         <f>'[1]TERM 1'!K60</f>
         <v/>
       </c>
-      <c r="L58" s="58" t="str">
+      <c r="L58" s="125" t="str">
         <f>'[1]TERM 1'!L60</f>
         <v/>
       </c>
-      <c r="M58" s="59" t="str">
+      <c r="M58" s="126" t="str">
         <f>'[1]TERM 1'!M60</f>
         <v/>
       </c>
@@ -10071,34 +10155,34 @@
         <f>'[1]TERM 1'!Q60</f>
         <v/>
       </c>
-      <c r="R58" s="58" t="str">
+      <c r="R58" s="125" t="str">
         <f>'[1]TERM 1'!R60</f>
         <v/>
       </c>
-      <c r="S58" s="61" t="str">
+      <c r="S58" s="127" t="str">
         <f>'[1]TERM 1'!S60</f>
         <v/>
       </c>
       <c r="T58" s="62"/>
       <c r="U58" s="55"/>
       <c r="V58" s="56"/>
-      <c r="W58" s="58" t="str">
+      <c r="W58" s="125" t="str">
         <f>'[1]TERM 1'!W60</f>
         <v/>
       </c>
-      <c r="X58" s="59" t="str">
+      <c r="X58" s="126" t="str">
         <f>'[1]TERM 1'!X60</f>
         <v/>
       </c>
-      <c r="Y58" s="63" t="str">
+      <c r="Y58" s="128" t="str">
         <f>'[1]TERM 1'!Y60</f>
         <v/>
       </c>
-      <c r="Z58" s="58" t="str">
+      <c r="Z58" s="125" t="str">
         <f>'[1]TERM 1'!Z60</f>
         <v/>
       </c>
-      <c r="AA58" s="61" t="str">
+      <c r="AA58" s="127" t="str">
         <f>'[1]TERM 1'!AA60</f>
         <v/>
       </c>
@@ -10132,11 +10216,11 @@
         <f>'[1]TERM 1'!K61</f>
         <v/>
       </c>
-      <c r="L59" s="58" t="str">
+      <c r="L59" s="125" t="str">
         <f>'[1]TERM 1'!L61</f>
         <v/>
       </c>
-      <c r="M59" s="59" t="str">
+      <c r="M59" s="126" t="str">
         <f>'[1]TERM 1'!M61</f>
         <v/>
       </c>
@@ -10147,34 +10231,34 @@
         <f>'[1]TERM 1'!Q61</f>
         <v/>
       </c>
-      <c r="R59" s="58" t="str">
+      <c r="R59" s="125" t="str">
         <f>'[1]TERM 1'!R61</f>
         <v/>
       </c>
-      <c r="S59" s="61" t="str">
+      <c r="S59" s="127" t="str">
         <f>'[1]TERM 1'!S61</f>
         <v/>
       </c>
       <c r="T59" s="62"/>
       <c r="U59" s="55"/>
       <c r="V59" s="56"/>
-      <c r="W59" s="58" t="str">
+      <c r="W59" s="125" t="str">
         <f>'[1]TERM 1'!W61</f>
         <v/>
       </c>
-      <c r="X59" s="59" t="str">
+      <c r="X59" s="126" t="str">
         <f>'[1]TERM 1'!X61</f>
         <v/>
       </c>
-      <c r="Y59" s="63" t="str">
+      <c r="Y59" s="128" t="str">
         <f>'[1]TERM 1'!Y61</f>
         <v/>
       </c>
-      <c r="Z59" s="58" t="str">
+      <c r="Z59" s="125" t="str">
         <f>'[1]TERM 1'!Z61</f>
         <v/>
       </c>
-      <c r="AA59" s="61" t="str">
+      <c r="AA59" s="127" t="str">
         <f>'[1]TERM 1'!AA61</f>
         <v/>
       </c>
@@ -10208,11 +10292,11 @@
         <f>'[1]TERM 1'!K62</f>
         <v/>
       </c>
-      <c r="L60" s="58" t="str">
+      <c r="L60" s="125" t="str">
         <f>'[1]TERM 1'!L62</f>
         <v/>
       </c>
-      <c r="M60" s="59" t="str">
+      <c r="M60" s="126" t="str">
         <f>'[1]TERM 1'!M62</f>
         <v/>
       </c>
@@ -10223,34 +10307,34 @@
         <f>'[1]TERM 1'!Q62</f>
         <v/>
       </c>
-      <c r="R60" s="58" t="str">
+      <c r="R60" s="125" t="str">
         <f>'[1]TERM 1'!R62</f>
         <v/>
       </c>
-      <c r="S60" s="61" t="str">
+      <c r="S60" s="127" t="str">
         <f>'[1]TERM 1'!S62</f>
         <v/>
       </c>
       <c r="T60" s="62"/>
       <c r="U60" s="55"/>
       <c r="V60" s="56"/>
-      <c r="W60" s="58" t="str">
+      <c r="W60" s="125" t="str">
         <f>'[1]TERM 1'!W62</f>
         <v/>
       </c>
-      <c r="X60" s="59" t="str">
+      <c r="X60" s="126" t="str">
         <f>'[1]TERM 1'!X62</f>
         <v/>
       </c>
-      <c r="Y60" s="63" t="str">
+      <c r="Y60" s="128" t="str">
         <f>'[1]TERM 1'!Y62</f>
         <v/>
       </c>
-      <c r="Z60" s="58" t="str">
+      <c r="Z60" s="125" t="str">
         <f>'[1]TERM 1'!Z62</f>
         <v/>
       </c>
-      <c r="AA60" s="61" t="str">
+      <c r="AA60" s="127" t="str">
         <f>'[1]TERM 1'!AA62</f>
         <v/>
       </c>
@@ -10284,11 +10368,11 @@
         <f>'[1]TERM 1'!K63</f>
         <v/>
       </c>
-      <c r="L61" s="58" t="str">
+      <c r="L61" s="125" t="str">
         <f>'[1]TERM 1'!L63</f>
         <v/>
       </c>
-      <c r="M61" s="59" t="str">
+      <c r="M61" s="126" t="str">
         <f>'[1]TERM 1'!M63</f>
         <v/>
       </c>
@@ -10299,34 +10383,34 @@
         <f>'[1]TERM 1'!Q63</f>
         <v/>
       </c>
-      <c r="R61" s="58" t="str">
+      <c r="R61" s="125" t="str">
         <f>'[1]TERM 1'!R63</f>
         <v/>
       </c>
-      <c r="S61" s="61" t="str">
+      <c r="S61" s="127" t="str">
         <f>'[1]TERM 1'!S63</f>
         <v/>
       </c>
       <c r="T61" s="62"/>
       <c r="U61" s="55"/>
       <c r="V61" s="56"/>
-      <c r="W61" s="58" t="str">
+      <c r="W61" s="125" t="str">
         <f>'[1]TERM 1'!W63</f>
         <v/>
       </c>
-      <c r="X61" s="59" t="str">
+      <c r="X61" s="126" t="str">
         <f>'[1]TERM 1'!X63</f>
         <v/>
       </c>
-      <c r="Y61" s="63" t="str">
+      <c r="Y61" s="128" t="str">
         <f>'[1]TERM 1'!Y63</f>
         <v/>
       </c>
-      <c r="Z61" s="58" t="str">
+      <c r="Z61" s="125" t="str">
         <f>'[1]TERM 1'!Z63</f>
         <v/>
       </c>
-      <c r="AA61" s="61" t="str">
+      <c r="AA61" s="127" t="str">
         <f>'[1]TERM 1'!AA63</f>
         <v/>
       </c>
@@ -10360,11 +10444,11 @@
         <f>'[1]TERM 1'!K64</f>
         <v/>
       </c>
-      <c r="L62" s="58" t="str">
+      <c r="L62" s="125" t="str">
         <f>'[1]TERM 1'!L64</f>
         <v/>
       </c>
-      <c r="M62" s="59" t="str">
+      <c r="M62" s="126" t="str">
         <f>'[1]TERM 1'!M64</f>
         <v/>
       </c>
@@ -10375,34 +10459,34 @@
         <f>'[1]TERM 1'!Q64</f>
         <v/>
       </c>
-      <c r="R62" s="58" t="str">
+      <c r="R62" s="125" t="str">
         <f>'[1]TERM 1'!R64</f>
         <v/>
       </c>
-      <c r="S62" s="61" t="str">
+      <c r="S62" s="127" t="str">
         <f>'[1]TERM 1'!S64</f>
         <v/>
       </c>
       <c r="T62" s="62"/>
       <c r="U62" s="55"/>
       <c r="V62" s="56"/>
-      <c r="W62" s="58" t="str">
+      <c r="W62" s="125" t="str">
         <f>'[1]TERM 1'!W64</f>
         <v/>
       </c>
-      <c r="X62" s="59" t="str">
+      <c r="X62" s="126" t="str">
         <f>'[1]TERM 1'!X64</f>
         <v/>
       </c>
-      <c r="Y62" s="63" t="str">
+      <c r="Y62" s="128" t="str">
         <f>'[1]TERM 1'!Y64</f>
         <v/>
       </c>
-      <c r="Z62" s="58" t="str">
+      <c r="Z62" s="125" t="str">
         <f>'[1]TERM 1'!Z64</f>
         <v/>
       </c>
-      <c r="AA62" s="61" t="str">
+      <c r="AA62" s="127" t="str">
         <f>'[1]TERM 1'!AA64</f>
         <v/>
       </c>
@@ -10436,11 +10520,11 @@
         <f>'[1]TERM 1'!K65</f>
         <v/>
       </c>
-      <c r="L63" s="58" t="str">
+      <c r="L63" s="125" t="str">
         <f>'[1]TERM 1'!L65</f>
         <v/>
       </c>
-      <c r="M63" s="59" t="str">
+      <c r="M63" s="126" t="str">
         <f>'[1]TERM 1'!M65</f>
         <v/>
       </c>
@@ -10451,34 +10535,34 @@
         <f>'[1]TERM 1'!Q65</f>
         <v/>
       </c>
-      <c r="R63" s="58" t="str">
+      <c r="R63" s="125" t="str">
         <f>'[1]TERM 1'!R65</f>
         <v/>
       </c>
-      <c r="S63" s="61" t="str">
+      <c r="S63" s="127" t="str">
         <f>'[1]TERM 1'!S65</f>
         <v/>
       </c>
       <c r="T63" s="62"/>
       <c r="U63" s="55"/>
       <c r="V63" s="56"/>
-      <c r="W63" s="58" t="str">
+      <c r="W63" s="125" t="str">
         <f>'[1]TERM 1'!W65</f>
         <v/>
       </c>
-      <c r="X63" s="59" t="str">
+      <c r="X63" s="126" t="str">
         <f>'[1]TERM 1'!X65</f>
         <v/>
       </c>
-      <c r="Y63" s="63" t="str">
+      <c r="Y63" s="128" t="str">
         <f>'[1]TERM 1'!Y65</f>
         <v/>
       </c>
-      <c r="Z63" s="58" t="str">
+      <c r="Z63" s="125" t="str">
         <f>'[1]TERM 1'!Z65</f>
         <v/>
       </c>
-      <c r="AA63" s="61" t="str">
+      <c r="AA63" s="127" t="str">
         <f>'[1]TERM 1'!AA65</f>
         <v/>
       </c>
@@ -10512,11 +10596,11 @@
         <f>'[1]TERM 1'!K66</f>
         <v/>
       </c>
-      <c r="L64" s="58" t="str">
+      <c r="L64" s="125" t="str">
         <f>'[1]TERM 1'!L66</f>
         <v/>
       </c>
-      <c r="M64" s="59" t="str">
+      <c r="M64" s="126" t="str">
         <f>'[1]TERM 1'!M66</f>
         <v/>
       </c>
@@ -10527,34 +10611,34 @@
         <f>'[1]TERM 1'!Q66</f>
         <v/>
       </c>
-      <c r="R64" s="58" t="str">
+      <c r="R64" s="125" t="str">
         <f>'[1]TERM 1'!R66</f>
         <v/>
       </c>
-      <c r="S64" s="61" t="str">
+      <c r="S64" s="127" t="str">
         <f>'[1]TERM 1'!S66</f>
         <v/>
       </c>
       <c r="T64" s="62"/>
       <c r="U64" s="55"/>
       <c r="V64" s="56"/>
-      <c r="W64" s="58" t="str">
+      <c r="W64" s="125" t="str">
         <f>'[1]TERM 1'!W66</f>
         <v/>
       </c>
-      <c r="X64" s="59" t="str">
+      <c r="X64" s="126" t="str">
         <f>'[1]TERM 1'!X66</f>
         <v/>
       </c>
-      <c r="Y64" s="63" t="str">
+      <c r="Y64" s="128" t="str">
         <f>'[1]TERM 1'!Y66</f>
         <v/>
       </c>
-      <c r="Z64" s="58" t="str">
+      <c r="Z64" s="125" t="str">
         <f>'[1]TERM 1'!Z66</f>
         <v/>
       </c>
-      <c r="AA64" s="61" t="str">
+      <c r="AA64" s="127" t="str">
         <f>'[1]TERM 1'!AA66</f>
         <v/>
       </c>
@@ -10588,11 +10672,11 @@
         <f>'[1]TERM 1'!K67</f>
         <v/>
       </c>
-      <c r="L65" s="58" t="str">
+      <c r="L65" s="125" t="str">
         <f>'[1]TERM 1'!L67</f>
         <v/>
       </c>
-      <c r="M65" s="59" t="str">
+      <c r="M65" s="126" t="str">
         <f>'[1]TERM 1'!M67</f>
         <v/>
       </c>
@@ -10603,34 +10687,34 @@
         <f>'[1]TERM 1'!Q67</f>
         <v/>
       </c>
-      <c r="R65" s="58" t="str">
+      <c r="R65" s="125" t="str">
         <f>'[1]TERM 1'!R67</f>
         <v/>
       </c>
-      <c r="S65" s="61" t="str">
+      <c r="S65" s="127" t="str">
         <f>'[1]TERM 1'!S67</f>
         <v/>
       </c>
       <c r="T65" s="62"/>
       <c r="U65" s="55"/>
       <c r="V65" s="56"/>
-      <c r="W65" s="58" t="str">
+      <c r="W65" s="125" t="str">
         <f>'[1]TERM 1'!W67</f>
         <v/>
       </c>
-      <c r="X65" s="59" t="str">
+      <c r="X65" s="126" t="str">
         <f>'[1]TERM 1'!X67</f>
         <v/>
       </c>
-      <c r="Y65" s="63" t="str">
+      <c r="Y65" s="128" t="str">
         <f>'[1]TERM 1'!Y67</f>
         <v/>
       </c>
-      <c r="Z65" s="58" t="str">
+      <c r="Z65" s="125" t="str">
         <f>'[1]TERM 1'!Z67</f>
         <v/>
       </c>
-      <c r="AA65" s="61" t="str">
+      <c r="AA65" s="127" t="str">
         <f>'[1]TERM 1'!AA67</f>
         <v/>
       </c>
@@ -10698,11 +10782,11 @@
         <f>'[1]TERM 1'!K69</f>
         <v/>
       </c>
-      <c r="L67" s="58" t="str">
+      <c r="L67" s="125" t="str">
         <f>'[1]TERM 1'!L69</f>
         <v/>
       </c>
-      <c r="M67" s="59" t="str">
+      <c r="M67" s="126" t="str">
         <f>'[1]TERM 1'!M69</f>
         <v/>
       </c>
@@ -10713,34 +10797,34 @@
         <f>'[1]TERM 1'!Q69</f>
         <v/>
       </c>
-      <c r="R67" s="58" t="str">
+      <c r="R67" s="125" t="str">
         <f>'[1]TERM 1'!R69</f>
         <v/>
       </c>
-      <c r="S67" s="61" t="str">
+      <c r="S67" s="127" t="str">
         <f>'[1]TERM 1'!S69</f>
         <v/>
       </c>
       <c r="T67" s="62"/>
       <c r="U67" s="55"/>
       <c r="V67" s="56"/>
-      <c r="W67" s="58" t="str">
+      <c r="W67" s="125" t="str">
         <f>'[1]TERM 1'!W69</f>
         <v/>
       </c>
-      <c r="X67" s="59" t="str">
+      <c r="X67" s="126" t="str">
         <f>'[1]TERM 1'!X69</f>
         <v/>
       </c>
-      <c r="Y67" s="63" t="str">
+      <c r="Y67" s="128" t="str">
         <f>'[1]TERM 1'!Y69</f>
         <v/>
       </c>
-      <c r="Z67" s="58" t="str">
+      <c r="Z67" s="125" t="str">
         <f>'[1]TERM 1'!Z69</f>
         <v/>
       </c>
-      <c r="AA67" s="61" t="str">
+      <c r="AA67" s="127" t="str">
         <f>'[1]TERM 1'!AA69</f>
         <v/>
       </c>
@@ -10774,11 +10858,11 @@
         <f>'[1]TERM 1'!K70</f>
         <v/>
       </c>
-      <c r="L68" s="58" t="str">
+      <c r="L68" s="125" t="str">
         <f>'[1]TERM 1'!L70</f>
         <v/>
       </c>
-      <c r="M68" s="59" t="str">
+      <c r="M68" s="126" t="str">
         <f>'[1]TERM 1'!M70</f>
         <v/>
       </c>
@@ -10789,34 +10873,34 @@
         <f>'[1]TERM 1'!Q70</f>
         <v/>
       </c>
-      <c r="R68" s="58" t="str">
+      <c r="R68" s="125" t="str">
         <f>'[1]TERM 1'!R70</f>
         <v/>
       </c>
-      <c r="S68" s="61" t="str">
+      <c r="S68" s="127" t="str">
         <f>'[1]TERM 1'!S70</f>
         <v/>
       </c>
       <c r="T68" s="62"/>
       <c r="U68" s="55"/>
       <c r="V68" s="56"/>
-      <c r="W68" s="58" t="str">
+      <c r="W68" s="125" t="str">
         <f>'[1]TERM 1'!W70</f>
         <v/>
       </c>
-      <c r="X68" s="59" t="str">
+      <c r="X68" s="126" t="str">
         <f>'[1]TERM 1'!X70</f>
         <v/>
       </c>
-      <c r="Y68" s="63" t="str">
+      <c r="Y68" s="128" t="str">
         <f>'[1]TERM 1'!Y70</f>
         <v/>
       </c>
-      <c r="Z68" s="58" t="str">
+      <c r="Z68" s="125" t="str">
         <f>'[1]TERM 1'!Z70</f>
         <v/>
       </c>
-      <c r="AA68" s="61" t="str">
+      <c r="AA68" s="127" t="str">
         <f>'[1]TERM 1'!AA70</f>
         <v/>
       </c>
@@ -10850,11 +10934,11 @@
         <f>'[1]TERM 1'!K71</f>
         <v/>
       </c>
-      <c r="L69" s="58" t="str">
+      <c r="L69" s="125" t="str">
         <f>'[1]TERM 1'!L71</f>
         <v/>
       </c>
-      <c r="M69" s="59" t="str">
+      <c r="M69" s="126" t="str">
         <f>'[1]TERM 1'!M71</f>
         <v/>
       </c>
@@ -10865,34 +10949,34 @@
         <f>'[1]TERM 1'!Q71</f>
         <v/>
       </c>
-      <c r="R69" s="58" t="str">
+      <c r="R69" s="125" t="str">
         <f>'[1]TERM 1'!R71</f>
         <v/>
       </c>
-      <c r="S69" s="61" t="str">
+      <c r="S69" s="127" t="str">
         <f>'[1]TERM 1'!S71</f>
         <v/>
       </c>
       <c r="T69" s="62"/>
       <c r="U69" s="55"/>
       <c r="V69" s="56"/>
-      <c r="W69" s="58" t="str">
+      <c r="W69" s="125" t="str">
         <f>'[1]TERM 1'!W71</f>
         <v/>
       </c>
-      <c r="X69" s="59" t="str">
+      <c r="X69" s="126" t="str">
         <f>'[1]TERM 1'!X71</f>
         <v/>
       </c>
-      <c r="Y69" s="63" t="str">
+      <c r="Y69" s="128" t="str">
         <f>'[1]TERM 1'!Y71</f>
         <v/>
       </c>
-      <c r="Z69" s="58" t="str">
+      <c r="Z69" s="125" t="str">
         <f>'[1]TERM 1'!Z71</f>
         <v/>
       </c>
-      <c r="AA69" s="61" t="str">
+      <c r="AA69" s="127" t="str">
         <f>'[1]TERM 1'!AA71</f>
         <v/>
       </c>
@@ -10926,11 +11010,11 @@
         <f>'[1]TERM 1'!K72</f>
         <v/>
       </c>
-      <c r="L70" s="58" t="str">
+      <c r="L70" s="125" t="str">
         <f>'[1]TERM 1'!L72</f>
         <v/>
       </c>
-      <c r="M70" s="59" t="str">
+      <c r="M70" s="126" t="str">
         <f>'[1]TERM 1'!M72</f>
         <v/>
       </c>
@@ -10941,34 +11025,34 @@
         <f>'[1]TERM 1'!Q72</f>
         <v/>
       </c>
-      <c r="R70" s="58" t="str">
+      <c r="R70" s="125" t="str">
         <f>'[1]TERM 1'!R72</f>
         <v/>
       </c>
-      <c r="S70" s="61" t="str">
+      <c r="S70" s="127" t="str">
         <f>'[1]TERM 1'!S72</f>
         <v/>
       </c>
       <c r="T70" s="62"/>
       <c r="U70" s="55"/>
       <c r="V70" s="56"/>
-      <c r="W70" s="58" t="str">
+      <c r="W70" s="125" t="str">
         <f>'[1]TERM 1'!W72</f>
         <v/>
       </c>
-      <c r="X70" s="59" t="str">
+      <c r="X70" s="126" t="str">
         <f>'[1]TERM 1'!X72</f>
         <v/>
       </c>
-      <c r="Y70" s="63" t="str">
+      <c r="Y70" s="128" t="str">
         <f>'[1]TERM 1'!Y72</f>
         <v/>
       </c>
-      <c r="Z70" s="58" t="str">
+      <c r="Z70" s="125" t="str">
         <f>'[1]TERM 1'!Z72</f>
         <v/>
       </c>
-      <c r="AA70" s="61" t="str">
+      <c r="AA70" s="127" t="str">
         <f>'[1]TERM 1'!AA72</f>
         <v/>
       </c>
@@ -11002,11 +11086,11 @@
         <f>'[1]TERM 1'!K73</f>
         <v/>
       </c>
-      <c r="L71" s="58" t="str">
+      <c r="L71" s="125" t="str">
         <f>'[1]TERM 1'!L73</f>
         <v/>
       </c>
-      <c r="M71" s="59" t="str">
+      <c r="M71" s="126" t="str">
         <f>'[1]TERM 1'!M73</f>
         <v/>
       </c>
@@ -11017,34 +11101,34 @@
         <f>'[1]TERM 1'!Q73</f>
         <v/>
       </c>
-      <c r="R71" s="58" t="str">
+      <c r="R71" s="125" t="str">
         <f>'[1]TERM 1'!R73</f>
         <v/>
       </c>
-      <c r="S71" s="61" t="str">
+      <c r="S71" s="127" t="str">
         <f>'[1]TERM 1'!S73</f>
         <v/>
       </c>
       <c r="T71" s="62"/>
       <c r="U71" s="55"/>
       <c r="V71" s="56"/>
-      <c r="W71" s="58" t="str">
+      <c r="W71" s="125" t="str">
         <f>'[1]TERM 1'!W73</f>
         <v/>
       </c>
-      <c r="X71" s="59" t="str">
+      <c r="X71" s="126" t="str">
         <f>'[1]TERM 1'!X73</f>
         <v/>
       </c>
-      <c r="Y71" s="63" t="str">
+      <c r="Y71" s="128" t="str">
         <f>'[1]TERM 1'!Y73</f>
         <v/>
       </c>
-      <c r="Z71" s="58" t="str">
+      <c r="Z71" s="125" t="str">
         <f>'[1]TERM 1'!Z73</f>
         <v/>
       </c>
-      <c r="AA71" s="61" t="str">
+      <c r="AA71" s="127" t="str">
         <f>'[1]TERM 1'!AA73</f>
         <v/>
       </c>
@@ -11078,11 +11162,11 @@
         <f>'[1]TERM 1'!K74</f>
         <v/>
       </c>
-      <c r="L72" s="58" t="str">
+      <c r="L72" s="125" t="str">
         <f>'[1]TERM 1'!L74</f>
         <v/>
       </c>
-      <c r="M72" s="59" t="str">
+      <c r="M72" s="126" t="str">
         <f>'[1]TERM 1'!M74</f>
         <v/>
       </c>
@@ -11093,34 +11177,34 @@
         <f>'[1]TERM 1'!Q74</f>
         <v/>
       </c>
-      <c r="R72" s="58" t="str">
+      <c r="R72" s="125" t="str">
         <f>'[1]TERM 1'!R74</f>
         <v/>
       </c>
-      <c r="S72" s="61" t="str">
+      <c r="S72" s="127" t="str">
         <f>'[1]TERM 1'!S74</f>
         <v/>
       </c>
       <c r="T72" s="62"/>
       <c r="U72" s="55"/>
       <c r="V72" s="56"/>
-      <c r="W72" s="58" t="str">
+      <c r="W72" s="125" t="str">
         <f>'[1]TERM 1'!W74</f>
         <v/>
       </c>
-      <c r="X72" s="59" t="str">
+      <c r="X72" s="126" t="str">
         <f>'[1]TERM 1'!X74</f>
         <v/>
       </c>
-      <c r="Y72" s="63" t="str">
+      <c r="Y72" s="128" t="str">
         <f>'[1]TERM 1'!Y74</f>
         <v/>
       </c>
-      <c r="Z72" s="58" t="str">
+      <c r="Z72" s="125" t="str">
         <f>'[1]TERM 1'!Z74</f>
         <v/>
       </c>
-      <c r="AA72" s="61" t="str">
+      <c r="AA72" s="127" t="str">
         <f>'[1]TERM 1'!AA74</f>
         <v/>
       </c>
@@ -11154,11 +11238,11 @@
         <f>'[1]TERM 1'!K75</f>
         <v/>
       </c>
-      <c r="L73" s="58" t="str">
+      <c r="L73" s="125" t="str">
         <f>'[1]TERM 1'!L75</f>
         <v/>
       </c>
-      <c r="M73" s="59" t="str">
+      <c r="M73" s="126" t="str">
         <f>'[1]TERM 1'!M75</f>
         <v/>
       </c>
@@ -11169,34 +11253,34 @@
         <f>'[1]TERM 1'!Q75</f>
         <v/>
       </c>
-      <c r="R73" s="58" t="str">
+      <c r="R73" s="125" t="str">
         <f>'[1]TERM 1'!R75</f>
         <v/>
       </c>
-      <c r="S73" s="61" t="str">
+      <c r="S73" s="127" t="str">
         <f>'[1]TERM 1'!S75</f>
         <v/>
       </c>
       <c r="T73" s="62"/>
       <c r="U73" s="55"/>
       <c r="V73" s="56"/>
-      <c r="W73" s="58" t="str">
+      <c r="W73" s="125" t="str">
         <f>'[1]TERM 1'!W75</f>
         <v/>
       </c>
-      <c r="X73" s="59" t="str">
+      <c r="X73" s="126" t="str">
         <f>'[1]TERM 1'!X75</f>
         <v/>
       </c>
-      <c r="Y73" s="63" t="str">
+      <c r="Y73" s="128" t="str">
         <f>'[1]TERM 1'!Y75</f>
         <v/>
       </c>
-      <c r="Z73" s="58" t="str">
+      <c r="Z73" s="125" t="str">
         <f>'[1]TERM 1'!Z75</f>
         <v/>
       </c>
-      <c r="AA73" s="61" t="str">
+      <c r="AA73" s="127" t="str">
         <f>'[1]TERM 1'!AA75</f>
         <v/>
       </c>
@@ -11230,11 +11314,11 @@
         <f>'[1]TERM 1'!K76</f>
         <v/>
       </c>
-      <c r="L74" s="58" t="str">
+      <c r="L74" s="125" t="str">
         <f>'[1]TERM 1'!L76</f>
         <v/>
       </c>
-      <c r="M74" s="59" t="str">
+      <c r="M74" s="126" t="str">
         <f>'[1]TERM 1'!M76</f>
         <v/>
       </c>
@@ -11245,34 +11329,34 @@
         <f>'[1]TERM 1'!Q76</f>
         <v/>
       </c>
-      <c r="R74" s="58" t="str">
+      <c r="R74" s="125" t="str">
         <f>'[1]TERM 1'!R76</f>
         <v/>
       </c>
-      <c r="S74" s="61" t="str">
+      <c r="S74" s="127" t="str">
         <f>'[1]TERM 1'!S76</f>
         <v/>
       </c>
       <c r="T74" s="62"/>
       <c r="U74" s="55"/>
       <c r="V74" s="56"/>
-      <c r="W74" s="58" t="str">
+      <c r="W74" s="125" t="str">
         <f>'[1]TERM 1'!W76</f>
         <v/>
       </c>
-      <c r="X74" s="59" t="str">
+      <c r="X74" s="126" t="str">
         <f>'[1]TERM 1'!X76</f>
         <v/>
       </c>
-      <c r="Y74" s="63" t="str">
+      <c r="Y74" s="128" t="str">
         <f>'[1]TERM 1'!Y76</f>
         <v/>
       </c>
-      <c r="Z74" s="58" t="str">
+      <c r="Z74" s="125" t="str">
         <f>'[1]TERM 1'!Z76</f>
         <v/>
       </c>
-      <c r="AA74" s="61" t="str">
+      <c r="AA74" s="127" t="str">
         <f>'[1]TERM 1'!AA76</f>
         <v/>
       </c>
@@ -11306,11 +11390,11 @@
         <f>'[1]TERM 1'!K77</f>
         <v/>
       </c>
-      <c r="L75" s="58" t="str">
+      <c r="L75" s="125" t="str">
         <f>'[1]TERM 1'!L77</f>
         <v/>
       </c>
-      <c r="M75" s="59" t="str">
+      <c r="M75" s="126" t="str">
         <f>'[1]TERM 1'!M77</f>
         <v/>
       </c>
@@ -11321,34 +11405,34 @@
         <f>'[1]TERM 1'!Q77</f>
         <v/>
       </c>
-      <c r="R75" s="58" t="str">
+      <c r="R75" s="125" t="str">
         <f>'[1]TERM 1'!R77</f>
         <v/>
       </c>
-      <c r="S75" s="61" t="str">
+      <c r="S75" s="127" t="str">
         <f>'[1]TERM 1'!S77</f>
         <v/>
       </c>
       <c r="T75" s="62"/>
       <c r="U75" s="55"/>
       <c r="V75" s="56"/>
-      <c r="W75" s="58" t="str">
+      <c r="W75" s="125" t="str">
         <f>'[1]TERM 1'!W77</f>
         <v/>
       </c>
-      <c r="X75" s="59" t="str">
+      <c r="X75" s="126" t="str">
         <f>'[1]TERM 1'!X77</f>
         <v/>
       </c>
-      <c r="Y75" s="63" t="str">
+      <c r="Y75" s="128" t="str">
         <f>'[1]TERM 1'!Y77</f>
         <v/>
       </c>
-      <c r="Z75" s="58" t="str">
+      <c r="Z75" s="125" t="str">
         <f>'[1]TERM 1'!Z77</f>
         <v/>
       </c>
-      <c r="AA75" s="61" t="str">
+      <c r="AA75" s="127" t="str">
         <f>'[1]TERM 1'!AA77</f>
         <v/>
       </c>
@@ -11382,11 +11466,11 @@
         <f>'[1]TERM 1'!K78</f>
         <v/>
       </c>
-      <c r="L76" s="58" t="str">
+      <c r="L76" s="125" t="str">
         <f>'[1]TERM 1'!L78</f>
         <v/>
       </c>
-      <c r="M76" s="59" t="str">
+      <c r="M76" s="126" t="str">
         <f>'[1]TERM 1'!M78</f>
         <v/>
       </c>
@@ -11397,34 +11481,34 @@
         <f>'[1]TERM 1'!Q78</f>
         <v/>
       </c>
-      <c r="R76" s="58" t="str">
+      <c r="R76" s="125" t="str">
         <f>'[1]TERM 1'!R78</f>
         <v/>
       </c>
-      <c r="S76" s="61" t="str">
+      <c r="S76" s="127" t="str">
         <f>'[1]TERM 1'!S78</f>
         <v/>
       </c>
       <c r="T76" s="62"/>
       <c r="U76" s="55"/>
       <c r="V76" s="56"/>
-      <c r="W76" s="58" t="str">
+      <c r="W76" s="125" t="str">
         <f>'[1]TERM 1'!W78</f>
         <v/>
       </c>
-      <c r="X76" s="59" t="str">
+      <c r="X76" s="126" t="str">
         <f>'[1]TERM 1'!X78</f>
         <v/>
       </c>
-      <c r="Y76" s="63" t="str">
+      <c r="Y76" s="128" t="str">
         <f>'[1]TERM 1'!Y78</f>
         <v/>
       </c>
-      <c r="Z76" s="58" t="str">
+      <c r="Z76" s="125" t="str">
         <f>'[1]TERM 1'!Z78</f>
         <v/>
       </c>
-      <c r="AA76" s="61" t="str">
+      <c r="AA76" s="127" t="str">
         <f>'[1]TERM 1'!AA78</f>
         <v/>
       </c>
@@ -11458,11 +11542,11 @@
         <f>'[1]TERM 1'!K79</f>
         <v/>
       </c>
-      <c r="L77" s="58" t="str">
+      <c r="L77" s="125" t="str">
         <f>'[1]TERM 1'!L79</f>
         <v/>
       </c>
-      <c r="M77" s="59" t="str">
+      <c r="M77" s="126" t="str">
         <f>'[1]TERM 1'!M79</f>
         <v/>
       </c>
@@ -11473,34 +11557,34 @@
         <f>'[1]TERM 1'!Q79</f>
         <v/>
       </c>
-      <c r="R77" s="58" t="str">
+      <c r="R77" s="125" t="str">
         <f>'[1]TERM 1'!R79</f>
         <v/>
       </c>
-      <c r="S77" s="61" t="str">
+      <c r="S77" s="127" t="str">
         <f>'[1]TERM 1'!S79</f>
         <v/>
       </c>
       <c r="T77" s="62"/>
       <c r="U77" s="55"/>
       <c r="V77" s="56"/>
-      <c r="W77" s="58" t="str">
+      <c r="W77" s="125" t="str">
         <f>'[1]TERM 1'!W79</f>
         <v/>
       </c>
-      <c r="X77" s="59" t="str">
+      <c r="X77" s="126" t="str">
         <f>'[1]TERM 1'!X79</f>
         <v/>
       </c>
-      <c r="Y77" s="63" t="str">
+      <c r="Y77" s="128" t="str">
         <f>'[1]TERM 1'!Y79</f>
         <v/>
       </c>
-      <c r="Z77" s="58" t="str">
+      <c r="Z77" s="125" t="str">
         <f>'[1]TERM 1'!Z79</f>
         <v/>
       </c>
-      <c r="AA77" s="61" t="str">
+      <c r="AA77" s="127" t="str">
         <f>'[1]TERM 1'!AA79</f>
         <v/>
       </c>
@@ -11534,11 +11618,11 @@
         <f>'[1]TERM 1'!K80</f>
         <v/>
       </c>
-      <c r="L78" s="58" t="str">
+      <c r="L78" s="125" t="str">
         <f>'[1]TERM 1'!L80</f>
         <v/>
       </c>
-      <c r="M78" s="59" t="str">
+      <c r="M78" s="126" t="str">
         <f>'[1]TERM 1'!M80</f>
         <v/>
       </c>
@@ -11549,34 +11633,34 @@
         <f>'[1]TERM 1'!Q80</f>
         <v/>
       </c>
-      <c r="R78" s="58" t="str">
+      <c r="R78" s="125" t="str">
         <f>'[1]TERM 1'!R80</f>
         <v/>
       </c>
-      <c r="S78" s="61" t="str">
+      <c r="S78" s="127" t="str">
         <f>'[1]TERM 1'!S80</f>
         <v/>
       </c>
       <c r="T78" s="62"/>
       <c r="U78" s="55"/>
       <c r="V78" s="56"/>
-      <c r="W78" s="58" t="str">
+      <c r="W78" s="125" t="str">
         <f>'[1]TERM 1'!W80</f>
         <v/>
       </c>
-      <c r="X78" s="59" t="str">
+      <c r="X78" s="126" t="str">
         <f>'[1]TERM 1'!X80</f>
         <v/>
       </c>
-      <c r="Y78" s="63" t="str">
+      <c r="Y78" s="128" t="str">
         <f>'[1]TERM 1'!Y80</f>
         <v/>
       </c>
-      <c r="Z78" s="58" t="str">
+      <c r="Z78" s="125" t="str">
         <f>'[1]TERM 1'!Z80</f>
         <v/>
       </c>
-      <c r="AA78" s="61" t="str">
+      <c r="AA78" s="127" t="str">
         <f>'[1]TERM 1'!AA80</f>
         <v/>
       </c>
@@ -11610,11 +11694,11 @@
         <f>'[1]TERM 1'!K81</f>
         <v/>
       </c>
-      <c r="L79" s="58" t="str">
+      <c r="L79" s="125" t="str">
         <f>'[1]TERM 1'!L81</f>
         <v/>
       </c>
-      <c r="M79" s="59" t="str">
+      <c r="M79" s="126" t="str">
         <f>'[1]TERM 1'!M81</f>
         <v/>
       </c>
@@ -11625,34 +11709,34 @@
         <f>'[1]TERM 1'!Q81</f>
         <v/>
       </c>
-      <c r="R79" s="58" t="str">
+      <c r="R79" s="125" t="str">
         <f>'[1]TERM 1'!R81</f>
         <v/>
       </c>
-      <c r="S79" s="61" t="str">
+      <c r="S79" s="127" t="str">
         <f>'[1]TERM 1'!S81</f>
         <v/>
       </c>
       <c r="T79" s="62"/>
       <c r="U79" s="55"/>
       <c r="V79" s="56"/>
-      <c r="W79" s="58" t="str">
+      <c r="W79" s="125" t="str">
         <f>'[1]TERM 1'!W81</f>
         <v/>
       </c>
-      <c r="X79" s="59" t="str">
+      <c r="X79" s="126" t="str">
         <f>'[1]TERM 1'!X81</f>
         <v/>
       </c>
-      <c r="Y79" s="63" t="str">
+      <c r="Y79" s="128" t="str">
         <f>'[1]TERM 1'!Y81</f>
         <v/>
       </c>
-      <c r="Z79" s="58" t="str">
+      <c r="Z79" s="125" t="str">
         <f>'[1]TERM 1'!Z81</f>
         <v/>
       </c>
-      <c r="AA79" s="61" t="str">
+      <c r="AA79" s="127" t="str">
         <f>'[1]TERM 1'!AA81</f>
         <v/>
       </c>
@@ -11686,11 +11770,11 @@
         <f>'[1]TERM 1'!K82</f>
         <v/>
       </c>
-      <c r="L80" s="58" t="str">
+      <c r="L80" s="125" t="str">
         <f>'[1]TERM 1'!L82</f>
         <v/>
       </c>
-      <c r="M80" s="59" t="str">
+      <c r="M80" s="126" t="str">
         <f>'[1]TERM 1'!M82</f>
         <v/>
       </c>
@@ -11701,34 +11785,34 @@
         <f>'[1]TERM 1'!Q82</f>
         <v/>
       </c>
-      <c r="R80" s="58" t="str">
+      <c r="R80" s="125" t="str">
         <f>'[1]TERM 1'!R82</f>
         <v/>
       </c>
-      <c r="S80" s="61" t="str">
+      <c r="S80" s="127" t="str">
         <f>'[1]TERM 1'!S82</f>
         <v/>
       </c>
       <c r="T80" s="62"/>
       <c r="U80" s="55"/>
       <c r="V80" s="56"/>
-      <c r="W80" s="58" t="str">
+      <c r="W80" s="125" t="str">
         <f>'[1]TERM 1'!W82</f>
         <v/>
       </c>
-      <c r="X80" s="59" t="str">
+      <c r="X80" s="126" t="str">
         <f>'[1]TERM 1'!X82</f>
         <v/>
       </c>
-      <c r="Y80" s="63" t="str">
+      <c r="Y80" s="128" t="str">
         <f>'[1]TERM 1'!Y82</f>
         <v/>
       </c>
-      <c r="Z80" s="58" t="str">
+      <c r="Z80" s="125" t="str">
         <f>'[1]TERM 1'!Z82</f>
         <v/>
       </c>
-      <c r="AA80" s="61" t="str">
+      <c r="AA80" s="127" t="str">
         <f>'[1]TERM 1'!AA82</f>
         <v/>
       </c>
@@ -11762,11 +11846,11 @@
         <f>'[1]TERM 1'!K83</f>
         <v/>
       </c>
-      <c r="L81" s="58" t="str">
+      <c r="L81" s="125" t="str">
         <f>'[1]TERM 1'!L83</f>
         <v/>
       </c>
-      <c r="M81" s="59" t="str">
+      <c r="M81" s="126" t="str">
         <f>'[1]TERM 1'!M83</f>
         <v/>
       </c>
@@ -11777,34 +11861,34 @@
         <f>'[1]TERM 1'!Q83</f>
         <v/>
       </c>
-      <c r="R81" s="58" t="str">
+      <c r="R81" s="125" t="str">
         <f>'[1]TERM 1'!R83</f>
         <v/>
       </c>
-      <c r="S81" s="61" t="str">
+      <c r="S81" s="127" t="str">
         <f>'[1]TERM 1'!S83</f>
         <v/>
       </c>
       <c r="T81" s="62"/>
       <c r="U81" s="55"/>
       <c r="V81" s="56"/>
-      <c r="W81" s="58" t="str">
+      <c r="W81" s="125" t="str">
         <f>'[1]TERM 1'!W83</f>
         <v/>
       </c>
-      <c r="X81" s="59" t="str">
+      <c r="X81" s="126" t="str">
         <f>'[1]TERM 1'!X83</f>
         <v/>
       </c>
-      <c r="Y81" s="63" t="str">
+      <c r="Y81" s="128" t="str">
         <f>'[1]TERM 1'!Y83</f>
         <v/>
       </c>
-      <c r="Z81" s="58" t="str">
+      <c r="Z81" s="125" t="str">
         <f>'[1]TERM 1'!Z83</f>
         <v/>
       </c>
-      <c r="AA81" s="61" t="str">
+      <c r="AA81" s="127" t="str">
         <f>'[1]TERM 1'!AA83</f>
         <v/>
       </c>
@@ -11838,11 +11922,11 @@
         <f>'[1]TERM 1'!K84</f>
         <v/>
       </c>
-      <c r="L82" s="58" t="str">
+      <c r="L82" s="125" t="str">
         <f>'[1]TERM 1'!L84</f>
         <v/>
       </c>
-      <c r="M82" s="59" t="str">
+      <c r="M82" s="126" t="str">
         <f>'[1]TERM 1'!M84</f>
         <v/>
       </c>
@@ -11853,34 +11937,34 @@
         <f>'[1]TERM 1'!Q84</f>
         <v/>
       </c>
-      <c r="R82" s="58" t="str">
+      <c r="R82" s="125" t="str">
         <f>'[1]TERM 1'!R84</f>
         <v/>
       </c>
-      <c r="S82" s="61" t="str">
+      <c r="S82" s="127" t="str">
         <f>'[1]TERM 1'!S84</f>
         <v/>
       </c>
       <c r="T82" s="62"/>
       <c r="U82" s="55"/>
       <c r="V82" s="56"/>
-      <c r="W82" s="58" t="str">
+      <c r="W82" s="125" t="str">
         <f>'[1]TERM 1'!W84</f>
         <v/>
       </c>
-      <c r="X82" s="59" t="str">
+      <c r="X82" s="126" t="str">
         <f>'[1]TERM 1'!X84</f>
         <v/>
       </c>
-      <c r="Y82" s="63" t="str">
+      <c r="Y82" s="128" t="str">
         <f>'[1]TERM 1'!Y84</f>
         <v/>
       </c>
-      <c r="Z82" s="58" t="str">
+      <c r="Z82" s="125" t="str">
         <f>'[1]TERM 1'!Z84</f>
         <v/>
       </c>
-      <c r="AA82" s="61" t="str">
+      <c r="AA82" s="127" t="str">
         <f>'[1]TERM 1'!AA84</f>
         <v/>
       </c>
@@ -11914,11 +11998,11 @@
         <f>'[1]TERM 1'!K85</f>
         <v/>
       </c>
-      <c r="L83" s="58" t="str">
+      <c r="L83" s="125" t="str">
         <f>'[1]TERM 1'!L85</f>
         <v/>
       </c>
-      <c r="M83" s="59" t="str">
+      <c r="M83" s="126" t="str">
         <f>'[1]TERM 1'!M85</f>
         <v/>
       </c>
@@ -11929,34 +12013,34 @@
         <f>'[1]TERM 1'!Q85</f>
         <v/>
       </c>
-      <c r="R83" s="58" t="str">
+      <c r="R83" s="125" t="str">
         <f>'[1]TERM 1'!R85</f>
         <v/>
       </c>
-      <c r="S83" s="61" t="str">
+      <c r="S83" s="127" t="str">
         <f>'[1]TERM 1'!S85</f>
         <v/>
       </c>
       <c r="T83" s="62"/>
       <c r="U83" s="55"/>
       <c r="V83" s="56"/>
-      <c r="W83" s="58" t="str">
+      <c r="W83" s="125" t="str">
         <f>'[1]TERM 1'!W85</f>
         <v/>
       </c>
-      <c r="X83" s="59" t="str">
+      <c r="X83" s="126" t="str">
         <f>'[1]TERM 1'!X85</f>
         <v/>
       </c>
-      <c r="Y83" s="63" t="str">
+      <c r="Y83" s="128" t="str">
         <f>'[1]TERM 1'!Y85</f>
         <v/>
       </c>
-      <c r="Z83" s="58" t="str">
+      <c r="Z83" s="125" t="str">
         <f>'[1]TERM 1'!Z85</f>
         <v/>
       </c>
-      <c r="AA83" s="61" t="str">
+      <c r="AA83" s="127" t="str">
         <f>'[1]TERM 1'!AA85</f>
         <v/>
       </c>
@@ -11990,11 +12074,11 @@
         <f>'[1]TERM 1'!K86</f>
         <v/>
       </c>
-      <c r="L84" s="58" t="str">
+      <c r="L84" s="125" t="str">
         <f>'[1]TERM 1'!L86</f>
         <v/>
       </c>
-      <c r="M84" s="59" t="str">
+      <c r="M84" s="126" t="str">
         <f>'[1]TERM 1'!M86</f>
         <v/>
       </c>
@@ -12005,34 +12089,34 @@
         <f>'[1]TERM 1'!Q86</f>
         <v/>
       </c>
-      <c r="R84" s="58" t="str">
+      <c r="R84" s="125" t="str">
         <f>'[1]TERM 1'!R86</f>
         <v/>
       </c>
-      <c r="S84" s="61" t="str">
+      <c r="S84" s="127" t="str">
         <f>'[1]TERM 1'!S86</f>
         <v/>
       </c>
       <c r="T84" s="62"/>
       <c r="U84" s="55"/>
       <c r="V84" s="56"/>
-      <c r="W84" s="58" t="str">
+      <c r="W84" s="125" t="str">
         <f>'[1]TERM 1'!W86</f>
         <v/>
       </c>
-      <c r="X84" s="59" t="str">
+      <c r="X84" s="126" t="str">
         <f>'[1]TERM 1'!X86</f>
         <v/>
       </c>
-      <c r="Y84" s="63" t="str">
+      <c r="Y84" s="128" t="str">
         <f>'[1]TERM 1'!Y86</f>
         <v/>
       </c>
-      <c r="Z84" s="58" t="str">
+      <c r="Z84" s="125" t="str">
         <f>'[1]TERM 1'!Z86</f>
         <v/>
       </c>
-      <c r="AA84" s="61" t="str">
+      <c r="AA84" s="127" t="str">
         <f>'[1]TERM 1'!AA86</f>
         <v/>
       </c>
@@ -12066,11 +12150,11 @@
         <f>'[1]TERM 1'!K87</f>
         <v/>
       </c>
-      <c r="L85" s="58" t="str">
+      <c r="L85" s="125" t="str">
         <f>'[1]TERM 1'!L87</f>
         <v/>
       </c>
-      <c r="M85" s="59" t="str">
+      <c r="M85" s="126" t="str">
         <f>'[1]TERM 1'!M87</f>
         <v/>
       </c>
@@ -12081,34 +12165,34 @@
         <f>'[1]TERM 1'!Q87</f>
         <v/>
       </c>
-      <c r="R85" s="58" t="str">
+      <c r="R85" s="125" t="str">
         <f>'[1]TERM 1'!R87</f>
         <v/>
       </c>
-      <c r="S85" s="61" t="str">
+      <c r="S85" s="127" t="str">
         <f>'[1]TERM 1'!S87</f>
         <v/>
       </c>
       <c r="T85" s="62"/>
       <c r="U85" s="55"/>
       <c r="V85" s="56"/>
-      <c r="W85" s="58" t="str">
+      <c r="W85" s="125" t="str">
         <f>'[1]TERM 1'!W87</f>
         <v/>
       </c>
-      <c r="X85" s="59" t="str">
+      <c r="X85" s="126" t="str">
         <f>'[1]TERM 1'!X87</f>
         <v/>
       </c>
-      <c r="Y85" s="63" t="str">
+      <c r="Y85" s="128" t="str">
         <f>'[1]TERM 1'!Y87</f>
         <v/>
       </c>
-      <c r="Z85" s="58" t="str">
+      <c r="Z85" s="125" t="str">
         <f>'[1]TERM 1'!Z87</f>
         <v/>
       </c>
-      <c r="AA85" s="61" t="str">
+      <c r="AA85" s="127" t="str">
         <f>'[1]TERM 1'!AA87</f>
         <v/>
       </c>
@@ -12142,11 +12226,11 @@
         <f>'[1]TERM 1'!K88</f>
         <v/>
       </c>
-      <c r="L86" s="58" t="str">
+      <c r="L86" s="125" t="str">
         <f>'[1]TERM 1'!L88</f>
         <v/>
       </c>
-      <c r="M86" s="59" t="str">
+      <c r="M86" s="126" t="str">
         <f>'[1]TERM 1'!M88</f>
         <v/>
       </c>
@@ -12157,34 +12241,34 @@
         <f>'[1]TERM 1'!Q88</f>
         <v/>
       </c>
-      <c r="R86" s="58" t="str">
+      <c r="R86" s="125" t="str">
         <f>'[1]TERM 1'!R88</f>
         <v/>
       </c>
-      <c r="S86" s="61" t="str">
+      <c r="S86" s="127" t="str">
         <f>'[1]TERM 1'!S88</f>
         <v/>
       </c>
       <c r="T86" s="62"/>
       <c r="U86" s="55"/>
       <c r="V86" s="56"/>
-      <c r="W86" s="58" t="str">
+      <c r="W86" s="125" t="str">
         <f>'[1]TERM 1'!W88</f>
         <v/>
       </c>
-      <c r="X86" s="59" t="str">
+      <c r="X86" s="126" t="str">
         <f>'[1]TERM 1'!X88</f>
         <v/>
       </c>
-      <c r="Y86" s="63" t="str">
+      <c r="Y86" s="128" t="str">
         <f>'[1]TERM 1'!Y88</f>
         <v/>
       </c>
-      <c r="Z86" s="58" t="str">
+      <c r="Z86" s="125" t="str">
         <f>'[1]TERM 1'!Z88</f>
         <v/>
       </c>
-      <c r="AA86" s="61" t="str">
+      <c r="AA86" s="127" t="str">
         <f>'[1]TERM 1'!AA88</f>
         <v/>
       </c>
@@ -12218,11 +12302,11 @@
         <f>'[1]TERM 1'!K89</f>
         <v/>
       </c>
-      <c r="L87" s="58" t="str">
+      <c r="L87" s="125" t="str">
         <f>'[1]TERM 1'!L89</f>
         <v/>
       </c>
-      <c r="M87" s="59" t="str">
+      <c r="M87" s="126" t="str">
         <f>'[1]TERM 1'!M89</f>
         <v/>
       </c>
@@ -12233,34 +12317,34 @@
         <f>'[1]TERM 1'!Q89</f>
         <v/>
       </c>
-      <c r="R87" s="58" t="str">
+      <c r="R87" s="125" t="str">
         <f>'[1]TERM 1'!R89</f>
         <v/>
       </c>
-      <c r="S87" s="61" t="str">
+      <c r="S87" s="127" t="str">
         <f>'[1]TERM 1'!S89</f>
         <v/>
       </c>
       <c r="T87" s="62"/>
       <c r="U87" s="55"/>
       <c r="V87" s="56"/>
-      <c r="W87" s="58" t="str">
+      <c r="W87" s="125" t="str">
         <f>'[1]TERM 1'!W89</f>
         <v/>
       </c>
-      <c r="X87" s="59" t="str">
+      <c r="X87" s="126" t="str">
         <f>'[1]TERM 1'!X89</f>
         <v/>
       </c>
-      <c r="Y87" s="63" t="str">
+      <c r="Y87" s="128" t="str">
         <f>'[1]TERM 1'!Y89</f>
         <v/>
       </c>
-      <c r="Z87" s="58" t="str">
+      <c r="Z87" s="125" t="str">
         <f>'[1]TERM 1'!Z89</f>
         <v/>
       </c>
-      <c r="AA87" s="61" t="str">
+      <c r="AA87" s="127" t="str">
         <f>'[1]TERM 1'!AA89</f>
         <v/>
       </c>
@@ -12294,11 +12378,11 @@
         <f>'[1]TERM 1'!K90</f>
         <v/>
       </c>
-      <c r="L88" s="83" t="str">
+      <c r="L88" s="129" t="str">
         <f>'[1]TERM 1'!L90</f>
         <v/>
       </c>
-      <c r="M88" s="84" t="str">
+      <c r="M88" s="130" t="str">
         <f>'[1]TERM 1'!M90</f>
         <v/>
       </c>
@@ -12309,34 +12393,34 @@
         <f>'[1]TERM 1'!Q90</f>
         <v/>
       </c>
-      <c r="R88" s="83" t="str">
+      <c r="R88" s="129" t="str">
         <f>'[1]TERM 1'!R90</f>
         <v/>
       </c>
-      <c r="S88" s="86" t="str">
+      <c r="S88" s="131" t="str">
         <f>'[1]TERM 1'!S90</f>
         <v/>
       </c>
       <c r="T88" s="79"/>
       <c r="U88" s="80"/>
       <c r="V88" s="81"/>
-      <c r="W88" s="83" t="str">
+      <c r="W88" s="129" t="str">
         <f>'[1]TERM 1'!W90</f>
         <v/>
       </c>
-      <c r="X88" s="84" t="str">
+      <c r="X88" s="130" t="str">
         <f>'[1]TERM 1'!X90</f>
         <v/>
       </c>
-      <c r="Y88" s="35" t="str">
+      <c r="Y88" s="120" t="str">
         <f>'[1]TERM 1'!Y90</f>
         <v/>
       </c>
-      <c r="Z88" s="83" t="str">
+      <c r="Z88" s="129" t="str">
         <f>'[1]TERM 1'!Z90</f>
         <v/>
       </c>
-      <c r="AA88" s="86" t="str">
+      <c r="AA88" s="131" t="str">
         <f>'[1]TERM 1'!AA90</f>
         <v/>
       </c>
@@ -12370,11 +12454,11 @@
         <f>'[1]TERM 1'!K91</f>
         <v/>
       </c>
-      <c r="L89" s="95" t="str">
+      <c r="L89" s="133" t="str">
         <f>'[1]TERM 1'!L91</f>
         <v/>
       </c>
-      <c r="M89" s="96" t="str">
+      <c r="M89" s="134" t="str">
         <f>'[1]TERM 1'!M91</f>
         <v/>
       </c>
@@ -12385,34 +12469,34 @@
         <f>'[1]TERM 1'!Q91</f>
         <v/>
       </c>
-      <c r="R89" s="95" t="str">
+      <c r="R89" s="133" t="str">
         <f>'[1]TERM 1'!R91</f>
         <v/>
       </c>
-      <c r="S89" s="96" t="str">
+      <c r="S89" s="134" t="str">
         <f>'[1]TERM 1'!S91</f>
         <v/>
       </c>
       <c r="T89" s="91"/>
       <c r="U89" s="92"/>
       <c r="V89" s="93"/>
-      <c r="W89" s="95" t="str">
+      <c r="W89" s="133" t="str">
         <f>'[1]TERM 1'!W91</f>
         <v/>
       </c>
-      <c r="X89" s="95" t="str">
+      <c r="X89" s="133" t="str">
         <f>'[1]TERM 1'!X91</f>
         <v/>
       </c>
-      <c r="Y89" s="94" t="str">
+      <c r="Y89" s="132" t="str">
         <f>'[1]TERM 1'!Y91</f>
         <v/>
       </c>
-      <c r="Z89" s="95" t="str">
+      <c r="Z89" s="133" t="str">
         <f>'[1]TERM 1'!Z91</f>
         <v/>
       </c>
-      <c r="AA89" s="95" t="str">
+      <c r="AA89" s="133" t="str">
         <f>'[1]TERM 1'!AA91</f>
         <v/>
       </c>
@@ -12446,11 +12530,11 @@
         <f>'[1]TERM 1'!K92</f>
         <v/>
       </c>
-      <c r="L90" s="104" t="str">
+      <c r="L90" s="136" t="str">
         <f>'[1]TERM 1'!L92</f>
         <v/>
       </c>
-      <c r="M90" s="105" t="str">
+      <c r="M90" s="137" t="str">
         <f>'[1]TERM 1'!M92</f>
         <v/>
       </c>
@@ -12461,34 +12545,34 @@
         <f>'[1]TERM 1'!Q92</f>
         <v/>
       </c>
-      <c r="R90" s="104" t="str">
+      <c r="R90" s="136" t="str">
         <f>'[1]TERM 1'!R92</f>
         <v/>
       </c>
-      <c r="S90" s="105" t="str">
+      <c r="S90" s="137" t="str">
         <f>'[1]TERM 1'!S92</f>
         <v/>
       </c>
       <c r="T90" s="100"/>
       <c r="U90" s="101"/>
       <c r="V90" s="102"/>
-      <c r="W90" s="104" t="str">
+      <c r="W90" s="136" t="str">
         <f>'[1]TERM 1'!W92</f>
         <v/>
       </c>
-      <c r="X90" s="104" t="str">
+      <c r="X90" s="136" t="str">
         <f>'[1]TERM 1'!X92</f>
         <v/>
       </c>
-      <c r="Y90" s="103" t="str">
+      <c r="Y90" s="135" t="str">
         <f>'[1]TERM 1'!Y92</f>
         <v/>
       </c>
-      <c r="Z90" s="104" t="str">
+      <c r="Z90" s="136" t="str">
         <f>'[1]TERM 1'!Z92</f>
         <v/>
       </c>
-      <c r="AA90" s="104" t="str">
+      <c r="AA90" s="136" t="str">
         <f>'[1]TERM 1'!AA92</f>
         <v/>
       </c>
@@ -12522,11 +12606,11 @@
         <f>'[1]TERM 1'!K93</f>
         <v/>
       </c>
-      <c r="L91" s="104" t="str">
+      <c r="L91" s="136" t="str">
         <f>'[1]TERM 1'!L93</f>
         <v/>
       </c>
-      <c r="M91" s="105" t="str">
+      <c r="M91" s="137" t="str">
         <f>'[1]TERM 1'!M93</f>
         <v/>
       </c>
@@ -12537,34 +12621,34 @@
         <f>'[1]TERM 1'!Q93</f>
         <v/>
       </c>
-      <c r="R91" s="104" t="str">
+      <c r="R91" s="136" t="str">
         <f>'[1]TERM 1'!R93</f>
         <v/>
       </c>
-      <c r="S91" s="105" t="str">
+      <c r="S91" s="137" t="str">
         <f>'[1]TERM 1'!S93</f>
         <v/>
       </c>
       <c r="T91" s="100"/>
       <c r="U91" s="101"/>
       <c r="V91" s="102"/>
-      <c r="W91" s="104" t="str">
+      <c r="W91" s="136" t="str">
         <f>'[1]TERM 1'!W93</f>
         <v/>
       </c>
-      <c r="X91" s="104" t="str">
+      <c r="X91" s="136" t="str">
         <f>'[1]TERM 1'!X93</f>
         <v/>
       </c>
-      <c r="Y91" s="103" t="str">
+      <c r="Y91" s="135" t="str">
         <f>'[1]TERM 1'!Y93</f>
         <v/>
       </c>
-      <c r="Z91" s="104" t="str">
+      <c r="Z91" s="136" t="str">
         <f>'[1]TERM 1'!Z93</f>
         <v/>
       </c>
-      <c r="AA91" s="104" t="str">
+      <c r="AA91" s="136" t="str">
         <f>'[1]TERM 1'!AA93</f>
         <v/>
       </c>
@@ -12598,11 +12682,11 @@
         <f>'[1]TERM 1'!K94</f>
         <v/>
       </c>
-      <c r="L92" s="104" t="str">
+      <c r="L92" s="136" t="str">
         <f>'[1]TERM 1'!L94</f>
         <v/>
       </c>
-      <c r="M92" s="105" t="str">
+      <c r="M92" s="137" t="str">
         <f>'[1]TERM 1'!M94</f>
         <v/>
       </c>
@@ -12613,34 +12697,34 @@
         <f>'[1]TERM 1'!Q94</f>
         <v/>
       </c>
-      <c r="R92" s="104" t="str">
+      <c r="R92" s="136" t="str">
         <f>'[1]TERM 1'!R94</f>
         <v/>
       </c>
-      <c r="S92" s="105" t="str">
+      <c r="S92" s="137" t="str">
         <f>'[1]TERM 1'!S94</f>
         <v/>
       </c>
       <c r="T92" s="100"/>
       <c r="U92" s="101"/>
       <c r="V92" s="102"/>
-      <c r="W92" s="104" t="str">
+      <c r="W92" s="136" t="str">
         <f>'[1]TERM 1'!W94</f>
         <v/>
       </c>
-      <c r="X92" s="104" t="str">
+      <c r="X92" s="136" t="str">
         <f>'[1]TERM 1'!X94</f>
         <v/>
       </c>
-      <c r="Y92" s="103" t="str">
+      <c r="Y92" s="135" t="str">
         <f>'[1]TERM 1'!Y94</f>
         <v/>
       </c>
-      <c r="Z92" s="104" t="str">
+      <c r="Z92" s="136" t="str">
         <f>'[1]TERM 1'!Z94</f>
         <v/>
       </c>
-      <c r="AA92" s="104" t="str">
+      <c r="AA92" s="136" t="str">
         <f>'[1]TERM 1'!AA94</f>
         <v/>
       </c>
@@ -12674,11 +12758,11 @@
         <f>'[1]TERM 1'!K95</f>
         <v/>
       </c>
-      <c r="L93" s="104" t="str">
+      <c r="L93" s="136" t="str">
         <f>'[1]TERM 1'!L95</f>
         <v/>
       </c>
-      <c r="M93" s="105" t="str">
+      <c r="M93" s="137" t="str">
         <f>'[1]TERM 1'!M95</f>
         <v/>
       </c>
@@ -12689,34 +12773,34 @@
         <f>'[1]TERM 1'!Q95</f>
         <v/>
       </c>
-      <c r="R93" s="104" t="str">
+      <c r="R93" s="136" t="str">
         <f>'[1]TERM 1'!R95</f>
         <v/>
       </c>
-      <c r="S93" s="105" t="str">
+      <c r="S93" s="137" t="str">
         <f>'[1]TERM 1'!S95</f>
         <v/>
       </c>
       <c r="T93" s="100"/>
       <c r="U93" s="101"/>
       <c r="V93" s="102"/>
-      <c r="W93" s="104" t="str">
+      <c r="W93" s="136" t="str">
         <f>'[1]TERM 1'!W95</f>
         <v/>
       </c>
-      <c r="X93" s="104" t="str">
+      <c r="X93" s="136" t="str">
         <f>'[1]TERM 1'!X95</f>
         <v/>
       </c>
-      <c r="Y93" s="103" t="str">
+      <c r="Y93" s="135" t="str">
         <f>'[1]TERM 1'!Y95</f>
         <v/>
       </c>
-      <c r="Z93" s="104" t="str">
+      <c r="Z93" s="136" t="str">
         <f>'[1]TERM 1'!Z95</f>
         <v/>
       </c>
-      <c r="AA93" s="104" t="str">
+      <c r="AA93" s="136" t="str">
         <f>'[1]TERM 1'!AA95</f>
         <v/>
       </c>
@@ -12750,11 +12834,11 @@
         <f>'[1]TERM 1'!K96</f>
         <v/>
       </c>
-      <c r="L94" s="104" t="str">
+      <c r="L94" s="136" t="str">
         <f>'[1]TERM 1'!L96</f>
         <v/>
       </c>
-      <c r="M94" s="105" t="str">
+      <c r="M94" s="137" t="str">
         <f>'[1]TERM 1'!M96</f>
         <v/>
       </c>
@@ -12765,34 +12849,34 @@
         <f>'[1]TERM 1'!Q96</f>
         <v/>
       </c>
-      <c r="R94" s="104" t="str">
+      <c r="R94" s="136" t="str">
         <f>'[1]TERM 1'!R96</f>
         <v/>
       </c>
-      <c r="S94" s="105" t="str">
+      <c r="S94" s="137" t="str">
         <f>'[1]TERM 1'!S96</f>
         <v/>
       </c>
       <c r="T94" s="100"/>
       <c r="U94" s="101"/>
       <c r="V94" s="102"/>
-      <c r="W94" s="104" t="str">
+      <c r="W94" s="136" t="str">
         <f>'[1]TERM 1'!W96</f>
         <v/>
       </c>
-      <c r="X94" s="104" t="str">
+      <c r="X94" s="136" t="str">
         <f>'[1]TERM 1'!X96</f>
         <v/>
       </c>
-      <c r="Y94" s="103" t="str">
+      <c r="Y94" s="135" t="str">
         <f>'[1]TERM 1'!Y96</f>
         <v/>
       </c>
-      <c r="Z94" s="104" t="str">
+      <c r="Z94" s="136" t="str">
         <f>'[1]TERM 1'!Z96</f>
         <v/>
       </c>
-      <c r="AA94" s="104" t="str">
+      <c r="AA94" s="136" t="str">
         <f>'[1]TERM 1'!AA96</f>
         <v/>
       </c>
@@ -12826,11 +12910,11 @@
         <f>'[1]TERM 1'!K97</f>
         <v/>
       </c>
-      <c r="L95" s="104" t="str">
+      <c r="L95" s="136" t="str">
         <f>'[1]TERM 1'!L97</f>
         <v/>
       </c>
-      <c r="M95" s="105" t="str">
+      <c r="M95" s="137" t="str">
         <f>'[1]TERM 1'!M97</f>
         <v/>
       </c>
@@ -12841,34 +12925,34 @@
         <f>'[1]TERM 1'!Q97</f>
         <v/>
       </c>
-      <c r="R95" s="104" t="str">
+      <c r="R95" s="136" t="str">
         <f>'[1]TERM 1'!R97</f>
         <v/>
       </c>
-      <c r="S95" s="105" t="str">
+      <c r="S95" s="137" t="str">
         <f>'[1]TERM 1'!S97</f>
         <v/>
       </c>
       <c r="T95" s="100"/>
       <c r="U95" s="101"/>
       <c r="V95" s="102"/>
-      <c r="W95" s="104" t="str">
+      <c r="W95" s="136" t="str">
         <f>'[1]TERM 1'!W97</f>
         <v/>
       </c>
-      <c r="X95" s="104" t="str">
+      <c r="X95" s="136" t="str">
         <f>'[1]TERM 1'!X97</f>
         <v/>
       </c>
-      <c r="Y95" s="103" t="str">
+      <c r="Y95" s="135" t="str">
         <f>'[1]TERM 1'!Y97</f>
         <v/>
       </c>
-      <c r="Z95" s="104" t="str">
+      <c r="Z95" s="136" t="str">
         <f>'[1]TERM 1'!Z97</f>
         <v/>
       </c>
-      <c r="AA95" s="104" t="str">
+      <c r="AA95" s="136" t="str">
         <f>'[1]TERM 1'!AA97</f>
         <v/>
       </c>
@@ -12902,11 +12986,11 @@
         <f>'[1]TERM 1'!K98</f>
         <v/>
       </c>
-      <c r="L96" s="104" t="str">
+      <c r="L96" s="136" t="str">
         <f>'[1]TERM 1'!L98</f>
         <v/>
       </c>
-      <c r="M96" s="105" t="str">
+      <c r="M96" s="137" t="str">
         <f>'[1]TERM 1'!M98</f>
         <v/>
       </c>
@@ -12917,34 +13001,34 @@
         <f>'[1]TERM 1'!Q98</f>
         <v/>
       </c>
-      <c r="R96" s="104" t="str">
+      <c r="R96" s="136" t="str">
         <f>'[1]TERM 1'!R98</f>
         <v/>
       </c>
-      <c r="S96" s="105" t="str">
+      <c r="S96" s="137" t="str">
         <f>'[1]TERM 1'!S98</f>
         <v/>
       </c>
       <c r="T96" s="100"/>
       <c r="U96" s="101"/>
       <c r="V96" s="102"/>
-      <c r="W96" s="104" t="str">
+      <c r="W96" s="136" t="str">
         <f>'[1]TERM 1'!W98</f>
         <v/>
       </c>
-      <c r="X96" s="104" t="str">
+      <c r="X96" s="136" t="str">
         <f>'[1]TERM 1'!X98</f>
         <v/>
       </c>
-      <c r="Y96" s="103" t="str">
+      <c r="Y96" s="135" t="str">
         <f>'[1]TERM 1'!Y98</f>
         <v/>
       </c>
-      <c r="Z96" s="104" t="str">
+      <c r="Z96" s="136" t="str">
         <f>'[1]TERM 1'!Z98</f>
         <v/>
       </c>
-      <c r="AA96" s="104" t="str">
+      <c r="AA96" s="136" t="str">
         <f>'[1]TERM 1'!AA98</f>
         <v/>
       </c>
@@ -12978,11 +13062,11 @@
         <f>'[1]TERM 1'!K99</f>
         <v/>
       </c>
-      <c r="L97" s="104" t="str">
+      <c r="L97" s="136" t="str">
         <f>'[1]TERM 1'!L99</f>
         <v/>
       </c>
-      <c r="M97" s="105" t="str">
+      <c r="M97" s="137" t="str">
         <f>'[1]TERM 1'!M99</f>
         <v/>
       </c>
@@ -12993,34 +13077,34 @@
         <f>'[1]TERM 1'!Q99</f>
         <v/>
       </c>
-      <c r="R97" s="104" t="str">
+      <c r="R97" s="136" t="str">
         <f>'[1]TERM 1'!R99</f>
         <v/>
       </c>
-      <c r="S97" s="105" t="str">
+      <c r="S97" s="137" t="str">
         <f>'[1]TERM 1'!S99</f>
         <v/>
       </c>
       <c r="T97" s="100"/>
       <c r="U97" s="101"/>
       <c r="V97" s="102"/>
-      <c r="W97" s="104" t="str">
+      <c r="W97" s="136" t="str">
         <f>'[1]TERM 1'!W99</f>
         <v/>
       </c>
-      <c r="X97" s="104" t="str">
+      <c r="X97" s="136" t="str">
         <f>'[1]TERM 1'!X99</f>
         <v/>
       </c>
-      <c r="Y97" s="103" t="str">
+      <c r="Y97" s="135" t="str">
         <f>'[1]TERM 1'!Y99</f>
         <v/>
       </c>
-      <c r="Z97" s="104" t="str">
+      <c r="Z97" s="136" t="str">
         <f>'[1]TERM 1'!Z99</f>
         <v/>
       </c>
-      <c r="AA97" s="104" t="str">
+      <c r="AA97" s="136" t="str">
         <f>'[1]TERM 1'!AA99</f>
         <v/>
       </c>
@@ -13054,11 +13138,11 @@
         <f>'[1]TERM 1'!K100</f>
         <v/>
       </c>
-      <c r="L98" s="104" t="str">
+      <c r="L98" s="136" t="str">
         <f>'[1]TERM 1'!L100</f>
         <v/>
       </c>
-      <c r="M98" s="105" t="str">
+      <c r="M98" s="137" t="str">
         <f>'[1]TERM 1'!M100</f>
         <v/>
       </c>
@@ -13069,34 +13153,34 @@
         <f>'[1]TERM 1'!Q100</f>
         <v/>
       </c>
-      <c r="R98" s="104" t="str">
+      <c r="R98" s="136" t="str">
         <f>'[1]TERM 1'!R100</f>
         <v/>
       </c>
-      <c r="S98" s="105" t="str">
+      <c r="S98" s="137" t="str">
         <f>'[1]TERM 1'!S100</f>
         <v/>
       </c>
       <c r="T98" s="100"/>
       <c r="U98" s="101"/>
       <c r="V98" s="102"/>
-      <c r="W98" s="104" t="str">
+      <c r="W98" s="136" t="str">
         <f>'[1]TERM 1'!W100</f>
         <v/>
       </c>
-      <c r="X98" s="104" t="str">
+      <c r="X98" s="136" t="str">
         <f>'[1]TERM 1'!X100</f>
         <v/>
       </c>
-      <c r="Y98" s="103" t="str">
+      <c r="Y98" s="135" t="str">
         <f>'[1]TERM 1'!Y100</f>
         <v/>
       </c>
-      <c r="Z98" s="104" t="str">
+      <c r="Z98" s="136" t="str">
         <f>'[1]TERM 1'!Z100</f>
         <v/>
       </c>
-      <c r="AA98" s="104" t="str">
+      <c r="AA98" s="136" t="str">
         <f>'[1]TERM 1'!AA100</f>
         <v/>
       </c>
@@ -13130,11 +13214,11 @@
         <f>'[1]TERM 1'!K101</f>
         <v/>
       </c>
-      <c r="L99" s="104" t="str">
+      <c r="L99" s="136" t="str">
         <f>'[1]TERM 1'!L101</f>
         <v/>
       </c>
-      <c r="M99" s="105" t="str">
+      <c r="M99" s="137" t="str">
         <f>'[1]TERM 1'!M101</f>
         <v/>
       </c>
@@ -13145,34 +13229,34 @@
         <f>'[1]TERM 1'!Q101</f>
         <v/>
       </c>
-      <c r="R99" s="104" t="str">
+      <c r="R99" s="136" t="str">
         <f>'[1]TERM 1'!R101</f>
         <v/>
       </c>
-      <c r="S99" s="105" t="str">
+      <c r="S99" s="137" t="str">
         <f>'[1]TERM 1'!S101</f>
         <v/>
       </c>
       <c r="T99" s="100"/>
       <c r="U99" s="101"/>
       <c r="V99" s="102"/>
-      <c r="W99" s="104" t="str">
+      <c r="W99" s="136" t="str">
         <f>'[1]TERM 1'!W101</f>
         <v/>
       </c>
-      <c r="X99" s="104" t="str">
+      <c r="X99" s="136" t="str">
         <f>'[1]TERM 1'!X101</f>
         <v/>
       </c>
-      <c r="Y99" s="103" t="str">
+      <c r="Y99" s="135" t="str">
         <f>'[1]TERM 1'!Y101</f>
         <v/>
       </c>
-      <c r="Z99" s="104" t="str">
+      <c r="Z99" s="136" t="str">
         <f>'[1]TERM 1'!Z101</f>
         <v/>
       </c>
-      <c r="AA99" s="104" t="str">
+      <c r="AA99" s="136" t="str">
         <f>'[1]TERM 1'!AA101</f>
         <v/>
       </c>
@@ -13206,11 +13290,11 @@
         <f>'[1]TERM 1'!K102</f>
         <v/>
       </c>
-      <c r="L100" s="104" t="str">
+      <c r="L100" s="136" t="str">
         <f>'[1]TERM 1'!L102</f>
         <v/>
       </c>
-      <c r="M100" s="105" t="str">
+      <c r="M100" s="137" t="str">
         <f>'[1]TERM 1'!M102</f>
         <v/>
       </c>
@@ -13221,34 +13305,34 @@
         <f>'[1]TERM 1'!Q102</f>
         <v/>
       </c>
-      <c r="R100" s="104" t="str">
+      <c r="R100" s="136" t="str">
         <f>'[1]TERM 1'!R102</f>
         <v/>
       </c>
-      <c r="S100" s="105" t="str">
+      <c r="S100" s="137" t="str">
         <f>'[1]TERM 1'!S102</f>
         <v/>
       </c>
       <c r="T100" s="100"/>
       <c r="U100" s="101"/>
       <c r="V100" s="102"/>
-      <c r="W100" s="104" t="str">
+      <c r="W100" s="136" t="str">
         <f>'[1]TERM 1'!W102</f>
         <v/>
       </c>
-      <c r="X100" s="104" t="str">
+      <c r="X100" s="136" t="str">
         <f>'[1]TERM 1'!X102</f>
         <v/>
       </c>
-      <c r="Y100" s="103" t="str">
+      <c r="Y100" s="135" t="str">
         <f>'[1]TERM 1'!Y102</f>
         <v/>
       </c>
-      <c r="Z100" s="104" t="str">
+      <c r="Z100" s="136" t="str">
         <f>'[1]TERM 1'!Z102</f>
         <v/>
       </c>
-      <c r="AA100" s="104" t="str">
+      <c r="AA100" s="136" t="str">
         <f>'[1]TERM 1'!AA102</f>
         <v/>
       </c>
@@ -13282,11 +13366,11 @@
         <f>'[1]TERM 1'!K103</f>
         <v/>
       </c>
-      <c r="L101" s="104" t="str">
+      <c r="L101" s="136" t="str">
         <f>'[1]TERM 1'!L103</f>
         <v/>
       </c>
-      <c r="M101" s="105" t="str">
+      <c r="M101" s="137" t="str">
         <f>'[1]TERM 1'!M103</f>
         <v/>
       </c>
@@ -13297,34 +13381,34 @@
         <f>'[1]TERM 1'!Q103</f>
         <v/>
       </c>
-      <c r="R101" s="104" t="str">
+      <c r="R101" s="136" t="str">
         <f>'[1]TERM 1'!R103</f>
         <v/>
       </c>
-      <c r="S101" s="105" t="str">
+      <c r="S101" s="137" t="str">
         <f>'[1]TERM 1'!S103</f>
         <v/>
       </c>
       <c r="T101" s="100"/>
       <c r="U101" s="101"/>
       <c r="V101" s="102"/>
-      <c r="W101" s="104" t="str">
+      <c r="W101" s="136" t="str">
         <f>'[1]TERM 1'!W103</f>
         <v/>
       </c>
-      <c r="X101" s="104" t="str">
+      <c r="X101" s="136" t="str">
         <f>'[1]TERM 1'!X103</f>
         <v/>
       </c>
-      <c r="Y101" s="103" t="str">
+      <c r="Y101" s="135" t="str">
         <f>'[1]TERM 1'!Y103</f>
         <v/>
       </c>
-      <c r="Z101" s="104" t="str">
+      <c r="Z101" s="136" t="str">
         <f>'[1]TERM 1'!Z103</f>
         <v/>
       </c>
-      <c r="AA101" s="104" t="str">
+      <c r="AA101" s="136" t="str">
         <f>'[1]TERM 1'!AA103</f>
         <v/>
       </c>
@@ -13358,11 +13442,11 @@
         <f>'[1]TERM 1'!K104</f>
         <v/>
       </c>
-      <c r="L102" s="104" t="str">
+      <c r="L102" s="136" t="str">
         <f>'[1]TERM 1'!L104</f>
         <v/>
       </c>
-      <c r="M102" s="105" t="str">
+      <c r="M102" s="137" t="str">
         <f>'[1]TERM 1'!M104</f>
         <v/>
       </c>
@@ -13373,34 +13457,34 @@
         <f>'[1]TERM 1'!Q104</f>
         <v/>
       </c>
-      <c r="R102" s="104" t="str">
+      <c r="R102" s="136" t="str">
         <f>'[1]TERM 1'!R104</f>
         <v/>
       </c>
-      <c r="S102" s="105" t="str">
+      <c r="S102" s="137" t="str">
         <f>'[1]TERM 1'!S104</f>
         <v/>
       </c>
       <c r="T102" s="100"/>
       <c r="U102" s="101"/>
       <c r="V102" s="102"/>
-      <c r="W102" s="104" t="str">
+      <c r="W102" s="136" t="str">
         <f>'[1]TERM 1'!W104</f>
         <v/>
       </c>
-      <c r="X102" s="104" t="str">
+      <c r="X102" s="136" t="str">
         <f>'[1]TERM 1'!X104</f>
         <v/>
       </c>
-      <c r="Y102" s="103" t="str">
+      <c r="Y102" s="135" t="str">
         <f>'[1]TERM 1'!Y104</f>
         <v/>
       </c>
-      <c r="Z102" s="104" t="str">
+      <c r="Z102" s="136" t="str">
         <f>'[1]TERM 1'!Z104</f>
         <v/>
       </c>
-      <c r="AA102" s="104" t="str">
+      <c r="AA102" s="136" t="str">
         <f>'[1]TERM 1'!AA104</f>
         <v/>
       </c>
@@ -13434,11 +13518,11 @@
         <f>'[1]TERM 1'!K105</f>
         <v/>
       </c>
-      <c r="L103" s="104" t="str">
+      <c r="L103" s="136" t="str">
         <f>'[1]TERM 1'!L105</f>
         <v/>
       </c>
-      <c r="M103" s="105" t="str">
+      <c r="M103" s="137" t="str">
         <f>'[1]TERM 1'!M105</f>
         <v/>
       </c>
@@ -13449,34 +13533,34 @@
         <f>'[1]TERM 1'!Q105</f>
         <v/>
       </c>
-      <c r="R103" s="104" t="str">
+      <c r="R103" s="136" t="str">
         <f>'[1]TERM 1'!R105</f>
         <v/>
       </c>
-      <c r="S103" s="105" t="str">
+      <c r="S103" s="137" t="str">
         <f>'[1]TERM 1'!S105</f>
         <v/>
       </c>
       <c r="T103" s="100"/>
       <c r="U103" s="101"/>
       <c r="V103" s="102"/>
-      <c r="W103" s="104" t="str">
+      <c r="W103" s="136" t="str">
         <f>'[1]TERM 1'!W105</f>
         <v/>
       </c>
-      <c r="X103" s="104" t="str">
+      <c r="X103" s="136" t="str">
         <f>'[1]TERM 1'!X105</f>
         <v/>
       </c>
-      <c r="Y103" s="103" t="str">
+      <c r="Y103" s="135" t="str">
         <f>'[1]TERM 1'!Y105</f>
         <v/>
       </c>
-      <c r="Z103" s="104" t="str">
+      <c r="Z103" s="136" t="str">
         <f>'[1]TERM 1'!Z105</f>
         <v/>
       </c>
-      <c r="AA103" s="104" t="str">
+      <c r="AA103" s="136" t="str">
         <f>'[1]TERM 1'!AA105</f>
         <v/>
       </c>
@@ -13510,11 +13594,11 @@
         <f>'[1]TERM 1'!K106</f>
         <v/>
       </c>
-      <c r="L104" s="104" t="str">
+      <c r="L104" s="136" t="str">
         <f>'[1]TERM 1'!L106</f>
         <v/>
       </c>
-      <c r="M104" s="105" t="str">
+      <c r="M104" s="137" t="str">
         <f>'[1]TERM 1'!M106</f>
         <v/>
       </c>
@@ -13525,34 +13609,34 @@
         <f>'[1]TERM 1'!Q106</f>
         <v/>
       </c>
-      <c r="R104" s="104" t="str">
+      <c r="R104" s="136" t="str">
         <f>'[1]TERM 1'!R106</f>
         <v/>
       </c>
-      <c r="S104" s="105" t="str">
+      <c r="S104" s="137" t="str">
         <f>'[1]TERM 1'!S106</f>
         <v/>
       </c>
       <c r="T104" s="100"/>
       <c r="U104" s="101"/>
       <c r="V104" s="102"/>
-      <c r="W104" s="104" t="str">
+      <c r="W104" s="136" t="str">
         <f>'[1]TERM 1'!W106</f>
         <v/>
       </c>
-      <c r="X104" s="104" t="str">
+      <c r="X104" s="136" t="str">
         <f>'[1]TERM 1'!X106</f>
         <v/>
       </c>
-      <c r="Y104" s="103" t="str">
+      <c r="Y104" s="135" t="str">
         <f>'[1]TERM 1'!Y106</f>
         <v/>
       </c>
-      <c r="Z104" s="104" t="str">
+      <c r="Z104" s="136" t="str">
         <f>'[1]TERM 1'!Z106</f>
         <v/>
       </c>
-      <c r="AA104" s="104" t="str">
+      <c r="AA104" s="136" t="str">
         <f>'[1]TERM 1'!AA106</f>
         <v/>
       </c>
@@ -13586,11 +13670,11 @@
         <f>'[1]TERM 1'!K107</f>
         <v/>
       </c>
-      <c r="L105" s="104" t="str">
+      <c r="L105" s="136" t="str">
         <f>'[1]TERM 1'!L107</f>
         <v/>
       </c>
-      <c r="M105" s="105" t="str">
+      <c r="M105" s="137" t="str">
         <f>'[1]TERM 1'!M107</f>
         <v/>
       </c>
@@ -13601,34 +13685,34 @@
         <f>'[1]TERM 1'!Q107</f>
         <v/>
       </c>
-      <c r="R105" s="104" t="str">
+      <c r="R105" s="136" t="str">
         <f>'[1]TERM 1'!R107</f>
         <v/>
       </c>
-      <c r="S105" s="105" t="str">
+      <c r="S105" s="137" t="str">
         <f>'[1]TERM 1'!S107</f>
         <v/>
       </c>
       <c r="T105" s="100"/>
       <c r="U105" s="101"/>
       <c r="V105" s="102"/>
-      <c r="W105" s="104" t="str">
+      <c r="W105" s="136" t="str">
         <f>'[1]TERM 1'!W107</f>
         <v/>
       </c>
-      <c r="X105" s="104" t="str">
+      <c r="X105" s="136" t="str">
         <f>'[1]TERM 1'!X107</f>
         <v/>
       </c>
-      <c r="Y105" s="103" t="str">
+      <c r="Y105" s="135" t="str">
         <f>'[1]TERM 1'!Y107</f>
         <v/>
       </c>
-      <c r="Z105" s="104" t="str">
+      <c r="Z105" s="136" t="str">
         <f>'[1]TERM 1'!Z107</f>
         <v/>
       </c>
-      <c r="AA105" s="104" t="str">
+      <c r="AA105" s="136" t="str">
         <f>'[1]TERM 1'!AA107</f>
         <v/>
       </c>
@@ -13662,11 +13746,11 @@
         <f>'[1]TERM 1'!K108</f>
         <v/>
       </c>
-      <c r="L106" s="104" t="str">
+      <c r="L106" s="136" t="str">
         <f>'[1]TERM 1'!L108</f>
         <v/>
       </c>
-      <c r="M106" s="105" t="str">
+      <c r="M106" s="137" t="str">
         <f>'[1]TERM 1'!M108</f>
         <v/>
       </c>
@@ -13677,34 +13761,34 @@
         <f>'[1]TERM 1'!Q108</f>
         <v/>
       </c>
-      <c r="R106" s="104" t="str">
+      <c r="R106" s="136" t="str">
         <f>'[1]TERM 1'!R108</f>
         <v/>
       </c>
-      <c r="S106" s="105" t="str">
+      <c r="S106" s="137" t="str">
         <f>'[1]TERM 1'!S108</f>
         <v/>
       </c>
       <c r="T106" s="100"/>
       <c r="U106" s="101"/>
       <c r="V106" s="102"/>
-      <c r="W106" s="104" t="str">
+      <c r="W106" s="136" t="str">
         <f>'[1]TERM 1'!W108</f>
         <v/>
       </c>
-      <c r="X106" s="104" t="str">
+      <c r="X106" s="136" t="str">
         <f>'[1]TERM 1'!X108</f>
         <v/>
       </c>
-      <c r="Y106" s="103" t="str">
+      <c r="Y106" s="135" t="str">
         <f>'[1]TERM 1'!Y108</f>
         <v/>
       </c>
-      <c r="Z106" s="104" t="str">
+      <c r="Z106" s="136" t="str">
         <f>'[1]TERM 1'!Z108</f>
         <v/>
       </c>
-      <c r="AA106" s="104" t="str">
+      <c r="AA106" s="136" t="str">
         <f>'[1]TERM 1'!AA108</f>
         <v/>
       </c>
@@ -13738,11 +13822,11 @@
         <f>'[1]TERM 1'!K109</f>
         <v/>
       </c>
-      <c r="L107" s="104" t="str">
+      <c r="L107" s="136" t="str">
         <f>'[1]TERM 1'!L109</f>
         <v/>
       </c>
-      <c r="M107" s="105" t="str">
+      <c r="M107" s="137" t="str">
         <f>'[1]TERM 1'!M109</f>
         <v/>
       </c>
@@ -13753,34 +13837,34 @@
         <f>'[1]TERM 1'!Q109</f>
         <v/>
       </c>
-      <c r="R107" s="104" t="str">
+      <c r="R107" s="136" t="str">
         <f>'[1]TERM 1'!R109</f>
         <v/>
       </c>
-      <c r="S107" s="105" t="str">
+      <c r="S107" s="137" t="str">
         <f>'[1]TERM 1'!S109</f>
         <v/>
       </c>
       <c r="T107" s="100"/>
       <c r="U107" s="101"/>
       <c r="V107" s="102"/>
-      <c r="W107" s="104" t="str">
+      <c r="W107" s="136" t="str">
         <f>'[1]TERM 1'!W109</f>
         <v/>
       </c>
-      <c r="X107" s="104" t="str">
+      <c r="X107" s="136" t="str">
         <f>'[1]TERM 1'!X109</f>
         <v/>
       </c>
-      <c r="Y107" s="103" t="str">
+      <c r="Y107" s="135" t="str">
         <f>'[1]TERM 1'!Y109</f>
         <v/>
       </c>
-      <c r="Z107" s="104" t="str">
+      <c r="Z107" s="136" t="str">
         <f>'[1]TERM 1'!Z109</f>
         <v/>
       </c>
-      <c r="AA107" s="104" t="str">
+      <c r="AA107" s="136" t="str">
         <f>'[1]TERM 1'!AA109</f>
         <v/>
       </c>
@@ -13814,11 +13898,11 @@
         <f>'[1]TERM 1'!K110</f>
         <v/>
       </c>
-      <c r="L108" s="104" t="str">
+      <c r="L108" s="136" t="str">
         <f>'[1]TERM 1'!L110</f>
         <v/>
       </c>
-      <c r="M108" s="105" t="str">
+      <c r="M108" s="137" t="str">
         <f>'[1]TERM 1'!M110</f>
         <v/>
       </c>
@@ -13829,34 +13913,34 @@
         <f>'[1]TERM 1'!Q110</f>
         <v/>
       </c>
-      <c r="R108" s="104" t="str">
+      <c r="R108" s="136" t="str">
         <f>'[1]TERM 1'!R110</f>
         <v/>
       </c>
-      <c r="S108" s="105" t="str">
+      <c r="S108" s="137" t="str">
         <f>'[1]TERM 1'!S110</f>
         <v/>
       </c>
       <c r="T108" s="100"/>
       <c r="U108" s="101"/>
       <c r="V108" s="102"/>
-      <c r="W108" s="104" t="str">
+      <c r="W108" s="136" t="str">
         <f>'[1]TERM 1'!W110</f>
         <v/>
       </c>
-      <c r="X108" s="104" t="str">
+      <c r="X108" s="136" t="str">
         <f>'[1]TERM 1'!X110</f>
         <v/>
       </c>
-      <c r="Y108" s="103" t="str">
+      <c r="Y108" s="135" t="str">
         <f>'[1]TERM 1'!Y110</f>
         <v/>
       </c>
-      <c r="Z108" s="104" t="str">
+      <c r="Z108" s="136" t="str">
         <f>'[1]TERM 1'!Z110</f>
         <v/>
       </c>
-      <c r="AA108" s="104" t="str">
+      <c r="AA108" s="136" t="str">
         <f>'[1]TERM 1'!AA110</f>
         <v/>
       </c>
@@ -13890,11 +13974,11 @@
         <f>'[1]TERM 1'!K111</f>
         <v/>
       </c>
-      <c r="L109" s="104" t="str">
+      <c r="L109" s="136" t="str">
         <f>'[1]TERM 1'!L111</f>
         <v/>
       </c>
-      <c r="M109" s="105" t="str">
+      <c r="M109" s="137" t="str">
         <f>'[1]TERM 1'!M111</f>
         <v/>
       </c>
@@ -13905,34 +13989,34 @@
         <f>'[1]TERM 1'!Q111</f>
         <v/>
       </c>
-      <c r="R109" s="104" t="str">
+      <c r="R109" s="136" t="str">
         <f>'[1]TERM 1'!R111</f>
         <v/>
       </c>
-      <c r="S109" s="105" t="str">
+      <c r="S109" s="137" t="str">
         <f>'[1]TERM 1'!S111</f>
         <v/>
       </c>
       <c r="T109" s="100"/>
       <c r="U109" s="101"/>
       <c r="V109" s="102"/>
-      <c r="W109" s="104" t="str">
+      <c r="W109" s="136" t="str">
         <f>'[1]TERM 1'!W111</f>
         <v/>
       </c>
-      <c r="X109" s="104" t="str">
+      <c r="X109" s="136" t="str">
         <f>'[1]TERM 1'!X111</f>
         <v/>
       </c>
-      <c r="Y109" s="103" t="str">
+      <c r="Y109" s="135" t="str">
         <f>'[1]TERM 1'!Y111</f>
         <v/>
       </c>
-      <c r="Z109" s="104" t="str">
+      <c r="Z109" s="136" t="str">
         <f>'[1]TERM 1'!Z111</f>
         <v/>
       </c>
-      <c r="AA109" s="104" t="str">
+      <c r="AA109" s="136" t="str">
         <f>'[1]TERM 1'!AA111</f>
         <v/>
       </c>
@@ -13966,11 +14050,11 @@
         <f>'[1]TERM 1'!K112</f>
         <v/>
       </c>
-      <c r="L110" s="104" t="str">
+      <c r="L110" s="136" t="str">
         <f>'[1]TERM 1'!L112</f>
         <v/>
       </c>
-      <c r="M110" s="105" t="str">
+      <c r="M110" s="137" t="str">
         <f>'[1]TERM 1'!M112</f>
         <v/>
       </c>
@@ -13981,34 +14065,34 @@
         <f>'[1]TERM 1'!Q112</f>
         <v/>
       </c>
-      <c r="R110" s="104" t="str">
+      <c r="R110" s="136" t="str">
         <f>'[1]TERM 1'!R112</f>
         <v/>
       </c>
-      <c r="S110" s="105" t="str">
+      <c r="S110" s="137" t="str">
         <f>'[1]TERM 1'!S112</f>
         <v/>
       </c>
       <c r="T110" s="100"/>
       <c r="U110" s="101"/>
       <c r="V110" s="102"/>
-      <c r="W110" s="104" t="str">
+      <c r="W110" s="136" t="str">
         <f>'[1]TERM 1'!W112</f>
         <v/>
       </c>
-      <c r="X110" s="104" t="str">
+      <c r="X110" s="136" t="str">
         <f>'[1]TERM 1'!X112</f>
         <v/>
       </c>
-      <c r="Y110" s="103" t="str">
+      <c r="Y110" s="135" t="str">
         <f>'[1]TERM 1'!Y112</f>
         <v/>
       </c>
-      <c r="Z110" s="104" t="str">
+      <c r="Z110" s="136" t="str">
         <f>'[1]TERM 1'!Z112</f>
         <v/>
       </c>
-      <c r="AA110" s="104" t="str">
+      <c r="AA110" s="136" t="str">
         <f>'[1]TERM 1'!AA112</f>
         <v/>
       </c>
@@ -14042,11 +14126,11 @@
         <f>'[1]TERM 1'!K113</f>
         <v/>
       </c>
-      <c r="L111" s="104" t="str">
+      <c r="L111" s="136" t="str">
         <f>'[1]TERM 1'!L113</f>
         <v/>
       </c>
-      <c r="M111" s="105" t="str">
+      <c r="M111" s="137" t="str">
         <f>'[1]TERM 1'!M113</f>
         <v/>
       </c>
@@ -14057,34 +14141,34 @@
         <f>'[1]TERM 1'!Q113</f>
         <v/>
       </c>
-      <c r="R111" s="104" t="str">
+      <c r="R111" s="136" t="str">
         <f>'[1]TERM 1'!R113</f>
         <v/>
       </c>
-      <c r="S111" s="105" t="str">
+      <c r="S111" s="137" t="str">
         <f>'[1]TERM 1'!S113</f>
         <v/>
       </c>
       <c r="T111" s="100"/>
       <c r="U111" s="101"/>
       <c r="V111" s="102"/>
-      <c r="W111" s="104" t="str">
+      <c r="W111" s="136" t="str">
         <f>'[1]TERM 1'!W113</f>
         <v/>
       </c>
-      <c r="X111" s="104" t="str">
+      <c r="X111" s="136" t="str">
         <f>'[1]TERM 1'!X113</f>
         <v/>
       </c>
-      <c r="Y111" s="103" t="str">
+      <c r="Y111" s="135" t="str">
         <f>'[1]TERM 1'!Y113</f>
         <v/>
       </c>
-      <c r="Z111" s="104" t="str">
+      <c r="Z111" s="136" t="str">
         <f>'[1]TERM 1'!Z113</f>
         <v/>
       </c>
-      <c r="AA111" s="104" t="str">
+      <c r="AA111" s="136" t="str">
         <f>'[1]TERM 1'!AA113</f>
         <v/>
       </c>
@@ -14118,11 +14202,11 @@
         <f>'[1]TERM 1'!K114</f>
         <v/>
       </c>
-      <c r="L112" s="104" t="str">
+      <c r="L112" s="136" t="str">
         <f>'[1]TERM 1'!L114</f>
         <v/>
       </c>
-      <c r="M112" s="105" t="str">
+      <c r="M112" s="137" t="str">
         <f>'[1]TERM 1'!M114</f>
         <v/>
       </c>
@@ -14133,34 +14217,34 @@
         <f>'[1]TERM 1'!Q114</f>
         <v/>
       </c>
-      <c r="R112" s="104" t="str">
+      <c r="R112" s="136" t="str">
         <f>'[1]TERM 1'!R114</f>
         <v/>
       </c>
-      <c r="S112" s="105" t="str">
+      <c r="S112" s="137" t="str">
         <f>'[1]TERM 1'!S114</f>
         <v/>
       </c>
       <c r="T112" s="100"/>
       <c r="U112" s="101"/>
       <c r="V112" s="102"/>
-      <c r="W112" s="104" t="str">
+      <c r="W112" s="136" t="str">
         <f>'[1]TERM 1'!W114</f>
         <v/>
       </c>
-      <c r="X112" s="104" t="str">
+      <c r="X112" s="136" t="str">
         <f>'[1]TERM 1'!X114</f>
         <v/>
       </c>
-      <c r="Y112" s="103" t="str">
+      <c r="Y112" s="135" t="str">
         <f>'[1]TERM 1'!Y114</f>
         <v/>
       </c>
-      <c r="Z112" s="104" t="str">
+      <c r="Z112" s="136" t="str">
         <f>'[1]TERM 1'!Z114</f>
         <v/>
       </c>
-      <c r="AA112" s="104" t="str">
+      <c r="AA112" s="136" t="str">
         <f>'[1]TERM 1'!AA114</f>
         <v/>
       </c>
@@ -14194,11 +14278,11 @@
         <f>'[1]TERM 1'!K115</f>
         <v/>
       </c>
-      <c r="L113" s="104" t="str">
+      <c r="L113" s="136" t="str">
         <f>'[1]TERM 1'!L115</f>
         <v/>
       </c>
-      <c r="M113" s="105" t="str">
+      <c r="M113" s="137" t="str">
         <f>'[1]TERM 1'!M115</f>
         <v/>
       </c>
@@ -14209,34 +14293,34 @@
         <f>'[1]TERM 1'!Q115</f>
         <v/>
       </c>
-      <c r="R113" s="104" t="str">
+      <c r="R113" s="136" t="str">
         <f>'[1]TERM 1'!R115</f>
         <v/>
       </c>
-      <c r="S113" s="105" t="str">
+      <c r="S113" s="137" t="str">
         <f>'[1]TERM 1'!S115</f>
         <v/>
       </c>
       <c r="T113" s="100"/>
       <c r="U113" s="101"/>
       <c r="V113" s="102"/>
-      <c r="W113" s="104" t="str">
+      <c r="W113" s="136" t="str">
         <f>'[1]TERM 1'!W115</f>
         <v/>
       </c>
-      <c r="X113" s="104" t="str">
+      <c r="X113" s="136" t="str">
         <f>'[1]TERM 1'!X115</f>
         <v/>
       </c>
-      <c r="Y113" s="103" t="str">
+      <c r="Y113" s="135" t="str">
         <f>'[1]TERM 1'!Y115</f>
         <v/>
       </c>
-      <c r="Z113" s="104" t="str">
+      <c r="Z113" s="136" t="str">
         <f>'[1]TERM 1'!Z115</f>
         <v/>
       </c>
-      <c r="AA113" s="104" t="str">
+      <c r="AA113" s="136" t="str">
         <f>'[1]TERM 1'!AA115</f>
         <v/>
       </c>
@@ -14270,11 +14354,11 @@
         <f>'[1]TERM 1'!K116</f>
         <v/>
       </c>
-      <c r="L114" s="104" t="str">
+      <c r="L114" s="136" t="str">
         <f>'[1]TERM 1'!L116</f>
         <v/>
       </c>
-      <c r="M114" s="105" t="str">
+      <c r="M114" s="137" t="str">
         <f>'[1]TERM 1'!M116</f>
         <v/>
       </c>
@@ -14285,34 +14369,34 @@
         <f>'[1]TERM 1'!Q116</f>
         <v/>
       </c>
-      <c r="R114" s="104" t="str">
+      <c r="R114" s="136" t="str">
         <f>'[1]TERM 1'!R116</f>
         <v/>
       </c>
-      <c r="S114" s="105" t="str">
+      <c r="S114" s="137" t="str">
         <f>'[1]TERM 1'!S116</f>
         <v/>
       </c>
       <c r="T114" s="100"/>
       <c r="U114" s="101"/>
       <c r="V114" s="102"/>
-      <c r="W114" s="104" t="str">
+      <c r="W114" s="136" t="str">
         <f>'[1]TERM 1'!W116</f>
         <v/>
       </c>
-      <c r="X114" s="104" t="str">
+      <c r="X114" s="136" t="str">
         <f>'[1]TERM 1'!X116</f>
         <v/>
       </c>
-      <c r="Y114" s="103" t="str">
+      <c r="Y114" s="135" t="str">
         <f>'[1]TERM 1'!Y116</f>
         <v/>
       </c>
-      <c r="Z114" s="104" t="str">
+      <c r="Z114" s="136" t="str">
         <f>'[1]TERM 1'!Z116</f>
         <v/>
       </c>
-      <c r="AA114" s="104" t="str">
+      <c r="AA114" s="136" t="str">
         <f>'[1]TERM 1'!AA116</f>
         <v/>
       </c>
@@ -14346,11 +14430,11 @@
         <f>'[1]TERM 1'!K117</f>
         <v/>
       </c>
-      <c r="L115" s="104" t="str">
+      <c r="L115" s="136" t="str">
         <f>'[1]TERM 1'!L117</f>
         <v/>
       </c>
-      <c r="M115" s="105" t="str">
+      <c r="M115" s="137" t="str">
         <f>'[1]TERM 1'!M117</f>
         <v/>
       </c>
@@ -14361,34 +14445,34 @@
         <f>'[1]TERM 1'!Q117</f>
         <v/>
       </c>
-      <c r="R115" s="104" t="str">
+      <c r="R115" s="136" t="str">
         <f>'[1]TERM 1'!R117</f>
         <v/>
       </c>
-      <c r="S115" s="105" t="str">
+      <c r="S115" s="137" t="str">
         <f>'[1]TERM 1'!S117</f>
         <v/>
       </c>
       <c r="T115" s="100"/>
       <c r="U115" s="101"/>
       <c r="V115" s="102"/>
-      <c r="W115" s="104" t="str">
+      <c r="W115" s="136" t="str">
         <f>'[1]TERM 1'!W117</f>
         <v/>
       </c>
-      <c r="X115" s="104" t="str">
+      <c r="X115" s="136" t="str">
         <f>'[1]TERM 1'!X117</f>
         <v/>
       </c>
-      <c r="Y115" s="103" t="str">
+      <c r="Y115" s="135" t="str">
         <f>'[1]TERM 1'!Y117</f>
         <v/>
       </c>
-      <c r="Z115" s="104" t="str">
+      <c r="Z115" s="136" t="str">
         <f>'[1]TERM 1'!Z117</f>
         <v/>
       </c>
-      <c r="AA115" s="104" t="str">
+      <c r="AA115" s="136" t="str">
         <f>'[1]TERM 1'!AA117</f>
         <v/>
       </c>
@@ -14422,11 +14506,11 @@
         <f>'[1]TERM 1'!K118</f>
         <v/>
       </c>
-      <c r="L116" s="113" t="str">
+      <c r="L116" s="139" t="str">
         <f>'[1]TERM 1'!L118</f>
         <v/>
       </c>
-      <c r="M116" s="114" t="str">
+      <c r="M116" s="140" t="str">
         <f>'[1]TERM 1'!M118</f>
         <v/>
       </c>
@@ -14437,34 +14521,34 @@
         <f>'[1]TERM 1'!Q118</f>
         <v/>
       </c>
-      <c r="R116" s="113" t="str">
+      <c r="R116" s="139" t="str">
         <f>'[1]TERM 1'!R118</f>
         <v/>
       </c>
-      <c r="S116" s="114" t="str">
+      <c r="S116" s="140" t="str">
         <f>'[1]TERM 1'!S118</f>
         <v/>
       </c>
       <c r="T116" s="109"/>
       <c r="U116" s="110"/>
       <c r="V116" s="111"/>
-      <c r="W116" s="113" t="str">
+      <c r="W116" s="139" t="str">
         <f>'[1]TERM 1'!W118</f>
         <v/>
       </c>
-      <c r="X116" s="113" t="str">
+      <c r="X116" s="139" t="str">
         <f>'[1]TERM 1'!X118</f>
         <v/>
       </c>
-      <c r="Y116" s="112" t="str">
+      <c r="Y116" s="138" t="str">
         <f>'[1]TERM 1'!Y118</f>
         <v/>
       </c>
-      <c r="Z116" s="113" t="str">
+      <c r="Z116" s="139" t="str">
         <f>'[1]TERM 1'!Z118</f>
         <v/>
       </c>
-      <c r="AA116" s="113" t="str">
+      <c r="AA116" s="139" t="str">
         <f>'[1]TERM 1'!AA118</f>
         <v/>
       </c>

--- a/templates/GS official Template.xlsx
+++ b/templates/GS official Template.xlsx
@@ -975,7 +975,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1425,90 +1425,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="5" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="5" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="5" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="5" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6948,11 +6864,11 @@
         <f>'[1]TERM 1'!K18</f>
         <v/>
       </c>
-      <c r="L16" s="121" t="str">
+      <c r="L16" s="44" t="str">
         <f>'[1]TERM 1'!L18</f>
         <v/>
       </c>
-      <c r="M16" s="122" t="str">
+      <c r="M16" s="45" t="str">
         <f>'[1]TERM 1'!M18</f>
         <v/>
       </c>
@@ -6963,34 +6879,34 @@
         <f>'[1]TERM 1'!Q18</f>
         <v/>
       </c>
-      <c r="R16" s="121" t="str">
+      <c r="R16" s="44" t="str">
         <f>'[1]TERM 1'!R18</f>
         <v/>
       </c>
-      <c r="S16" s="123" t="str">
+      <c r="S16" s="47" t="str">
         <f>'[1]TERM 1'!S18</f>
         <v/>
       </c>
       <c r="T16" s="40"/>
       <c r="U16" s="41"/>
       <c r="V16" s="42"/>
-      <c r="W16" s="121" t="str">
+      <c r="W16" s="44" t="str">
         <f>'[1]TERM 1'!W18</f>
         <v/>
       </c>
-      <c r="X16" s="122" t="str">
+      <c r="X16" s="45" t="str">
         <f>'[1]TERM 1'!X18</f>
         <v/>
       </c>
-      <c r="Y16" s="124" t="str">
+      <c r="Y16" s="48" t="str">
         <f>'[1]TERM 1'!Y18</f>
         <v/>
       </c>
-      <c r="Z16" s="121" t="str">
+      <c r="Z16" s="44" t="str">
         <f>'[1]TERM 1'!Z18</f>
         <v/>
       </c>
-      <c r="AA16" s="123" t="str">
+      <c r="AA16" s="47" t="str">
         <f>'[1]TERM 1'!AA18</f>
         <v/>
       </c>
@@ -7024,11 +6940,11 @@
         <f>'[1]TERM 1'!K19</f>
         <v/>
       </c>
-      <c r="L17" s="125" t="str">
+      <c r="L17" s="58" t="str">
         <f>'[1]TERM 1'!L19</f>
         <v/>
       </c>
-      <c r="M17" s="126" t="str">
+      <c r="M17" s="59" t="str">
         <f>'[1]TERM 1'!M19</f>
         <v/>
       </c>
@@ -7039,34 +6955,34 @@
         <f>'[1]TERM 1'!Q19</f>
         <v/>
       </c>
-      <c r="R17" s="125" t="str">
+      <c r="R17" s="58" t="str">
         <f>'[1]TERM 1'!R19</f>
         <v/>
       </c>
-      <c r="S17" s="127" t="str">
+      <c r="S17" s="61" t="str">
         <f>'[1]TERM 1'!S19</f>
         <v/>
       </c>
       <c r="T17" s="62"/>
       <c r="U17" s="55"/>
       <c r="V17" s="56"/>
-      <c r="W17" s="125" t="str">
+      <c r="W17" s="58" t="str">
         <f>'[1]TERM 1'!W19</f>
         <v/>
       </c>
-      <c r="X17" s="126" t="str">
+      <c r="X17" s="59" t="str">
         <f>'[1]TERM 1'!X19</f>
         <v/>
       </c>
-      <c r="Y17" s="128" t="str">
+      <c r="Y17" s="63" t="str">
         <f>'[1]TERM 1'!Y19</f>
         <v/>
       </c>
-      <c r="Z17" s="125" t="str">
+      <c r="Z17" s="58" t="str">
         <f>'[1]TERM 1'!Z19</f>
         <v/>
       </c>
-      <c r="AA17" s="127" t="str">
+      <c r="AA17" s="61" t="str">
         <f>'[1]TERM 1'!AA19</f>
         <v/>
       </c>
@@ -7100,11 +7016,11 @@
         <f>'[1]TERM 1'!K20</f>
         <v/>
       </c>
-      <c r="L18" s="125" t="str">
+      <c r="L18" s="58" t="str">
         <f>'[1]TERM 1'!L20</f>
         <v/>
       </c>
-      <c r="M18" s="126" t="str">
+      <c r="M18" s="59" t="str">
         <f>'[1]TERM 1'!M20</f>
         <v/>
       </c>
@@ -7115,34 +7031,34 @@
         <f>'[1]TERM 1'!Q20</f>
         <v/>
       </c>
-      <c r="R18" s="125" t="str">
+      <c r="R18" s="58" t="str">
         <f>'[1]TERM 1'!R20</f>
         <v/>
       </c>
-      <c r="S18" s="127" t="str">
+      <c r="S18" s="61" t="str">
         <f>'[1]TERM 1'!S20</f>
         <v/>
       </c>
       <c r="T18" s="62"/>
       <c r="U18" s="55"/>
       <c r="V18" s="56"/>
-      <c r="W18" s="125" t="str">
+      <c r="W18" s="58" t="str">
         <f>'[1]TERM 1'!W20</f>
         <v/>
       </c>
-      <c r="X18" s="126" t="str">
+      <c r="X18" s="59" t="str">
         <f>'[1]TERM 1'!X20</f>
         <v/>
       </c>
-      <c r="Y18" s="128" t="str">
+      <c r="Y18" s="63" t="str">
         <f>'[1]TERM 1'!Y20</f>
         <v/>
       </c>
-      <c r="Z18" s="125" t="str">
+      <c r="Z18" s="58" t="str">
         <f>'[1]TERM 1'!Z20</f>
         <v/>
       </c>
-      <c r="AA18" s="127" t="str">
+      <c r="AA18" s="61" t="str">
         <f>'[1]TERM 1'!AA20</f>
         <v/>
       </c>
@@ -7176,11 +7092,11 @@
         <f>'[1]TERM 1'!K21</f>
         <v/>
       </c>
-      <c r="L19" s="125" t="str">
+      <c r="L19" s="58" t="str">
         <f>'[1]TERM 1'!L21</f>
         <v/>
       </c>
-      <c r="M19" s="126" t="str">
+      <c r="M19" s="59" t="str">
         <f>'[1]TERM 1'!M21</f>
         <v/>
       </c>
@@ -7191,34 +7107,34 @@
         <f>'[1]TERM 1'!Q21</f>
         <v/>
       </c>
-      <c r="R19" s="125" t="str">
+      <c r="R19" s="58" t="str">
         <f>'[1]TERM 1'!R21</f>
         <v/>
       </c>
-      <c r="S19" s="127" t="str">
+      <c r="S19" s="61" t="str">
         <f>'[1]TERM 1'!S21</f>
         <v/>
       </c>
       <c r="T19" s="62"/>
       <c r="U19" s="55"/>
       <c r="V19" s="56"/>
-      <c r="W19" s="125" t="str">
+      <c r="W19" s="58" t="str">
         <f>'[1]TERM 1'!W21</f>
         <v/>
       </c>
-      <c r="X19" s="126" t="str">
+      <c r="X19" s="59" t="str">
         <f>'[1]TERM 1'!X21</f>
         <v/>
       </c>
-      <c r="Y19" s="128" t="str">
+      <c r="Y19" s="63" t="str">
         <f>'[1]TERM 1'!Y21</f>
         <v/>
       </c>
-      <c r="Z19" s="125" t="str">
+      <c r="Z19" s="58" t="str">
         <f>'[1]TERM 1'!Z21</f>
         <v/>
       </c>
-      <c r="AA19" s="127" t="str">
+      <c r="AA19" s="61" t="str">
         <f>'[1]TERM 1'!AA21</f>
         <v/>
       </c>
@@ -7252,11 +7168,11 @@
         <f>'[1]TERM 1'!K22</f>
         <v/>
       </c>
-      <c r="L20" s="125" t="str">
+      <c r="L20" s="58" t="str">
         <f>'[1]TERM 1'!L22</f>
         <v/>
       </c>
-      <c r="M20" s="126" t="str">
+      <c r="M20" s="59" t="str">
         <f>'[1]TERM 1'!M22</f>
         <v/>
       </c>
@@ -7267,34 +7183,34 @@
         <f>'[1]TERM 1'!Q22</f>
         <v/>
       </c>
-      <c r="R20" s="125" t="str">
+      <c r="R20" s="58" t="str">
         <f>'[1]TERM 1'!R22</f>
         <v/>
       </c>
-      <c r="S20" s="127" t="str">
+      <c r="S20" s="61" t="str">
         <f>'[1]TERM 1'!S22</f>
         <v/>
       </c>
       <c r="T20" s="62"/>
       <c r="U20" s="55"/>
       <c r="V20" s="56"/>
-      <c r="W20" s="125" t="str">
+      <c r="W20" s="58" t="str">
         <f>'[1]TERM 1'!W22</f>
         <v/>
       </c>
-      <c r="X20" s="126" t="str">
+      <c r="X20" s="59" t="str">
         <f>'[1]TERM 1'!X22</f>
         <v/>
       </c>
-      <c r="Y20" s="128" t="str">
+      <c r="Y20" s="63" t="str">
         <f>'[1]TERM 1'!Y22</f>
         <v/>
       </c>
-      <c r="Z20" s="125" t="str">
+      <c r="Z20" s="58" t="str">
         <f>'[1]TERM 1'!Z22</f>
         <v/>
       </c>
-      <c r="AA20" s="127" t="str">
+      <c r="AA20" s="61" t="str">
         <f>'[1]TERM 1'!AA22</f>
         <v/>
       </c>
@@ -7328,11 +7244,11 @@
         <f>'[1]TERM 1'!K23</f>
         <v/>
       </c>
-      <c r="L21" s="125" t="str">
+      <c r="L21" s="58" t="str">
         <f>'[1]TERM 1'!L23</f>
         <v/>
       </c>
-      <c r="M21" s="126" t="str">
+      <c r="M21" s="59" t="str">
         <f>'[1]TERM 1'!M23</f>
         <v/>
       </c>
@@ -7343,34 +7259,34 @@
         <f>'[1]TERM 1'!Q23</f>
         <v/>
       </c>
-      <c r="R21" s="125" t="str">
+      <c r="R21" s="58" t="str">
         <f>'[1]TERM 1'!R23</f>
         <v/>
       </c>
-      <c r="S21" s="127" t="str">
+      <c r="S21" s="61" t="str">
         <f>'[1]TERM 1'!S23</f>
         <v/>
       </c>
       <c r="T21" s="62"/>
       <c r="U21" s="55"/>
       <c r="V21" s="56"/>
-      <c r="W21" s="125" t="str">
+      <c r="W21" s="58" t="str">
         <f>'[1]TERM 1'!W23</f>
         <v/>
       </c>
-      <c r="X21" s="126" t="str">
+      <c r="X21" s="59" t="str">
         <f>'[1]TERM 1'!X23</f>
         <v/>
       </c>
-      <c r="Y21" s="128" t="str">
+      <c r="Y21" s="63" t="str">
         <f>'[1]TERM 1'!Y23</f>
         <v/>
       </c>
-      <c r="Z21" s="125" t="str">
+      <c r="Z21" s="58" t="str">
         <f>'[1]TERM 1'!Z23</f>
         <v/>
       </c>
-      <c r="AA21" s="127" t="str">
+      <c r="AA21" s="61" t="str">
         <f>'[1]TERM 1'!AA23</f>
         <v/>
       </c>
@@ -7404,11 +7320,11 @@
         <f>'[1]TERM 1'!K24</f>
         <v/>
       </c>
-      <c r="L22" s="125" t="str">
+      <c r="L22" s="58" t="str">
         <f>'[1]TERM 1'!L24</f>
         <v/>
       </c>
-      <c r="M22" s="126" t="str">
+      <c r="M22" s="59" t="str">
         <f>'[1]TERM 1'!M24</f>
         <v/>
       </c>
@@ -7419,34 +7335,34 @@
         <f>'[1]TERM 1'!Q24</f>
         <v/>
       </c>
-      <c r="R22" s="125" t="str">
+      <c r="R22" s="58" t="str">
         <f>'[1]TERM 1'!R24</f>
         <v/>
       </c>
-      <c r="S22" s="127" t="str">
+      <c r="S22" s="61" t="str">
         <f>'[1]TERM 1'!S24</f>
         <v/>
       </c>
       <c r="T22" s="62"/>
       <c r="U22" s="55"/>
       <c r="V22" s="56"/>
-      <c r="W22" s="125" t="str">
+      <c r="W22" s="58" t="str">
         <f>'[1]TERM 1'!W24</f>
         <v/>
       </c>
-      <c r="X22" s="126" t="str">
+      <c r="X22" s="59" t="str">
         <f>'[1]TERM 1'!X24</f>
         <v/>
       </c>
-      <c r="Y22" s="128" t="str">
+      <c r="Y22" s="63" t="str">
         <f>'[1]TERM 1'!Y24</f>
         <v/>
       </c>
-      <c r="Z22" s="125" t="str">
+      <c r="Z22" s="58" t="str">
         <f>'[1]TERM 1'!Z24</f>
         <v/>
       </c>
-      <c r="AA22" s="127" t="str">
+      <c r="AA22" s="61" t="str">
         <f>'[1]TERM 1'!AA24</f>
         <v/>
       </c>
@@ -7480,11 +7396,11 @@
         <f>'[1]TERM 1'!K25</f>
         <v/>
       </c>
-      <c r="L23" s="125" t="str">
+      <c r="L23" s="58" t="str">
         <f>'[1]TERM 1'!L25</f>
         <v/>
       </c>
-      <c r="M23" s="126" t="str">
+      <c r="M23" s="59" t="str">
         <f>'[1]TERM 1'!M25</f>
         <v/>
       </c>
@@ -7495,34 +7411,34 @@
         <f>'[1]TERM 1'!Q25</f>
         <v/>
       </c>
-      <c r="R23" s="125" t="str">
+      <c r="R23" s="58" t="str">
         <f>'[1]TERM 1'!R25</f>
         <v/>
       </c>
-      <c r="S23" s="127" t="str">
+      <c r="S23" s="61" t="str">
         <f>'[1]TERM 1'!S25</f>
         <v/>
       </c>
       <c r="T23" s="62"/>
       <c r="U23" s="55"/>
       <c r="V23" s="56"/>
-      <c r="W23" s="125" t="str">
+      <c r="W23" s="58" t="str">
         <f>'[1]TERM 1'!W25</f>
         <v/>
       </c>
-      <c r="X23" s="126" t="str">
+      <c r="X23" s="59" t="str">
         <f>'[1]TERM 1'!X25</f>
         <v/>
       </c>
-      <c r="Y23" s="128" t="str">
+      <c r="Y23" s="63" t="str">
         <f>'[1]TERM 1'!Y25</f>
         <v/>
       </c>
-      <c r="Z23" s="125" t="str">
+      <c r="Z23" s="58" t="str">
         <f>'[1]TERM 1'!Z25</f>
         <v/>
       </c>
-      <c r="AA23" s="127" t="str">
+      <c r="AA23" s="61" t="str">
         <f>'[1]TERM 1'!AA25</f>
         <v/>
       </c>
@@ -7556,11 +7472,11 @@
         <f>'[1]TERM 1'!K26</f>
         <v/>
       </c>
-      <c r="L24" s="125" t="str">
+      <c r="L24" s="58" t="str">
         <f>'[1]TERM 1'!L26</f>
         <v/>
       </c>
-      <c r="M24" s="126" t="str">
+      <c r="M24" s="59" t="str">
         <f>'[1]TERM 1'!M26</f>
         <v/>
       </c>
@@ -7571,34 +7487,34 @@
         <f>'[1]TERM 1'!Q26</f>
         <v/>
       </c>
-      <c r="R24" s="125" t="str">
+      <c r="R24" s="58" t="str">
         <f>'[1]TERM 1'!R26</f>
         <v/>
       </c>
-      <c r="S24" s="127" t="str">
+      <c r="S24" s="61" t="str">
         <f>'[1]TERM 1'!S26</f>
         <v/>
       </c>
       <c r="T24" s="62"/>
       <c r="U24" s="55"/>
       <c r="V24" s="56"/>
-      <c r="W24" s="125" t="str">
+      <c r="W24" s="58" t="str">
         <f>'[1]TERM 1'!W26</f>
         <v/>
       </c>
-      <c r="X24" s="126" t="str">
+      <c r="X24" s="59" t="str">
         <f>'[1]TERM 1'!X26</f>
         <v/>
       </c>
-      <c r="Y24" s="128" t="str">
+      <c r="Y24" s="63" t="str">
         <f>'[1]TERM 1'!Y26</f>
         <v/>
       </c>
-      <c r="Z24" s="125" t="str">
+      <c r="Z24" s="58" t="str">
         <f>'[1]TERM 1'!Z26</f>
         <v/>
       </c>
-      <c r="AA24" s="127" t="str">
+      <c r="AA24" s="61" t="str">
         <f>'[1]TERM 1'!AA26</f>
         <v/>
       </c>
@@ -7632,11 +7548,11 @@
         <f>'[1]TERM 1'!K27</f>
         <v/>
       </c>
-      <c r="L25" s="125" t="str">
+      <c r="L25" s="58" t="str">
         <f>'[1]TERM 1'!L27</f>
         <v/>
       </c>
-      <c r="M25" s="126" t="str">
+      <c r="M25" s="59" t="str">
         <f>'[1]TERM 1'!M27</f>
         <v/>
       </c>
@@ -7647,34 +7563,34 @@
         <f>'[1]TERM 1'!Q27</f>
         <v/>
       </c>
-      <c r="R25" s="125" t="str">
+      <c r="R25" s="58" t="str">
         <f>'[1]TERM 1'!R27</f>
         <v/>
       </c>
-      <c r="S25" s="127" t="str">
+      <c r="S25" s="61" t="str">
         <f>'[1]TERM 1'!S27</f>
         <v/>
       </c>
       <c r="T25" s="62"/>
       <c r="U25" s="55"/>
       <c r="V25" s="56"/>
-      <c r="W25" s="125" t="str">
+      <c r="W25" s="58" t="str">
         <f>'[1]TERM 1'!W27</f>
         <v/>
       </c>
-      <c r="X25" s="126" t="str">
+      <c r="X25" s="59" t="str">
         <f>'[1]TERM 1'!X27</f>
         <v/>
       </c>
-      <c r="Y25" s="128" t="str">
+      <c r="Y25" s="63" t="str">
         <f>'[1]TERM 1'!Y27</f>
         <v/>
       </c>
-      <c r="Z25" s="125" t="str">
+      <c r="Z25" s="58" t="str">
         <f>'[1]TERM 1'!Z27</f>
         <v/>
       </c>
-      <c r="AA25" s="127" t="str">
+      <c r="AA25" s="61" t="str">
         <f>'[1]TERM 1'!AA27</f>
         <v/>
       </c>
@@ -7708,11 +7624,11 @@
         <f>'[1]TERM 1'!K28</f>
         <v/>
       </c>
-      <c r="L26" s="125" t="str">
+      <c r="L26" s="58" t="str">
         <f>'[1]TERM 1'!L28</f>
         <v/>
       </c>
-      <c r="M26" s="126" t="str">
+      <c r="M26" s="59" t="str">
         <f>'[1]TERM 1'!M28</f>
         <v/>
       </c>
@@ -7723,34 +7639,34 @@
         <f>'[1]TERM 1'!Q28</f>
         <v/>
       </c>
-      <c r="R26" s="125" t="str">
+      <c r="R26" s="58" t="str">
         <f>'[1]TERM 1'!R28</f>
         <v/>
       </c>
-      <c r="S26" s="127" t="str">
+      <c r="S26" s="61" t="str">
         <f>'[1]TERM 1'!S28</f>
         <v/>
       </c>
       <c r="T26" s="62"/>
       <c r="U26" s="55"/>
       <c r="V26" s="56"/>
-      <c r="W26" s="125" t="str">
+      <c r="W26" s="58" t="str">
         <f>'[1]TERM 1'!W28</f>
         <v/>
       </c>
-      <c r="X26" s="126" t="str">
+      <c r="X26" s="59" t="str">
         <f>'[1]TERM 1'!X28</f>
         <v/>
       </c>
-      <c r="Y26" s="128" t="str">
+      <c r="Y26" s="63" t="str">
         <f>'[1]TERM 1'!Y28</f>
         <v/>
       </c>
-      <c r="Z26" s="125" t="str">
+      <c r="Z26" s="58" t="str">
         <f>'[1]TERM 1'!Z28</f>
         <v/>
       </c>
-      <c r="AA26" s="127" t="str">
+      <c r="AA26" s="61" t="str">
         <f>'[1]TERM 1'!AA28</f>
         <v/>
       </c>
@@ -7784,11 +7700,11 @@
         <f>'[1]TERM 1'!K29</f>
         <v/>
       </c>
-      <c r="L27" s="125" t="str">
+      <c r="L27" s="58" t="str">
         <f>'[1]TERM 1'!L29</f>
         <v/>
       </c>
-      <c r="M27" s="126" t="str">
+      <c r="M27" s="59" t="str">
         <f>'[1]TERM 1'!M29</f>
         <v/>
       </c>
@@ -7799,34 +7715,34 @@
         <f>'[1]TERM 1'!Q29</f>
         <v/>
       </c>
-      <c r="R27" s="125" t="str">
+      <c r="R27" s="58" t="str">
         <f>'[1]TERM 1'!R29</f>
         <v/>
       </c>
-      <c r="S27" s="127" t="str">
+      <c r="S27" s="61" t="str">
         <f>'[1]TERM 1'!S29</f>
         <v/>
       </c>
       <c r="T27" s="62"/>
       <c r="U27" s="55"/>
       <c r="V27" s="56"/>
-      <c r="W27" s="125" t="str">
+      <c r="W27" s="58" t="str">
         <f>'[1]TERM 1'!W29</f>
         <v/>
       </c>
-      <c r="X27" s="126" t="str">
+      <c r="X27" s="59" t="str">
         <f>'[1]TERM 1'!X29</f>
         <v/>
       </c>
-      <c r="Y27" s="128" t="str">
+      <c r="Y27" s="63" t="str">
         <f>'[1]TERM 1'!Y29</f>
         <v/>
       </c>
-      <c r="Z27" s="125" t="str">
+      <c r="Z27" s="58" t="str">
         <f>'[1]TERM 1'!Z29</f>
         <v/>
       </c>
-      <c r="AA27" s="127" t="str">
+      <c r="AA27" s="61" t="str">
         <f>'[1]TERM 1'!AA29</f>
         <v/>
       </c>
@@ -7860,11 +7776,11 @@
         <f>'[1]TERM 1'!K30</f>
         <v/>
       </c>
-      <c r="L28" s="125" t="str">
+      <c r="L28" s="58" t="str">
         <f>'[1]TERM 1'!L30</f>
         <v/>
       </c>
-      <c r="M28" s="126" t="str">
+      <c r="M28" s="59" t="str">
         <f>'[1]TERM 1'!M30</f>
         <v/>
       </c>
@@ -7875,34 +7791,34 @@
         <f>'[1]TERM 1'!Q30</f>
         <v/>
       </c>
-      <c r="R28" s="125" t="str">
+      <c r="R28" s="58" t="str">
         <f>'[1]TERM 1'!R30</f>
         <v/>
       </c>
-      <c r="S28" s="127" t="str">
+      <c r="S28" s="61" t="str">
         <f>'[1]TERM 1'!S30</f>
         <v/>
       </c>
       <c r="T28" s="62"/>
       <c r="U28" s="55"/>
       <c r="V28" s="56"/>
-      <c r="W28" s="125" t="str">
+      <c r="W28" s="58" t="str">
         <f>'[1]TERM 1'!W30</f>
         <v/>
       </c>
-      <c r="X28" s="126" t="str">
+      <c r="X28" s="59" t="str">
         <f>'[1]TERM 1'!X30</f>
         <v/>
       </c>
-      <c r="Y28" s="128" t="str">
+      <c r="Y28" s="63" t="str">
         <f>'[1]TERM 1'!Y30</f>
         <v/>
       </c>
-      <c r="Z28" s="125" t="str">
+      <c r="Z28" s="58" t="str">
         <f>'[1]TERM 1'!Z30</f>
         <v/>
       </c>
-      <c r="AA28" s="127" t="str">
+      <c r="AA28" s="61" t="str">
         <f>'[1]TERM 1'!AA30</f>
         <v/>
       </c>
@@ -7936,11 +7852,11 @@
         <f>'[1]TERM 1'!K31</f>
         <v/>
       </c>
-      <c r="L29" s="125" t="str">
+      <c r="L29" s="58" t="str">
         <f>'[1]TERM 1'!L31</f>
         <v/>
       </c>
-      <c r="M29" s="126" t="str">
+      <c r="M29" s="59" t="str">
         <f>'[1]TERM 1'!M31</f>
         <v/>
       </c>
@@ -7951,34 +7867,34 @@
         <f>'[1]TERM 1'!Q31</f>
         <v/>
       </c>
-      <c r="R29" s="125" t="str">
+      <c r="R29" s="58" t="str">
         <f>'[1]TERM 1'!R31</f>
         <v/>
       </c>
-      <c r="S29" s="127" t="str">
+      <c r="S29" s="61" t="str">
         <f>'[1]TERM 1'!S31</f>
         <v/>
       </c>
       <c r="T29" s="62"/>
       <c r="U29" s="55"/>
       <c r="V29" s="56"/>
-      <c r="W29" s="125" t="str">
+      <c r="W29" s="58" t="str">
         <f>'[1]TERM 1'!W31</f>
         <v/>
       </c>
-      <c r="X29" s="126" t="str">
+      <c r="X29" s="59" t="str">
         <f>'[1]TERM 1'!X31</f>
         <v/>
       </c>
-      <c r="Y29" s="128" t="str">
+      <c r="Y29" s="63" t="str">
         <f>'[1]TERM 1'!Y31</f>
         <v/>
       </c>
-      <c r="Z29" s="125" t="str">
+      <c r="Z29" s="58" t="str">
         <f>'[1]TERM 1'!Z31</f>
         <v/>
       </c>
-      <c r="AA29" s="127" t="str">
+      <c r="AA29" s="61" t="str">
         <f>'[1]TERM 1'!AA31</f>
         <v/>
       </c>
@@ -8012,11 +7928,11 @@
         <f>'[1]TERM 1'!K32</f>
         <v/>
       </c>
-      <c r="L30" s="125" t="str">
+      <c r="L30" s="58" t="str">
         <f>'[1]TERM 1'!L32</f>
         <v/>
       </c>
-      <c r="M30" s="126" t="str">
+      <c r="M30" s="59" t="str">
         <f>'[1]TERM 1'!M32</f>
         <v/>
       </c>
@@ -8027,34 +7943,34 @@
         <f>'[1]TERM 1'!Q32</f>
         <v/>
       </c>
-      <c r="R30" s="125" t="str">
+      <c r="R30" s="58" t="str">
         <f>'[1]TERM 1'!R32</f>
         <v/>
       </c>
-      <c r="S30" s="127" t="str">
+      <c r="S30" s="61" t="str">
         <f>'[1]TERM 1'!S32</f>
         <v/>
       </c>
       <c r="T30" s="62"/>
       <c r="U30" s="55"/>
       <c r="V30" s="56"/>
-      <c r="W30" s="125" t="str">
+      <c r="W30" s="58" t="str">
         <f>'[1]TERM 1'!W32</f>
         <v/>
       </c>
-      <c r="X30" s="126" t="str">
+      <c r="X30" s="59" t="str">
         <f>'[1]TERM 1'!X32</f>
         <v/>
       </c>
-      <c r="Y30" s="128" t="str">
+      <c r="Y30" s="63" t="str">
         <f>'[1]TERM 1'!Y32</f>
         <v/>
       </c>
-      <c r="Z30" s="125" t="str">
+      <c r="Z30" s="58" t="str">
         <f>'[1]TERM 1'!Z32</f>
         <v/>
       </c>
-      <c r="AA30" s="127" t="str">
+      <c r="AA30" s="61" t="str">
         <f>'[1]TERM 1'!AA32</f>
         <v/>
       </c>
@@ -8088,11 +8004,11 @@
         <f>'[1]TERM 1'!K33</f>
         <v/>
       </c>
-      <c r="L31" s="125" t="str">
+      <c r="L31" s="58" t="str">
         <f>'[1]TERM 1'!L33</f>
         <v/>
       </c>
-      <c r="M31" s="126" t="str">
+      <c r="M31" s="59" t="str">
         <f>'[1]TERM 1'!M33</f>
         <v/>
       </c>
@@ -8103,34 +8019,34 @@
         <f>'[1]TERM 1'!Q33</f>
         <v/>
       </c>
-      <c r="R31" s="125" t="str">
+      <c r="R31" s="58" t="str">
         <f>'[1]TERM 1'!R33</f>
         <v/>
       </c>
-      <c r="S31" s="127" t="str">
+      <c r="S31" s="61" t="str">
         <f>'[1]TERM 1'!S33</f>
         <v/>
       </c>
       <c r="T31" s="62"/>
       <c r="U31" s="55"/>
       <c r="V31" s="56"/>
-      <c r="W31" s="125" t="str">
+      <c r="W31" s="58" t="str">
         <f>'[1]TERM 1'!W33</f>
         <v/>
       </c>
-      <c r="X31" s="126" t="str">
+      <c r="X31" s="59" t="str">
         <f>'[1]TERM 1'!X33</f>
         <v/>
       </c>
-      <c r="Y31" s="128" t="str">
+      <c r="Y31" s="63" t="str">
         <f>'[1]TERM 1'!Y33</f>
         <v/>
       </c>
-      <c r="Z31" s="125" t="str">
+      <c r="Z31" s="58" t="str">
         <f>'[1]TERM 1'!Z33</f>
         <v/>
       </c>
-      <c r="AA31" s="127" t="str">
+      <c r="AA31" s="61" t="str">
         <f>'[1]TERM 1'!AA33</f>
         <v/>
       </c>
@@ -8164,11 +8080,11 @@
         <f>'[1]TERM 1'!K34</f>
         <v/>
       </c>
-      <c r="L32" s="125" t="str">
+      <c r="L32" s="58" t="str">
         <f>'[1]TERM 1'!L34</f>
         <v/>
       </c>
-      <c r="M32" s="126" t="str">
+      <c r="M32" s="59" t="str">
         <f>'[1]TERM 1'!M34</f>
         <v/>
       </c>
@@ -8179,34 +8095,34 @@
         <f>'[1]TERM 1'!Q34</f>
         <v/>
       </c>
-      <c r="R32" s="125" t="str">
+      <c r="R32" s="58" t="str">
         <f>'[1]TERM 1'!R34</f>
         <v/>
       </c>
-      <c r="S32" s="127" t="str">
+      <c r="S32" s="61" t="str">
         <f>'[1]TERM 1'!S34</f>
         <v/>
       </c>
       <c r="T32" s="62"/>
       <c r="U32" s="55"/>
       <c r="V32" s="56"/>
-      <c r="W32" s="125" t="str">
+      <c r="W32" s="58" t="str">
         <f>'[1]TERM 1'!W34</f>
         <v/>
       </c>
-      <c r="X32" s="126" t="str">
+      <c r="X32" s="59" t="str">
         <f>'[1]TERM 1'!X34</f>
         <v/>
       </c>
-      <c r="Y32" s="128" t="str">
+      <c r="Y32" s="63" t="str">
         <f>'[1]TERM 1'!Y34</f>
         <v/>
       </c>
-      <c r="Z32" s="125" t="str">
+      <c r="Z32" s="58" t="str">
         <f>'[1]TERM 1'!Z34</f>
         <v/>
       </c>
-      <c r="AA32" s="127" t="str">
+      <c r="AA32" s="61" t="str">
         <f>'[1]TERM 1'!AA34</f>
         <v/>
       </c>
@@ -8240,11 +8156,11 @@
         <f>'[1]TERM 1'!K35</f>
         <v/>
       </c>
-      <c r="L33" s="125" t="str">
+      <c r="L33" s="58" t="str">
         <f>'[1]TERM 1'!L35</f>
         <v/>
       </c>
-      <c r="M33" s="126" t="str">
+      <c r="M33" s="59" t="str">
         <f>'[1]TERM 1'!M35</f>
         <v/>
       </c>
@@ -8255,34 +8171,34 @@
         <f>'[1]TERM 1'!Q35</f>
         <v/>
       </c>
-      <c r="R33" s="125" t="str">
+      <c r="R33" s="58" t="str">
         <f>'[1]TERM 1'!R35</f>
         <v/>
       </c>
-      <c r="S33" s="127" t="str">
+      <c r="S33" s="61" t="str">
         <f>'[1]TERM 1'!S35</f>
         <v/>
       </c>
       <c r="T33" s="62"/>
       <c r="U33" s="55"/>
       <c r="V33" s="56"/>
-      <c r="W33" s="125" t="str">
+      <c r="W33" s="58" t="str">
         <f>'[1]TERM 1'!W35</f>
         <v/>
       </c>
-      <c r="X33" s="126" t="str">
+      <c r="X33" s="59" t="str">
         <f>'[1]TERM 1'!X35</f>
         <v/>
       </c>
-      <c r="Y33" s="128" t="str">
+      <c r="Y33" s="63" t="str">
         <f>'[1]TERM 1'!Y35</f>
         <v/>
       </c>
-      <c r="Z33" s="125" t="str">
+      <c r="Z33" s="58" t="str">
         <f>'[1]TERM 1'!Z35</f>
         <v/>
       </c>
-      <c r="AA33" s="127" t="str">
+      <c r="AA33" s="61" t="str">
         <f>'[1]TERM 1'!AA35</f>
         <v/>
       </c>
@@ -8316,11 +8232,11 @@
         <f>'[1]TERM 1'!K36</f>
         <v/>
       </c>
-      <c r="L34" s="125" t="str">
+      <c r="L34" s="58" t="str">
         <f>'[1]TERM 1'!L36</f>
         <v/>
       </c>
-      <c r="M34" s="126" t="str">
+      <c r="M34" s="59" t="str">
         <f>'[1]TERM 1'!M36</f>
         <v/>
       </c>
@@ -8331,34 +8247,34 @@
         <f>'[1]TERM 1'!Q36</f>
         <v/>
       </c>
-      <c r="R34" s="125" t="str">
+      <c r="R34" s="58" t="str">
         <f>'[1]TERM 1'!R36</f>
         <v/>
       </c>
-      <c r="S34" s="127" t="str">
+      <c r="S34" s="61" t="str">
         <f>'[1]TERM 1'!S36</f>
         <v/>
       </c>
       <c r="T34" s="62"/>
       <c r="U34" s="55"/>
       <c r="V34" s="56"/>
-      <c r="W34" s="125" t="str">
+      <c r="W34" s="58" t="str">
         <f>'[1]TERM 1'!W36</f>
         <v/>
       </c>
-      <c r="X34" s="126" t="str">
+      <c r="X34" s="59" t="str">
         <f>'[1]TERM 1'!X36</f>
         <v/>
       </c>
-      <c r="Y34" s="128" t="str">
+      <c r="Y34" s="63" t="str">
         <f>'[1]TERM 1'!Y36</f>
         <v/>
       </c>
-      <c r="Z34" s="125" t="str">
+      <c r="Z34" s="58" t="str">
         <f>'[1]TERM 1'!Z36</f>
         <v/>
       </c>
-      <c r="AA34" s="127" t="str">
+      <c r="AA34" s="61" t="str">
         <f>'[1]TERM 1'!AA36</f>
         <v/>
       </c>
@@ -8392,11 +8308,11 @@
         <f>'[1]TERM 1'!K37</f>
         <v/>
       </c>
-      <c r="L35" s="125" t="str">
+      <c r="L35" s="58" t="str">
         <f>'[1]TERM 1'!L37</f>
         <v/>
       </c>
-      <c r="M35" s="126" t="str">
+      <c r="M35" s="59" t="str">
         <f>'[1]TERM 1'!M37</f>
         <v/>
       </c>
@@ -8407,34 +8323,34 @@
         <f>'[1]TERM 1'!Q37</f>
         <v/>
       </c>
-      <c r="R35" s="125" t="str">
+      <c r="R35" s="58" t="str">
         <f>'[1]TERM 1'!R37</f>
         <v/>
       </c>
-      <c r="S35" s="127" t="str">
+      <c r="S35" s="61" t="str">
         <f>'[1]TERM 1'!S37</f>
         <v/>
       </c>
       <c r="T35" s="62"/>
       <c r="U35" s="55"/>
       <c r="V35" s="56"/>
-      <c r="W35" s="125" t="str">
+      <c r="W35" s="58" t="str">
         <f>'[1]TERM 1'!W37</f>
         <v/>
       </c>
-      <c r="X35" s="126" t="str">
+      <c r="X35" s="59" t="str">
         <f>'[1]TERM 1'!X37</f>
         <v/>
       </c>
-      <c r="Y35" s="128" t="str">
+      <c r="Y35" s="63" t="str">
         <f>'[1]TERM 1'!Y37</f>
         <v/>
       </c>
-      <c r="Z35" s="125" t="str">
+      <c r="Z35" s="58" t="str">
         <f>'[1]TERM 1'!Z37</f>
         <v/>
       </c>
-      <c r="AA35" s="127" t="str">
+      <c r="AA35" s="61" t="str">
         <f>'[1]TERM 1'!AA37</f>
         <v/>
       </c>
@@ -8468,11 +8384,11 @@
         <f>'[1]TERM 1'!K38</f>
         <v/>
       </c>
-      <c r="L36" s="125" t="str">
+      <c r="L36" s="58" t="str">
         <f>'[1]TERM 1'!L38</f>
         <v/>
       </c>
-      <c r="M36" s="126" t="str">
+      <c r="M36" s="59" t="str">
         <f>'[1]TERM 1'!M38</f>
         <v/>
       </c>
@@ -8483,34 +8399,34 @@
         <f>'[1]TERM 1'!Q38</f>
         <v/>
       </c>
-      <c r="R36" s="125" t="str">
+      <c r="R36" s="58" t="str">
         <f>'[1]TERM 1'!R38</f>
         <v/>
       </c>
-      <c r="S36" s="127" t="str">
+      <c r="S36" s="61" t="str">
         <f>'[1]TERM 1'!S38</f>
         <v/>
       </c>
       <c r="T36" s="62"/>
       <c r="U36" s="55"/>
       <c r="V36" s="56"/>
-      <c r="W36" s="125" t="str">
+      <c r="W36" s="58" t="str">
         <f>'[1]TERM 1'!W38</f>
         <v/>
       </c>
-      <c r="X36" s="126" t="str">
+      <c r="X36" s="59" t="str">
         <f>'[1]TERM 1'!X38</f>
         <v/>
       </c>
-      <c r="Y36" s="128" t="str">
+      <c r="Y36" s="63" t="str">
         <f>'[1]TERM 1'!Y38</f>
         <v/>
       </c>
-      <c r="Z36" s="125" t="str">
+      <c r="Z36" s="58" t="str">
         <f>'[1]TERM 1'!Z38</f>
         <v/>
       </c>
-      <c r="AA36" s="127" t="str">
+      <c r="AA36" s="61" t="str">
         <f>'[1]TERM 1'!AA38</f>
         <v/>
       </c>
@@ -8544,11 +8460,11 @@
         <f>'[1]TERM 1'!K39</f>
         <v/>
       </c>
-      <c r="L37" s="125" t="str">
+      <c r="L37" s="58" t="str">
         <f>'[1]TERM 1'!L39</f>
         <v/>
       </c>
-      <c r="M37" s="126" t="str">
+      <c r="M37" s="59" t="str">
         <f>'[1]TERM 1'!M39</f>
         <v/>
       </c>
@@ -8559,34 +8475,34 @@
         <f>'[1]TERM 1'!Q39</f>
         <v/>
       </c>
-      <c r="R37" s="125" t="str">
+      <c r="R37" s="58" t="str">
         <f>'[1]TERM 1'!R39</f>
         <v/>
       </c>
-      <c r="S37" s="127" t="str">
+      <c r="S37" s="61" t="str">
         <f>'[1]TERM 1'!S39</f>
         <v/>
       </c>
       <c r="T37" s="62"/>
       <c r="U37" s="55"/>
       <c r="V37" s="56"/>
-      <c r="W37" s="125" t="str">
+      <c r="W37" s="58" t="str">
         <f>'[1]TERM 1'!W39</f>
         <v/>
       </c>
-      <c r="X37" s="126" t="str">
+      <c r="X37" s="59" t="str">
         <f>'[1]TERM 1'!X39</f>
         <v/>
       </c>
-      <c r="Y37" s="128" t="str">
+      <c r="Y37" s="63" t="str">
         <f>'[1]TERM 1'!Y39</f>
         <v/>
       </c>
-      <c r="Z37" s="125" t="str">
+      <c r="Z37" s="58" t="str">
         <f>'[1]TERM 1'!Z39</f>
         <v/>
       </c>
-      <c r="AA37" s="127" t="str">
+      <c r="AA37" s="61" t="str">
         <f>'[1]TERM 1'!AA39</f>
         <v/>
       </c>
@@ -8620,11 +8536,11 @@
         <f>'[1]TERM 1'!K40</f>
         <v/>
       </c>
-      <c r="L38" s="125" t="str">
+      <c r="L38" s="58" t="str">
         <f>'[1]TERM 1'!L40</f>
         <v/>
       </c>
-      <c r="M38" s="126" t="str">
+      <c r="M38" s="59" t="str">
         <f>'[1]TERM 1'!M40</f>
         <v/>
       </c>
@@ -8635,34 +8551,34 @@
         <f>'[1]TERM 1'!Q40</f>
         <v/>
       </c>
-      <c r="R38" s="125" t="str">
+      <c r="R38" s="58" t="str">
         <f>'[1]TERM 1'!R40</f>
         <v/>
       </c>
-      <c r="S38" s="127" t="str">
+      <c r="S38" s="61" t="str">
         <f>'[1]TERM 1'!S40</f>
         <v/>
       </c>
       <c r="T38" s="62"/>
       <c r="U38" s="55"/>
       <c r="V38" s="56"/>
-      <c r="W38" s="125" t="str">
+      <c r="W38" s="58" t="str">
         <f>'[1]TERM 1'!W40</f>
         <v/>
       </c>
-      <c r="X38" s="126" t="str">
+      <c r="X38" s="59" t="str">
         <f>'[1]TERM 1'!X40</f>
         <v/>
       </c>
-      <c r="Y38" s="128" t="str">
+      <c r="Y38" s="63" t="str">
         <f>'[1]TERM 1'!Y40</f>
         <v/>
       </c>
-      <c r="Z38" s="125" t="str">
+      <c r="Z38" s="58" t="str">
         <f>'[1]TERM 1'!Z40</f>
         <v/>
       </c>
-      <c r="AA38" s="127" t="str">
+      <c r="AA38" s="61" t="str">
         <f>'[1]TERM 1'!AA40</f>
         <v/>
       </c>
@@ -8696,11 +8612,11 @@
         <f>'[1]TERM 1'!K41</f>
         <v/>
       </c>
-      <c r="L39" s="125" t="str">
+      <c r="L39" s="58" t="str">
         <f>'[1]TERM 1'!L41</f>
         <v/>
       </c>
-      <c r="M39" s="126" t="str">
+      <c r="M39" s="59" t="str">
         <f>'[1]TERM 1'!M41</f>
         <v/>
       </c>
@@ -8711,34 +8627,34 @@
         <f>'[1]TERM 1'!Q41</f>
         <v/>
       </c>
-      <c r="R39" s="125" t="str">
+      <c r="R39" s="58" t="str">
         <f>'[1]TERM 1'!R41</f>
         <v/>
       </c>
-      <c r="S39" s="127" t="str">
+      <c r="S39" s="61" t="str">
         <f>'[1]TERM 1'!S41</f>
         <v/>
       </c>
       <c r="T39" s="62"/>
       <c r="U39" s="55"/>
       <c r="V39" s="56"/>
-      <c r="W39" s="125" t="str">
+      <c r="W39" s="58" t="str">
         <f>'[1]TERM 1'!W41</f>
         <v/>
       </c>
-      <c r="X39" s="126" t="str">
+      <c r="X39" s="59" t="str">
         <f>'[1]TERM 1'!X41</f>
         <v/>
       </c>
-      <c r="Y39" s="128" t="str">
+      <c r="Y39" s="63" t="str">
         <f>'[1]TERM 1'!Y41</f>
         <v/>
       </c>
-      <c r="Z39" s="125" t="str">
+      <c r="Z39" s="58" t="str">
         <f>'[1]TERM 1'!Z41</f>
         <v/>
       </c>
-      <c r="AA39" s="127" t="str">
+      <c r="AA39" s="61" t="str">
         <f>'[1]TERM 1'!AA41</f>
         <v/>
       </c>
@@ -8772,11 +8688,11 @@
         <f>'[1]TERM 1'!K42</f>
         <v/>
       </c>
-      <c r="L40" s="125" t="str">
+      <c r="L40" s="58" t="str">
         <f>'[1]TERM 1'!L42</f>
         <v/>
       </c>
-      <c r="M40" s="126" t="str">
+      <c r="M40" s="59" t="str">
         <f>'[1]TERM 1'!M42</f>
         <v/>
       </c>
@@ -8787,34 +8703,34 @@
         <f>'[1]TERM 1'!Q42</f>
         <v/>
       </c>
-      <c r="R40" s="125" t="str">
+      <c r="R40" s="58" t="str">
         <f>'[1]TERM 1'!R42</f>
         <v/>
       </c>
-      <c r="S40" s="127" t="str">
+      <c r="S40" s="61" t="str">
         <f>'[1]TERM 1'!S42</f>
         <v/>
       </c>
       <c r="T40" s="62"/>
       <c r="U40" s="55"/>
       <c r="V40" s="56"/>
-      <c r="W40" s="125" t="str">
+      <c r="W40" s="58" t="str">
         <f>'[1]TERM 1'!W42</f>
         <v/>
       </c>
-      <c r="X40" s="126" t="str">
+      <c r="X40" s="59" t="str">
         <f>'[1]TERM 1'!X42</f>
         <v/>
       </c>
-      <c r="Y40" s="128" t="str">
+      <c r="Y40" s="63" t="str">
         <f>'[1]TERM 1'!Y42</f>
         <v/>
       </c>
-      <c r="Z40" s="125" t="str">
+      <c r="Z40" s="58" t="str">
         <f>'[1]TERM 1'!Z42</f>
         <v/>
       </c>
-      <c r="AA40" s="127" t="str">
+      <c r="AA40" s="61" t="str">
         <f>'[1]TERM 1'!AA42</f>
         <v/>
       </c>
@@ -8848,11 +8764,11 @@
         <f>'[1]TERM 1'!K43</f>
         <v/>
       </c>
-      <c r="L41" s="125" t="str">
+      <c r="L41" s="58" t="str">
         <f>'[1]TERM 1'!L43</f>
         <v/>
       </c>
-      <c r="M41" s="126" t="str">
+      <c r="M41" s="59" t="str">
         <f>'[1]TERM 1'!M43</f>
         <v/>
       </c>
@@ -8863,34 +8779,34 @@
         <f>'[1]TERM 1'!Q43</f>
         <v/>
       </c>
-      <c r="R41" s="125" t="str">
+      <c r="R41" s="58" t="str">
         <f>'[1]TERM 1'!R43</f>
         <v/>
       </c>
-      <c r="S41" s="127" t="str">
+      <c r="S41" s="61" t="str">
         <f>'[1]TERM 1'!S43</f>
         <v/>
       </c>
       <c r="T41" s="62"/>
       <c r="U41" s="55"/>
       <c r="V41" s="56"/>
-      <c r="W41" s="125" t="str">
+      <c r="W41" s="58" t="str">
         <f>'[1]TERM 1'!W43</f>
         <v/>
       </c>
-      <c r="X41" s="126" t="str">
+      <c r="X41" s="59" t="str">
         <f>'[1]TERM 1'!X43</f>
         <v/>
       </c>
-      <c r="Y41" s="128" t="str">
+      <c r="Y41" s="63" t="str">
         <f>'[1]TERM 1'!Y43</f>
         <v/>
       </c>
-      <c r="Z41" s="125" t="str">
+      <c r="Z41" s="58" t="str">
         <f>'[1]TERM 1'!Z43</f>
         <v/>
       </c>
-      <c r="AA41" s="127" t="str">
+      <c r="AA41" s="61" t="str">
         <f>'[1]TERM 1'!AA43</f>
         <v/>
       </c>
@@ -8924,11 +8840,11 @@
         <f>'[1]TERM 1'!K44</f>
         <v/>
       </c>
-      <c r="L42" s="125" t="str">
+      <c r="L42" s="58" t="str">
         <f>'[1]TERM 1'!L44</f>
         <v/>
       </c>
-      <c r="M42" s="126" t="str">
+      <c r="M42" s="59" t="str">
         <f>'[1]TERM 1'!M44</f>
         <v/>
       </c>
@@ -8939,34 +8855,34 @@
         <f>'[1]TERM 1'!Q44</f>
         <v/>
       </c>
-      <c r="R42" s="125" t="str">
+      <c r="R42" s="58" t="str">
         <f>'[1]TERM 1'!R44</f>
         <v/>
       </c>
-      <c r="S42" s="127" t="str">
+      <c r="S42" s="61" t="str">
         <f>'[1]TERM 1'!S44</f>
         <v/>
       </c>
       <c r="T42" s="62"/>
       <c r="U42" s="55"/>
       <c r="V42" s="56"/>
-      <c r="W42" s="125" t="str">
+      <c r="W42" s="58" t="str">
         <f>'[1]TERM 1'!W44</f>
         <v/>
       </c>
-      <c r="X42" s="126" t="str">
+      <c r="X42" s="59" t="str">
         <f>'[1]TERM 1'!X44</f>
         <v/>
       </c>
-      <c r="Y42" s="128" t="str">
+      <c r="Y42" s="63" t="str">
         <f>'[1]TERM 1'!Y44</f>
         <v/>
       </c>
-      <c r="Z42" s="125" t="str">
+      <c r="Z42" s="58" t="str">
         <f>'[1]TERM 1'!Z44</f>
         <v/>
       </c>
-      <c r="AA42" s="127" t="str">
+      <c r="AA42" s="61" t="str">
         <f>'[1]TERM 1'!AA44</f>
         <v/>
       </c>
@@ -9000,11 +8916,11 @@
         <f>'[1]TERM 1'!K45</f>
         <v/>
       </c>
-      <c r="L43" s="125" t="str">
+      <c r="L43" s="58" t="str">
         <f>'[1]TERM 1'!L45</f>
         <v/>
       </c>
-      <c r="M43" s="126" t="str">
+      <c r="M43" s="59" t="str">
         <f>'[1]TERM 1'!M45</f>
         <v/>
       </c>
@@ -9015,34 +8931,34 @@
         <f>'[1]TERM 1'!Q45</f>
         <v/>
       </c>
-      <c r="R43" s="125" t="str">
+      <c r="R43" s="58" t="str">
         <f>'[1]TERM 1'!R45</f>
         <v/>
       </c>
-      <c r="S43" s="127" t="str">
+      <c r="S43" s="61" t="str">
         <f>'[1]TERM 1'!S45</f>
         <v/>
       </c>
       <c r="T43" s="62"/>
       <c r="U43" s="55"/>
       <c r="V43" s="56"/>
-      <c r="W43" s="125" t="str">
+      <c r="W43" s="58" t="str">
         <f>'[1]TERM 1'!W45</f>
         <v/>
       </c>
-      <c r="X43" s="126" t="str">
+      <c r="X43" s="59" t="str">
         <f>'[1]TERM 1'!X45</f>
         <v/>
       </c>
-      <c r="Y43" s="128" t="str">
+      <c r="Y43" s="63" t="str">
         <f>'[1]TERM 1'!Y45</f>
         <v/>
       </c>
-      <c r="Z43" s="125" t="str">
+      <c r="Z43" s="58" t="str">
         <f>'[1]TERM 1'!Z45</f>
         <v/>
       </c>
-      <c r="AA43" s="127" t="str">
+      <c r="AA43" s="61" t="str">
         <f>'[1]TERM 1'!AA45</f>
         <v/>
       </c>
@@ -9076,11 +8992,11 @@
         <f>'[1]TERM 1'!K46</f>
         <v/>
       </c>
-      <c r="L44" s="125" t="str">
+      <c r="L44" s="58" t="str">
         <f>'[1]TERM 1'!L46</f>
         <v/>
       </c>
-      <c r="M44" s="126" t="str">
+      <c r="M44" s="59" t="str">
         <f>'[1]TERM 1'!M46</f>
         <v/>
       </c>
@@ -9091,34 +9007,34 @@
         <f>'[1]TERM 1'!Q46</f>
         <v/>
       </c>
-      <c r="R44" s="125" t="str">
+      <c r="R44" s="58" t="str">
         <f>'[1]TERM 1'!R46</f>
         <v/>
       </c>
-      <c r="S44" s="127" t="str">
+      <c r="S44" s="61" t="str">
         <f>'[1]TERM 1'!S46</f>
         <v/>
       </c>
       <c r="T44" s="62"/>
       <c r="U44" s="55"/>
       <c r="V44" s="56"/>
-      <c r="W44" s="125" t="str">
+      <c r="W44" s="58" t="str">
         <f>'[1]TERM 1'!W46</f>
         <v/>
       </c>
-      <c r="X44" s="126" t="str">
+      <c r="X44" s="59" t="str">
         <f>'[1]TERM 1'!X46</f>
         <v/>
       </c>
-      <c r="Y44" s="128" t="str">
+      <c r="Y44" s="63" t="str">
         <f>'[1]TERM 1'!Y46</f>
         <v/>
       </c>
-      <c r="Z44" s="125" t="str">
+      <c r="Z44" s="58" t="str">
         <f>'[1]TERM 1'!Z46</f>
         <v/>
       </c>
-      <c r="AA44" s="127" t="str">
+      <c r="AA44" s="61" t="str">
         <f>'[1]TERM 1'!AA46</f>
         <v/>
       </c>
@@ -9152,11 +9068,11 @@
         <f>'[1]TERM 1'!K47</f>
         <v/>
       </c>
-      <c r="L45" s="125" t="str">
+      <c r="L45" s="58" t="str">
         <f>'[1]TERM 1'!L47</f>
         <v/>
       </c>
-      <c r="M45" s="126" t="str">
+      <c r="M45" s="59" t="str">
         <f>'[1]TERM 1'!M47</f>
         <v/>
       </c>
@@ -9167,34 +9083,34 @@
         <f>'[1]TERM 1'!Q47</f>
         <v/>
       </c>
-      <c r="R45" s="125" t="str">
+      <c r="R45" s="58" t="str">
         <f>'[1]TERM 1'!R47</f>
         <v/>
       </c>
-      <c r="S45" s="127" t="str">
+      <c r="S45" s="61" t="str">
         <f>'[1]TERM 1'!S47</f>
         <v/>
       </c>
       <c r="T45" s="62"/>
       <c r="U45" s="55"/>
       <c r="V45" s="56"/>
-      <c r="W45" s="125" t="str">
+      <c r="W45" s="58" t="str">
         <f>'[1]TERM 1'!W47</f>
         <v/>
       </c>
-      <c r="X45" s="126" t="str">
+      <c r="X45" s="59" t="str">
         <f>'[1]TERM 1'!X47</f>
         <v/>
       </c>
-      <c r="Y45" s="128" t="str">
+      <c r="Y45" s="63" t="str">
         <f>'[1]TERM 1'!Y47</f>
         <v/>
       </c>
-      <c r="Z45" s="125" t="str">
+      <c r="Z45" s="58" t="str">
         <f>'[1]TERM 1'!Z47</f>
         <v/>
       </c>
-      <c r="AA45" s="127" t="str">
+      <c r="AA45" s="61" t="str">
         <f>'[1]TERM 1'!AA47</f>
         <v/>
       </c>
@@ -9228,11 +9144,11 @@
         <f>'[1]TERM 1'!K48</f>
         <v/>
       </c>
-      <c r="L46" s="125" t="str">
+      <c r="L46" s="58" t="str">
         <f>'[1]TERM 1'!L48</f>
         <v/>
       </c>
-      <c r="M46" s="126" t="str">
+      <c r="M46" s="59" t="str">
         <f>'[1]TERM 1'!M48</f>
         <v/>
       </c>
@@ -9243,34 +9159,34 @@
         <f>'[1]TERM 1'!Q48</f>
         <v/>
       </c>
-      <c r="R46" s="125" t="str">
+      <c r="R46" s="58" t="str">
         <f>'[1]TERM 1'!R48</f>
         <v/>
       </c>
-      <c r="S46" s="127" t="str">
+      <c r="S46" s="61" t="str">
         <f>'[1]TERM 1'!S48</f>
         <v/>
       </c>
       <c r="T46" s="62"/>
       <c r="U46" s="55"/>
       <c r="V46" s="56"/>
-      <c r="W46" s="125" t="str">
+      <c r="W46" s="58" t="str">
         <f>'[1]TERM 1'!W48</f>
         <v/>
       </c>
-      <c r="X46" s="126" t="str">
+      <c r="X46" s="59" t="str">
         <f>'[1]TERM 1'!X48</f>
         <v/>
       </c>
-      <c r="Y46" s="128" t="str">
+      <c r="Y46" s="63" t="str">
         <f>'[1]TERM 1'!Y48</f>
         <v/>
       </c>
-      <c r="Z46" s="125" t="str">
+      <c r="Z46" s="58" t="str">
         <f>'[1]TERM 1'!Z48</f>
         <v/>
       </c>
-      <c r="AA46" s="127" t="str">
+      <c r="AA46" s="61" t="str">
         <f>'[1]TERM 1'!AA48</f>
         <v/>
       </c>
@@ -9304,11 +9220,11 @@
         <f>'[1]TERM 1'!K49</f>
         <v/>
       </c>
-      <c r="L47" s="125" t="str">
+      <c r="L47" s="58" t="str">
         <f>'[1]TERM 1'!L49</f>
         <v/>
       </c>
-      <c r="M47" s="126" t="str">
+      <c r="M47" s="59" t="str">
         <f>'[1]TERM 1'!M49</f>
         <v/>
       </c>
@@ -9319,34 +9235,34 @@
         <f>'[1]TERM 1'!Q49</f>
         <v/>
       </c>
-      <c r="R47" s="125" t="str">
+      <c r="R47" s="58" t="str">
         <f>'[1]TERM 1'!R49</f>
         <v/>
       </c>
-      <c r="S47" s="127" t="str">
+      <c r="S47" s="61" t="str">
         <f>'[1]TERM 1'!S49</f>
         <v/>
       </c>
       <c r="T47" s="62"/>
       <c r="U47" s="55"/>
       <c r="V47" s="56"/>
-      <c r="W47" s="125" t="str">
+      <c r="W47" s="58" t="str">
         <f>'[1]TERM 1'!W49</f>
         <v/>
       </c>
-      <c r="X47" s="126" t="str">
+      <c r="X47" s="59" t="str">
         <f>'[1]TERM 1'!X49</f>
         <v/>
       </c>
-      <c r="Y47" s="128" t="str">
+      <c r="Y47" s="63" t="str">
         <f>'[1]TERM 1'!Y49</f>
         <v/>
       </c>
-      <c r="Z47" s="125" t="str">
+      <c r="Z47" s="58" t="str">
         <f>'[1]TERM 1'!Z49</f>
         <v/>
       </c>
-      <c r="AA47" s="127" t="str">
+      <c r="AA47" s="61" t="str">
         <f>'[1]TERM 1'!AA49</f>
         <v/>
       </c>
@@ -9380,11 +9296,11 @@
         <f>'[1]TERM 1'!K50</f>
         <v/>
       </c>
-      <c r="L48" s="125" t="str">
+      <c r="L48" s="58" t="str">
         <f>'[1]TERM 1'!L50</f>
         <v/>
       </c>
-      <c r="M48" s="126" t="str">
+      <c r="M48" s="59" t="str">
         <f>'[1]TERM 1'!M50</f>
         <v/>
       </c>
@@ -9395,34 +9311,34 @@
         <f>'[1]TERM 1'!Q50</f>
         <v/>
       </c>
-      <c r="R48" s="125" t="str">
+      <c r="R48" s="58" t="str">
         <f>'[1]TERM 1'!R50</f>
         <v/>
       </c>
-      <c r="S48" s="127" t="str">
+      <c r="S48" s="61" t="str">
         <f>'[1]TERM 1'!S50</f>
         <v/>
       </c>
       <c r="T48" s="62"/>
       <c r="U48" s="55"/>
       <c r="V48" s="56"/>
-      <c r="W48" s="125" t="str">
+      <c r="W48" s="58" t="str">
         <f>'[1]TERM 1'!W50</f>
         <v/>
       </c>
-      <c r="X48" s="126" t="str">
+      <c r="X48" s="59" t="str">
         <f>'[1]TERM 1'!X50</f>
         <v/>
       </c>
-      <c r="Y48" s="128" t="str">
+      <c r="Y48" s="63" t="str">
         <f>'[1]TERM 1'!Y50</f>
         <v/>
       </c>
-      <c r="Z48" s="125" t="str">
+      <c r="Z48" s="58" t="str">
         <f>'[1]TERM 1'!Z50</f>
         <v/>
       </c>
-      <c r="AA48" s="127" t="str">
+      <c r="AA48" s="61" t="str">
         <f>'[1]TERM 1'!AA50</f>
         <v/>
       </c>
@@ -9456,11 +9372,11 @@
         <f>'[1]TERM 1'!K51</f>
         <v/>
       </c>
-      <c r="L49" s="125" t="str">
+      <c r="L49" s="58" t="str">
         <f>'[1]TERM 1'!L51</f>
         <v/>
       </c>
-      <c r="M49" s="126" t="str">
+      <c r="M49" s="59" t="str">
         <f>'[1]TERM 1'!M51</f>
         <v/>
       </c>
@@ -9471,34 +9387,34 @@
         <f>'[1]TERM 1'!Q51</f>
         <v/>
       </c>
-      <c r="R49" s="125" t="str">
+      <c r="R49" s="58" t="str">
         <f>'[1]TERM 1'!R51</f>
         <v/>
       </c>
-      <c r="S49" s="127" t="str">
+      <c r="S49" s="61" t="str">
         <f>'[1]TERM 1'!S51</f>
         <v/>
       </c>
       <c r="T49" s="62"/>
       <c r="U49" s="55"/>
       <c r="V49" s="56"/>
-      <c r="W49" s="125" t="str">
+      <c r="W49" s="58" t="str">
         <f>'[1]TERM 1'!W51</f>
         <v/>
       </c>
-      <c r="X49" s="126" t="str">
+      <c r="X49" s="59" t="str">
         <f>'[1]TERM 1'!X51</f>
         <v/>
       </c>
-      <c r="Y49" s="128" t="str">
+      <c r="Y49" s="63" t="str">
         <f>'[1]TERM 1'!Y51</f>
         <v/>
       </c>
-      <c r="Z49" s="125" t="str">
+      <c r="Z49" s="58" t="str">
         <f>'[1]TERM 1'!Z51</f>
         <v/>
       </c>
-      <c r="AA49" s="127" t="str">
+      <c r="AA49" s="61" t="str">
         <f>'[1]TERM 1'!AA51</f>
         <v/>
       </c>
@@ -9532,11 +9448,11 @@
         <f>'[1]TERM 1'!K52</f>
         <v/>
       </c>
-      <c r="L50" s="125" t="str">
+      <c r="L50" s="58" t="str">
         <f>'[1]TERM 1'!L52</f>
         <v/>
       </c>
-      <c r="M50" s="126" t="str">
+      <c r="M50" s="59" t="str">
         <f>'[1]TERM 1'!M52</f>
         <v/>
       </c>
@@ -9547,34 +9463,34 @@
         <f>'[1]TERM 1'!Q52</f>
         <v/>
       </c>
-      <c r="R50" s="125" t="str">
+      <c r="R50" s="58" t="str">
         <f>'[1]TERM 1'!R52</f>
         <v/>
       </c>
-      <c r="S50" s="127" t="str">
+      <c r="S50" s="61" t="str">
         <f>'[1]TERM 1'!S52</f>
         <v/>
       </c>
       <c r="T50" s="62"/>
       <c r="U50" s="55"/>
       <c r="V50" s="56"/>
-      <c r="W50" s="125" t="str">
+      <c r="W50" s="58" t="str">
         <f>'[1]TERM 1'!W52</f>
         <v/>
       </c>
-      <c r="X50" s="126" t="str">
+      <c r="X50" s="59" t="str">
         <f>'[1]TERM 1'!X52</f>
         <v/>
       </c>
-      <c r="Y50" s="128" t="str">
+      <c r="Y50" s="63" t="str">
         <f>'[1]TERM 1'!Y52</f>
         <v/>
       </c>
-      <c r="Z50" s="125" t="str">
+      <c r="Z50" s="58" t="str">
         <f>'[1]TERM 1'!Z52</f>
         <v/>
       </c>
-      <c r="AA50" s="127" t="str">
+      <c r="AA50" s="61" t="str">
         <f>'[1]TERM 1'!AA52</f>
         <v/>
       </c>
@@ -9608,11 +9524,11 @@
         <f>'[1]TERM 1'!K53</f>
         <v/>
       </c>
-      <c r="L51" s="125" t="str">
+      <c r="L51" s="58" t="str">
         <f>'[1]TERM 1'!L53</f>
         <v/>
       </c>
-      <c r="M51" s="126" t="str">
+      <c r="M51" s="59" t="str">
         <f>'[1]TERM 1'!M53</f>
         <v/>
       </c>
@@ -9623,34 +9539,34 @@
         <f>'[1]TERM 1'!Q53</f>
         <v/>
       </c>
-      <c r="R51" s="125" t="str">
+      <c r="R51" s="58" t="str">
         <f>'[1]TERM 1'!R53</f>
         <v/>
       </c>
-      <c r="S51" s="127" t="str">
+      <c r="S51" s="61" t="str">
         <f>'[1]TERM 1'!S53</f>
         <v/>
       </c>
       <c r="T51" s="62"/>
       <c r="U51" s="55"/>
       <c r="V51" s="56"/>
-      <c r="W51" s="125" t="str">
+      <c r="W51" s="58" t="str">
         <f>'[1]TERM 1'!W53</f>
         <v/>
       </c>
-      <c r="X51" s="126" t="str">
+      <c r="X51" s="59" t="str">
         <f>'[1]TERM 1'!X53</f>
         <v/>
       </c>
-      <c r="Y51" s="128" t="str">
+      <c r="Y51" s="63" t="str">
         <f>'[1]TERM 1'!Y53</f>
         <v/>
       </c>
-      <c r="Z51" s="125" t="str">
+      <c r="Z51" s="58" t="str">
         <f>'[1]TERM 1'!Z53</f>
         <v/>
       </c>
-      <c r="AA51" s="127" t="str">
+      <c r="AA51" s="61" t="str">
         <f>'[1]TERM 1'!AA53</f>
         <v/>
       </c>
@@ -9684,11 +9600,11 @@
         <f>'[1]TERM 1'!K54</f>
         <v/>
       </c>
-      <c r="L52" s="125" t="str">
+      <c r="L52" s="58" t="str">
         <f>'[1]TERM 1'!L54</f>
         <v/>
       </c>
-      <c r="M52" s="126" t="str">
+      <c r="M52" s="59" t="str">
         <f>'[1]TERM 1'!M54</f>
         <v/>
       </c>
@@ -9699,34 +9615,34 @@
         <f>'[1]TERM 1'!Q54</f>
         <v/>
       </c>
-      <c r="R52" s="125" t="str">
+      <c r="R52" s="58" t="str">
         <f>'[1]TERM 1'!R54</f>
         <v/>
       </c>
-      <c r="S52" s="127" t="str">
+      <c r="S52" s="61" t="str">
         <f>'[1]TERM 1'!S54</f>
         <v/>
       </c>
       <c r="T52" s="62"/>
       <c r="U52" s="55"/>
       <c r="V52" s="56"/>
-      <c r="W52" s="125" t="str">
+      <c r="W52" s="58" t="str">
         <f>'[1]TERM 1'!W54</f>
         <v/>
       </c>
-      <c r="X52" s="126" t="str">
+      <c r="X52" s="59" t="str">
         <f>'[1]TERM 1'!X54</f>
         <v/>
       </c>
-      <c r="Y52" s="128" t="str">
+      <c r="Y52" s="63" t="str">
         <f>'[1]TERM 1'!Y54</f>
         <v/>
       </c>
-      <c r="Z52" s="125" t="str">
+      <c r="Z52" s="58" t="str">
         <f>'[1]TERM 1'!Z54</f>
         <v/>
       </c>
-      <c r="AA52" s="127" t="str">
+      <c r="AA52" s="61" t="str">
         <f>'[1]TERM 1'!AA54</f>
         <v/>
       </c>
@@ -9760,11 +9676,11 @@
         <f>'[1]TERM 1'!K55</f>
         <v/>
       </c>
-      <c r="L53" s="125" t="str">
+      <c r="L53" s="58" t="str">
         <f>'[1]TERM 1'!L55</f>
         <v/>
       </c>
-      <c r="M53" s="126" t="str">
+      <c r="M53" s="59" t="str">
         <f>'[1]TERM 1'!M55</f>
         <v/>
       </c>
@@ -9775,34 +9691,34 @@
         <f>'[1]TERM 1'!Q55</f>
         <v/>
       </c>
-      <c r="R53" s="125" t="str">
+      <c r="R53" s="58" t="str">
         <f>'[1]TERM 1'!R55</f>
         <v/>
       </c>
-      <c r="S53" s="127" t="str">
+      <c r="S53" s="61" t="str">
         <f>'[1]TERM 1'!S55</f>
         <v/>
       </c>
       <c r="T53" s="62"/>
       <c r="U53" s="55"/>
       <c r="V53" s="56"/>
-      <c r="W53" s="125" t="str">
+      <c r="W53" s="58" t="str">
         <f>'[1]TERM 1'!W55</f>
         <v/>
       </c>
-      <c r="X53" s="126" t="str">
+      <c r="X53" s="59" t="str">
         <f>'[1]TERM 1'!X55</f>
         <v/>
       </c>
-      <c r="Y53" s="128" t="str">
+      <c r="Y53" s="63" t="str">
         <f>'[1]TERM 1'!Y55</f>
         <v/>
       </c>
-      <c r="Z53" s="125" t="str">
+      <c r="Z53" s="58" t="str">
         <f>'[1]TERM 1'!Z55</f>
         <v/>
       </c>
-      <c r="AA53" s="127" t="str">
+      <c r="AA53" s="61" t="str">
         <f>'[1]TERM 1'!AA55</f>
         <v/>
       </c>
@@ -9836,11 +9752,11 @@
         <f>'[1]TERM 1'!K56</f>
         <v/>
       </c>
-      <c r="L54" s="125" t="str">
+      <c r="L54" s="58" t="str">
         <f>'[1]TERM 1'!L56</f>
         <v/>
       </c>
-      <c r="M54" s="126" t="str">
+      <c r="M54" s="59" t="str">
         <f>'[1]TERM 1'!M56</f>
         <v/>
       </c>
@@ -9851,34 +9767,34 @@
         <f>'[1]TERM 1'!Q56</f>
         <v/>
       </c>
-      <c r="R54" s="125" t="str">
+      <c r="R54" s="58" t="str">
         <f>'[1]TERM 1'!R56</f>
         <v/>
       </c>
-      <c r="S54" s="127" t="str">
+      <c r="S54" s="61" t="str">
         <f>'[1]TERM 1'!S56</f>
         <v/>
       </c>
       <c r="T54" s="62"/>
       <c r="U54" s="55"/>
       <c r="V54" s="56"/>
-      <c r="W54" s="125" t="str">
+      <c r="W54" s="58" t="str">
         <f>'[1]TERM 1'!W56</f>
         <v/>
       </c>
-      <c r="X54" s="126" t="str">
+      <c r="X54" s="59" t="str">
         <f>'[1]TERM 1'!X56</f>
         <v/>
       </c>
-      <c r="Y54" s="128" t="str">
+      <c r="Y54" s="63" t="str">
         <f>'[1]TERM 1'!Y56</f>
         <v/>
       </c>
-      <c r="Z54" s="125" t="str">
+      <c r="Z54" s="58" t="str">
         <f>'[1]TERM 1'!Z56</f>
         <v/>
       </c>
-      <c r="AA54" s="127" t="str">
+      <c r="AA54" s="61" t="str">
         <f>'[1]TERM 1'!AA56</f>
         <v/>
       </c>
@@ -9912,11 +9828,11 @@
         <f>'[1]TERM 1'!K57</f>
         <v/>
       </c>
-      <c r="L55" s="125" t="str">
+      <c r="L55" s="58" t="str">
         <f>'[1]TERM 1'!L57</f>
         <v/>
       </c>
-      <c r="M55" s="126" t="str">
+      <c r="M55" s="59" t="str">
         <f>'[1]TERM 1'!M57</f>
         <v/>
       </c>
@@ -9927,34 +9843,34 @@
         <f>'[1]TERM 1'!Q57</f>
         <v/>
       </c>
-      <c r="R55" s="125" t="str">
+      <c r="R55" s="58" t="str">
         <f>'[1]TERM 1'!R57</f>
         <v/>
       </c>
-      <c r="S55" s="127" t="str">
+      <c r="S55" s="61" t="str">
         <f>'[1]TERM 1'!S57</f>
         <v/>
       </c>
       <c r="T55" s="62"/>
       <c r="U55" s="55"/>
       <c r="V55" s="56"/>
-      <c r="W55" s="125" t="str">
+      <c r="W55" s="58" t="str">
         <f>'[1]TERM 1'!W57</f>
         <v/>
       </c>
-      <c r="X55" s="126" t="str">
+      <c r="X55" s="59" t="str">
         <f>'[1]TERM 1'!X57</f>
         <v/>
       </c>
-      <c r="Y55" s="128" t="str">
+      <c r="Y55" s="63" t="str">
         <f>'[1]TERM 1'!Y57</f>
         <v/>
       </c>
-      <c r="Z55" s="125" t="str">
+      <c r="Z55" s="58" t="str">
         <f>'[1]TERM 1'!Z57</f>
         <v/>
       </c>
-      <c r="AA55" s="127" t="str">
+      <c r="AA55" s="61" t="str">
         <f>'[1]TERM 1'!AA57</f>
         <v/>
       </c>
@@ -9988,11 +9904,11 @@
         <f>'[1]TERM 1'!K58</f>
         <v/>
       </c>
-      <c r="L56" s="125" t="str">
+      <c r="L56" s="58" t="str">
         <f>'[1]TERM 1'!L58</f>
         <v/>
       </c>
-      <c r="M56" s="126" t="str">
+      <c r="M56" s="59" t="str">
         <f>'[1]TERM 1'!M58</f>
         <v/>
       </c>
@@ -10003,34 +9919,34 @@
         <f>'[1]TERM 1'!Q58</f>
         <v/>
       </c>
-      <c r="R56" s="125" t="str">
+      <c r="R56" s="58" t="str">
         <f>'[1]TERM 1'!R58</f>
         <v/>
       </c>
-      <c r="S56" s="127" t="str">
+      <c r="S56" s="61" t="str">
         <f>'[1]TERM 1'!S58</f>
         <v/>
       </c>
       <c r="T56" s="62"/>
       <c r="U56" s="55"/>
       <c r="V56" s="56"/>
-      <c r="W56" s="125" t="str">
+      <c r="W56" s="58" t="str">
         <f>'[1]TERM 1'!W58</f>
         <v/>
       </c>
-      <c r="X56" s="126" t="str">
+      <c r="X56" s="59" t="str">
         <f>'[1]TERM 1'!X58</f>
         <v/>
       </c>
-      <c r="Y56" s="128" t="str">
+      <c r="Y56" s="63" t="str">
         <f>'[1]TERM 1'!Y58</f>
         <v/>
       </c>
-      <c r="Z56" s="125" t="str">
+      <c r="Z56" s="58" t="str">
         <f>'[1]TERM 1'!Z58</f>
         <v/>
       </c>
-      <c r="AA56" s="127" t="str">
+      <c r="AA56" s="61" t="str">
         <f>'[1]TERM 1'!AA58</f>
         <v/>
       </c>
@@ -10064,11 +9980,11 @@
         <f>'[1]TERM 1'!K59</f>
         <v/>
       </c>
-      <c r="L57" s="125" t="str">
+      <c r="L57" s="58" t="str">
         <f>'[1]TERM 1'!L59</f>
         <v/>
       </c>
-      <c r="M57" s="126" t="str">
+      <c r="M57" s="59" t="str">
         <f>'[1]TERM 1'!M59</f>
         <v/>
       </c>
@@ -10079,34 +9995,34 @@
         <f>'[1]TERM 1'!Q59</f>
         <v/>
       </c>
-      <c r="R57" s="125" t="str">
+      <c r="R57" s="58" t="str">
         <f>'[1]TERM 1'!R59</f>
         <v/>
       </c>
-      <c r="S57" s="127" t="str">
+      <c r="S57" s="61" t="str">
         <f>'[1]TERM 1'!S59</f>
         <v/>
       </c>
       <c r="T57" s="62"/>
       <c r="U57" s="55"/>
       <c r="V57" s="56"/>
-      <c r="W57" s="125" t="str">
+      <c r="W57" s="58" t="str">
         <f>'[1]TERM 1'!W59</f>
         <v/>
       </c>
-      <c r="X57" s="126" t="str">
+      <c r="X57" s="59" t="str">
         <f>'[1]TERM 1'!X59</f>
         <v/>
       </c>
-      <c r="Y57" s="128" t="str">
+      <c r="Y57" s="63" t="str">
         <f>'[1]TERM 1'!Y59</f>
         <v/>
       </c>
-      <c r="Z57" s="125" t="str">
+      <c r="Z57" s="58" t="str">
         <f>'[1]TERM 1'!Z59</f>
         <v/>
       </c>
-      <c r="AA57" s="127" t="str">
+      <c r="AA57" s="61" t="str">
         <f>'[1]TERM 1'!AA59</f>
         <v/>
       </c>
@@ -10140,11 +10056,11 @@
         <f>'[1]TERM 1'!K60</f>
         <v/>
       </c>
-      <c r="L58" s="125" t="str">
+      <c r="L58" s="58" t="str">
         <f>'[1]TERM 1'!L60</f>
         <v/>
       </c>
-      <c r="M58" s="126" t="str">
+      <c r="M58" s="59" t="str">
         <f>'[1]TERM 1'!M60</f>
         <v/>
       </c>
@@ -10155,34 +10071,34 @@
         <f>'[1]TERM 1'!Q60</f>
         <v/>
       </c>
-      <c r="R58" s="125" t="str">
+      <c r="R58" s="58" t="str">
         <f>'[1]TERM 1'!R60</f>
         <v/>
       </c>
-      <c r="S58" s="127" t="str">
+      <c r="S58" s="61" t="str">
         <f>'[1]TERM 1'!S60</f>
         <v/>
       </c>
       <c r="T58" s="62"/>
       <c r="U58" s="55"/>
       <c r="V58" s="56"/>
-      <c r="W58" s="125" t="str">
+      <c r="W58" s="58" t="str">
         <f>'[1]TERM 1'!W60</f>
         <v/>
       </c>
-      <c r="X58" s="126" t="str">
+      <c r="X58" s="59" t="str">
         <f>'[1]TERM 1'!X60</f>
         <v/>
       </c>
-      <c r="Y58" s="128" t="str">
+      <c r="Y58" s="63" t="str">
         <f>'[1]TERM 1'!Y60</f>
         <v/>
       </c>
-      <c r="Z58" s="125" t="str">
+      <c r="Z58" s="58" t="str">
         <f>'[1]TERM 1'!Z60</f>
         <v/>
       </c>
-      <c r="AA58" s="127" t="str">
+      <c r="AA58" s="61" t="str">
         <f>'[1]TERM 1'!AA60</f>
         <v/>
       </c>
@@ -10216,11 +10132,11 @@
         <f>'[1]TERM 1'!K61</f>
         <v/>
       </c>
-      <c r="L59" s="125" t="str">
+      <c r="L59" s="58" t="str">
         <f>'[1]TERM 1'!L61</f>
         <v/>
       </c>
-      <c r="M59" s="126" t="str">
+      <c r="M59" s="59" t="str">
         <f>'[1]TERM 1'!M61</f>
         <v/>
       </c>
@@ -10231,34 +10147,34 @@
         <f>'[1]TERM 1'!Q61</f>
         <v/>
       </c>
-      <c r="R59" s="125" t="str">
+      <c r="R59" s="58" t="str">
         <f>'[1]TERM 1'!R61</f>
         <v/>
       </c>
-      <c r="S59" s="127" t="str">
+      <c r="S59" s="61" t="str">
         <f>'[1]TERM 1'!S61</f>
         <v/>
       </c>
       <c r="T59" s="62"/>
       <c r="U59" s="55"/>
       <c r="V59" s="56"/>
-      <c r="W59" s="125" t="str">
+      <c r="W59" s="58" t="str">
         <f>'[1]TERM 1'!W61</f>
         <v/>
       </c>
-      <c r="X59" s="126" t="str">
+      <c r="X59" s="59" t="str">
         <f>'[1]TERM 1'!X61</f>
         <v/>
       </c>
-      <c r="Y59" s="128" t="str">
+      <c r="Y59" s="63" t="str">
         <f>'[1]TERM 1'!Y61</f>
         <v/>
       </c>
-      <c r="Z59" s="125" t="str">
+      <c r="Z59" s="58" t="str">
         <f>'[1]TERM 1'!Z61</f>
         <v/>
       </c>
-      <c r="AA59" s="127" t="str">
+      <c r="AA59" s="61" t="str">
         <f>'[1]TERM 1'!AA61</f>
         <v/>
       </c>
@@ -10292,11 +10208,11 @@
         <f>'[1]TERM 1'!K62</f>
         <v/>
       </c>
-      <c r="L60" s="125" t="str">
+      <c r="L60" s="58" t="str">
         <f>'[1]TERM 1'!L62</f>
         <v/>
       </c>
-      <c r="M60" s="126" t="str">
+      <c r="M60" s="59" t="str">
         <f>'[1]TERM 1'!M62</f>
         <v/>
       </c>
@@ -10307,34 +10223,34 @@
         <f>'[1]TERM 1'!Q62</f>
         <v/>
       </c>
-      <c r="R60" s="125" t="str">
+      <c r="R60" s="58" t="str">
         <f>'[1]TERM 1'!R62</f>
         <v/>
       </c>
-      <c r="S60" s="127" t="str">
+      <c r="S60" s="61" t="str">
         <f>'[1]TERM 1'!S62</f>
         <v/>
       </c>
       <c r="T60" s="62"/>
       <c r="U60" s="55"/>
       <c r="V60" s="56"/>
-      <c r="W60" s="125" t="str">
+      <c r="W60" s="58" t="str">
         <f>'[1]TERM 1'!W62</f>
         <v/>
       </c>
-      <c r="X60" s="126" t="str">
+      <c r="X60" s="59" t="str">
         <f>'[1]TERM 1'!X62</f>
         <v/>
       </c>
-      <c r="Y60" s="128" t="str">
+      <c r="Y60" s="63" t="str">
         <f>'[1]TERM 1'!Y62</f>
         <v/>
       </c>
-      <c r="Z60" s="125" t="str">
+      <c r="Z60" s="58" t="str">
         <f>'[1]TERM 1'!Z62</f>
         <v/>
       </c>
-      <c r="AA60" s="127" t="str">
+      <c r="AA60" s="61" t="str">
         <f>'[1]TERM 1'!AA62</f>
         <v/>
       </c>
@@ -10368,11 +10284,11 @@
         <f>'[1]TERM 1'!K63</f>
         <v/>
       </c>
-      <c r="L61" s="125" t="str">
+      <c r="L61" s="58" t="str">
         <f>'[1]TERM 1'!L63</f>
         <v/>
       </c>
-      <c r="M61" s="126" t="str">
+      <c r="M61" s="59" t="str">
         <f>'[1]TERM 1'!M63</f>
         <v/>
       </c>
@@ -10383,34 +10299,34 @@
         <f>'[1]TERM 1'!Q63</f>
         <v/>
       </c>
-      <c r="R61" s="125" t="str">
+      <c r="R61" s="58" t="str">
         <f>'[1]TERM 1'!R63</f>
         <v/>
       </c>
-      <c r="S61" s="127" t="str">
+      <c r="S61" s="61" t="str">
         <f>'[1]TERM 1'!S63</f>
         <v/>
       </c>
       <c r="T61" s="62"/>
       <c r="U61" s="55"/>
       <c r="V61" s="56"/>
-      <c r="W61" s="125" t="str">
+      <c r="W61" s="58" t="str">
         <f>'[1]TERM 1'!W63</f>
         <v/>
       </c>
-      <c r="X61" s="126" t="str">
+      <c r="X61" s="59" t="str">
         <f>'[1]TERM 1'!X63</f>
         <v/>
       </c>
-      <c r="Y61" s="128" t="str">
+      <c r="Y61" s="63" t="str">
         <f>'[1]TERM 1'!Y63</f>
         <v/>
       </c>
-      <c r="Z61" s="125" t="str">
+      <c r="Z61" s="58" t="str">
         <f>'[1]TERM 1'!Z63</f>
         <v/>
       </c>
-      <c r="AA61" s="127" t="str">
+      <c r="AA61" s="61" t="str">
         <f>'[1]TERM 1'!AA63</f>
         <v/>
       </c>
@@ -10444,11 +10360,11 @@
         <f>'[1]TERM 1'!K64</f>
         <v/>
       </c>
-      <c r="L62" s="125" t="str">
+      <c r="L62" s="58" t="str">
         <f>'[1]TERM 1'!L64</f>
         <v/>
       </c>
-      <c r="M62" s="126" t="str">
+      <c r="M62" s="59" t="str">
         <f>'[1]TERM 1'!M64</f>
         <v/>
       </c>
@@ -10459,34 +10375,34 @@
         <f>'[1]TERM 1'!Q64</f>
         <v/>
       </c>
-      <c r="R62" s="125" t="str">
+      <c r="R62" s="58" t="str">
         <f>'[1]TERM 1'!R64</f>
         <v/>
       </c>
-      <c r="S62" s="127" t="str">
+      <c r="S62" s="61" t="str">
         <f>'[1]TERM 1'!S64</f>
         <v/>
       </c>
       <c r="T62" s="62"/>
       <c r="U62" s="55"/>
       <c r="V62" s="56"/>
-      <c r="W62" s="125" t="str">
+      <c r="W62" s="58" t="str">
         <f>'[1]TERM 1'!W64</f>
         <v/>
       </c>
-      <c r="X62" s="126" t="str">
+      <c r="X62" s="59" t="str">
         <f>'[1]TERM 1'!X64</f>
         <v/>
       </c>
-      <c r="Y62" s="128" t="str">
+      <c r="Y62" s="63" t="str">
         <f>'[1]TERM 1'!Y64</f>
         <v/>
       </c>
-      <c r="Z62" s="125" t="str">
+      <c r="Z62" s="58" t="str">
         <f>'[1]TERM 1'!Z64</f>
         <v/>
       </c>
-      <c r="AA62" s="127" t="str">
+      <c r="AA62" s="61" t="str">
         <f>'[1]TERM 1'!AA64</f>
         <v/>
       </c>
@@ -10520,11 +10436,11 @@
         <f>'[1]TERM 1'!K65</f>
         <v/>
       </c>
-      <c r="L63" s="125" t="str">
+      <c r="L63" s="58" t="str">
         <f>'[1]TERM 1'!L65</f>
         <v/>
       </c>
-      <c r="M63" s="126" t="str">
+      <c r="M63" s="59" t="str">
         <f>'[1]TERM 1'!M65</f>
         <v/>
       </c>
@@ -10535,34 +10451,34 @@
         <f>'[1]TERM 1'!Q65</f>
         <v/>
       </c>
-      <c r="R63" s="125" t="str">
+      <c r="R63" s="58" t="str">
         <f>'[1]TERM 1'!R65</f>
         <v/>
       </c>
-      <c r="S63" s="127" t="str">
+      <c r="S63" s="61" t="str">
         <f>'[1]TERM 1'!S65</f>
         <v/>
       </c>
       <c r="T63" s="62"/>
       <c r="U63" s="55"/>
       <c r="V63" s="56"/>
-      <c r="W63" s="125" t="str">
+      <c r="W63" s="58" t="str">
         <f>'[1]TERM 1'!W65</f>
         <v/>
       </c>
-      <c r="X63" s="126" t="str">
+      <c r="X63" s="59" t="str">
         <f>'[1]TERM 1'!X65</f>
         <v/>
       </c>
-      <c r="Y63" s="128" t="str">
+      <c r="Y63" s="63" t="str">
         <f>'[1]TERM 1'!Y65</f>
         <v/>
       </c>
-      <c r="Z63" s="125" t="str">
+      <c r="Z63" s="58" t="str">
         <f>'[1]TERM 1'!Z65</f>
         <v/>
       </c>
-      <c r="AA63" s="127" t="str">
+      <c r="AA63" s="61" t="str">
         <f>'[1]TERM 1'!AA65</f>
         <v/>
       </c>
@@ -10596,11 +10512,11 @@
         <f>'[1]TERM 1'!K66</f>
         <v/>
       </c>
-      <c r="L64" s="125" t="str">
+      <c r="L64" s="58" t="str">
         <f>'[1]TERM 1'!L66</f>
         <v/>
       </c>
-      <c r="M64" s="126" t="str">
+      <c r="M64" s="59" t="str">
         <f>'[1]TERM 1'!M66</f>
         <v/>
       </c>
@@ -10611,34 +10527,34 @@
         <f>'[1]TERM 1'!Q66</f>
         <v/>
       </c>
-      <c r="R64" s="125" t="str">
+      <c r="R64" s="58" t="str">
         <f>'[1]TERM 1'!R66</f>
         <v/>
       </c>
-      <c r="S64" s="127" t="str">
+      <c r="S64" s="61" t="str">
         <f>'[1]TERM 1'!S66</f>
         <v/>
       </c>
       <c r="T64" s="62"/>
       <c r="U64" s="55"/>
       <c r="V64" s="56"/>
-      <c r="W64" s="125" t="str">
+      <c r="W64" s="58" t="str">
         <f>'[1]TERM 1'!W66</f>
         <v/>
       </c>
-      <c r="X64" s="126" t="str">
+      <c r="X64" s="59" t="str">
         <f>'[1]TERM 1'!X66</f>
         <v/>
       </c>
-      <c r="Y64" s="128" t="str">
+      <c r="Y64" s="63" t="str">
         <f>'[1]TERM 1'!Y66</f>
         <v/>
       </c>
-      <c r="Z64" s="125" t="str">
+      <c r="Z64" s="58" t="str">
         <f>'[1]TERM 1'!Z66</f>
         <v/>
       </c>
-      <c r="AA64" s="127" t="str">
+      <c r="AA64" s="61" t="str">
         <f>'[1]TERM 1'!AA66</f>
         <v/>
       </c>
@@ -10672,11 +10588,11 @@
         <f>'[1]TERM 1'!K67</f>
         <v/>
       </c>
-      <c r="L65" s="125" t="str">
+      <c r="L65" s="58" t="str">
         <f>'[1]TERM 1'!L67</f>
         <v/>
       </c>
-      <c r="M65" s="126" t="str">
+      <c r="M65" s="59" t="str">
         <f>'[1]TERM 1'!M67</f>
         <v/>
       </c>
@@ -10687,34 +10603,34 @@
         <f>'[1]TERM 1'!Q67</f>
         <v/>
       </c>
-      <c r="R65" s="125" t="str">
+      <c r="R65" s="58" t="str">
         <f>'[1]TERM 1'!R67</f>
         <v/>
       </c>
-      <c r="S65" s="127" t="str">
+      <c r="S65" s="61" t="str">
         <f>'[1]TERM 1'!S67</f>
         <v/>
       </c>
       <c r="T65" s="62"/>
       <c r="U65" s="55"/>
       <c r="V65" s="56"/>
-      <c r="W65" s="125" t="str">
+      <c r="W65" s="58" t="str">
         <f>'[1]TERM 1'!W67</f>
         <v/>
       </c>
-      <c r="X65" s="126" t="str">
+      <c r="X65" s="59" t="str">
         <f>'[1]TERM 1'!X67</f>
         <v/>
       </c>
-      <c r="Y65" s="128" t="str">
+      <c r="Y65" s="63" t="str">
         <f>'[1]TERM 1'!Y67</f>
         <v/>
       </c>
-      <c r="Z65" s="125" t="str">
+      <c r="Z65" s="58" t="str">
         <f>'[1]TERM 1'!Z67</f>
         <v/>
       </c>
-      <c r="AA65" s="127" t="str">
+      <c r="AA65" s="61" t="str">
         <f>'[1]TERM 1'!AA67</f>
         <v/>
       </c>
@@ -10782,11 +10698,11 @@
         <f>'[1]TERM 1'!K69</f>
         <v/>
       </c>
-      <c r="L67" s="125" t="str">
+      <c r="L67" s="58" t="str">
         <f>'[1]TERM 1'!L69</f>
         <v/>
       </c>
-      <c r="M67" s="126" t="str">
+      <c r="M67" s="59" t="str">
         <f>'[1]TERM 1'!M69</f>
         <v/>
       </c>
@@ -10797,34 +10713,34 @@
         <f>'[1]TERM 1'!Q69</f>
         <v/>
       </c>
-      <c r="R67" s="125" t="str">
+      <c r="R67" s="58" t="str">
         <f>'[1]TERM 1'!R69</f>
         <v/>
       </c>
-      <c r="S67" s="127" t="str">
+      <c r="S67" s="61" t="str">
         <f>'[1]TERM 1'!S69</f>
         <v/>
       </c>
       <c r="T67" s="62"/>
       <c r="U67" s="55"/>
       <c r="V67" s="56"/>
-      <c r="W67" s="125" t="str">
+      <c r="W67" s="58" t="str">
         <f>'[1]TERM 1'!W69</f>
         <v/>
       </c>
-      <c r="X67" s="126" t="str">
+      <c r="X67" s="59" t="str">
         <f>'[1]TERM 1'!X69</f>
         <v/>
       </c>
-      <c r="Y67" s="128" t="str">
+      <c r="Y67" s="63" t="str">
         <f>'[1]TERM 1'!Y69</f>
         <v/>
       </c>
-      <c r="Z67" s="125" t="str">
+      <c r="Z67" s="58" t="str">
         <f>'[1]TERM 1'!Z69</f>
         <v/>
       </c>
-      <c r="AA67" s="127" t="str">
+      <c r="AA67" s="61" t="str">
         <f>'[1]TERM 1'!AA69</f>
         <v/>
       </c>
@@ -10858,11 +10774,11 @@
         <f>'[1]TERM 1'!K70</f>
         <v/>
       </c>
-      <c r="L68" s="125" t="str">
+      <c r="L68" s="58" t="str">
         <f>'[1]TERM 1'!L70</f>
         <v/>
       </c>
-      <c r="M68" s="126" t="str">
+      <c r="M68" s="59" t="str">
         <f>'[1]TERM 1'!M70</f>
         <v/>
       </c>
@@ -10873,34 +10789,34 @@
         <f>'[1]TERM 1'!Q70</f>
         <v/>
       </c>
-      <c r="R68" s="125" t="str">
+      <c r="R68" s="58" t="str">
         <f>'[1]TERM 1'!R70</f>
         <v/>
       </c>
-      <c r="S68" s="127" t="str">
+      <c r="S68" s="61" t="str">
         <f>'[1]TERM 1'!S70</f>
         <v/>
       </c>
       <c r="T68" s="62"/>
       <c r="U68" s="55"/>
       <c r="V68" s="56"/>
-      <c r="W68" s="125" t="str">
+      <c r="W68" s="58" t="str">
         <f>'[1]TERM 1'!W70</f>
         <v/>
       </c>
-      <c r="X68" s="126" t="str">
+      <c r="X68" s="59" t="str">
         <f>'[1]TERM 1'!X70</f>
         <v/>
       </c>
-      <c r="Y68" s="128" t="str">
+      <c r="Y68" s="63" t="str">
         <f>'[1]TERM 1'!Y70</f>
         <v/>
       </c>
-      <c r="Z68" s="125" t="str">
+      <c r="Z68" s="58" t="str">
         <f>'[1]TERM 1'!Z70</f>
         <v/>
       </c>
-      <c r="AA68" s="127" t="str">
+      <c r="AA68" s="61" t="str">
         <f>'[1]TERM 1'!AA70</f>
         <v/>
       </c>
@@ -10934,11 +10850,11 @@
         <f>'[1]TERM 1'!K71</f>
         <v/>
       </c>
-      <c r="L69" s="125" t="str">
+      <c r="L69" s="58" t="str">
         <f>'[1]TERM 1'!L71</f>
         <v/>
       </c>
-      <c r="M69" s="126" t="str">
+      <c r="M69" s="59" t="str">
         <f>'[1]TERM 1'!M71</f>
         <v/>
       </c>
@@ -10949,34 +10865,34 @@
         <f>'[1]TERM 1'!Q71</f>
         <v/>
       </c>
-      <c r="R69" s="125" t="str">
+      <c r="R69" s="58" t="str">
         <f>'[1]TERM 1'!R71</f>
         <v/>
       </c>
-      <c r="S69" s="127" t="str">
+      <c r="S69" s="61" t="str">
         <f>'[1]TERM 1'!S71</f>
         <v/>
       </c>
       <c r="T69" s="62"/>
       <c r="U69" s="55"/>
       <c r="V69" s="56"/>
-      <c r="W69" s="125" t="str">
+      <c r="W69" s="58" t="str">
         <f>'[1]TERM 1'!W71</f>
         <v/>
       </c>
-      <c r="X69" s="126" t="str">
+      <c r="X69" s="59" t="str">
         <f>'[1]TERM 1'!X71</f>
         <v/>
       </c>
-      <c r="Y69" s="128" t="str">
+      <c r="Y69" s="63" t="str">
         <f>'[1]TERM 1'!Y71</f>
         <v/>
       </c>
-      <c r="Z69" s="125" t="str">
+      <c r="Z69" s="58" t="str">
         <f>'[1]TERM 1'!Z71</f>
         <v/>
       </c>
-      <c r="AA69" s="127" t="str">
+      <c r="AA69" s="61" t="str">
         <f>'[1]TERM 1'!AA71</f>
         <v/>
       </c>
@@ -11010,11 +10926,11 @@
         <f>'[1]TERM 1'!K72</f>
         <v/>
       </c>
-      <c r="L70" s="125" t="str">
+      <c r="L70" s="58" t="str">
         <f>'[1]TERM 1'!L72</f>
         <v/>
       </c>
-      <c r="M70" s="126" t="str">
+      <c r="M70" s="59" t="str">
         <f>'[1]TERM 1'!M72</f>
         <v/>
       </c>
@@ -11025,34 +10941,34 @@
         <f>'[1]TERM 1'!Q72</f>
         <v/>
       </c>
-      <c r="R70" s="125" t="str">
+      <c r="R70" s="58" t="str">
         <f>'[1]TERM 1'!R72</f>
         <v/>
       </c>
-      <c r="S70" s="127" t="str">
+      <c r="S70" s="61" t="str">
         <f>'[1]TERM 1'!S72</f>
         <v/>
       </c>
       <c r="T70" s="62"/>
       <c r="U70" s="55"/>
       <c r="V70" s="56"/>
-      <c r="W70" s="125" t="str">
+      <c r="W70" s="58" t="str">
         <f>'[1]TERM 1'!W72</f>
         <v/>
       </c>
-      <c r="X70" s="126" t="str">
+      <c r="X70" s="59" t="str">
         <f>'[1]TERM 1'!X72</f>
         <v/>
       </c>
-      <c r="Y70" s="128" t="str">
+      <c r="Y70" s="63" t="str">
         <f>'[1]TERM 1'!Y72</f>
         <v/>
       </c>
-      <c r="Z70" s="125" t="str">
+      <c r="Z70" s="58" t="str">
         <f>'[1]TERM 1'!Z72</f>
         <v/>
       </c>
-      <c r="AA70" s="127" t="str">
+      <c r="AA70" s="61" t="str">
         <f>'[1]TERM 1'!AA72</f>
         <v/>
       </c>
@@ -11086,11 +11002,11 @@
         <f>'[1]TERM 1'!K73</f>
         <v/>
       </c>
-      <c r="L71" s="125" t="str">
+      <c r="L71" s="58" t="str">
         <f>'[1]TERM 1'!L73</f>
         <v/>
       </c>
-      <c r="M71" s="126" t="str">
+      <c r="M71" s="59" t="str">
         <f>'[1]TERM 1'!M73</f>
         <v/>
       </c>
@@ -11101,34 +11017,34 @@
         <f>'[1]TERM 1'!Q73</f>
         <v/>
       </c>
-      <c r="R71" s="125" t="str">
+      <c r="R71" s="58" t="str">
         <f>'[1]TERM 1'!R73</f>
         <v/>
       </c>
-      <c r="S71" s="127" t="str">
+      <c r="S71" s="61" t="str">
         <f>'[1]TERM 1'!S73</f>
         <v/>
       </c>
       <c r="T71" s="62"/>
       <c r="U71" s="55"/>
       <c r="V71" s="56"/>
-      <c r="W71" s="125" t="str">
+      <c r="W71" s="58" t="str">
         <f>'[1]TERM 1'!W73</f>
         <v/>
       </c>
-      <c r="X71" s="126" t="str">
+      <c r="X71" s="59" t="str">
         <f>'[1]TERM 1'!X73</f>
         <v/>
       </c>
-      <c r="Y71" s="128" t="str">
+      <c r="Y71" s="63" t="str">
         <f>'[1]TERM 1'!Y73</f>
         <v/>
       </c>
-      <c r="Z71" s="125" t="str">
+      <c r="Z71" s="58" t="str">
         <f>'[1]TERM 1'!Z73</f>
         <v/>
       </c>
-      <c r="AA71" s="127" t="str">
+      <c r="AA71" s="61" t="str">
         <f>'[1]TERM 1'!AA73</f>
         <v/>
       </c>
@@ -11162,11 +11078,11 @@
         <f>'[1]TERM 1'!K74</f>
         <v/>
       </c>
-      <c r="L72" s="125" t="str">
+      <c r="L72" s="58" t="str">
         <f>'[1]TERM 1'!L74</f>
         <v/>
       </c>
-      <c r="M72" s="126" t="str">
+      <c r="M72" s="59" t="str">
         <f>'[1]TERM 1'!M74</f>
         <v/>
       </c>
@@ -11177,34 +11093,34 @@
         <f>'[1]TERM 1'!Q74</f>
         <v/>
       </c>
-      <c r="R72" s="125" t="str">
+      <c r="R72" s="58" t="str">
         <f>'[1]TERM 1'!R74</f>
         <v/>
       </c>
-      <c r="S72" s="127" t="str">
+      <c r="S72" s="61" t="str">
         <f>'[1]TERM 1'!S74</f>
         <v/>
       </c>
       <c r="T72" s="62"/>
       <c r="U72" s="55"/>
       <c r="V72" s="56"/>
-      <c r="W72" s="125" t="str">
+      <c r="W72" s="58" t="str">
         <f>'[1]TERM 1'!W74</f>
         <v/>
       </c>
-      <c r="X72" s="126" t="str">
+      <c r="X72" s="59" t="str">
         <f>'[1]TERM 1'!X74</f>
         <v/>
       </c>
-      <c r="Y72" s="128" t="str">
+      <c r="Y72" s="63" t="str">
         <f>'[1]TERM 1'!Y74</f>
         <v/>
       </c>
-      <c r="Z72" s="125" t="str">
+      <c r="Z72" s="58" t="str">
         <f>'[1]TERM 1'!Z74</f>
         <v/>
       </c>
-      <c r="AA72" s="127" t="str">
+      <c r="AA72" s="61" t="str">
         <f>'[1]TERM 1'!AA74</f>
         <v/>
       </c>
@@ -11238,11 +11154,11 @@
         <f>'[1]TERM 1'!K75</f>
         <v/>
       </c>
-      <c r="L73" s="125" t="str">
+      <c r="L73" s="58" t="str">
         <f>'[1]TERM 1'!L75</f>
         <v/>
       </c>
-      <c r="M73" s="126" t="str">
+      <c r="M73" s="59" t="str">
         <f>'[1]TERM 1'!M75</f>
         <v/>
       </c>
@@ -11253,34 +11169,34 @@
         <f>'[1]TERM 1'!Q75</f>
         <v/>
       </c>
-      <c r="R73" s="125" t="str">
+      <c r="R73" s="58" t="str">
         <f>'[1]TERM 1'!R75</f>
         <v/>
       </c>
-      <c r="S73" s="127" t="str">
+      <c r="S73" s="61" t="str">
         <f>'[1]TERM 1'!S75</f>
         <v/>
       </c>
       <c r="T73" s="62"/>
       <c r="U73" s="55"/>
       <c r="V73" s="56"/>
-      <c r="W73" s="125" t="str">
+      <c r="W73" s="58" t="str">
         <f>'[1]TERM 1'!W75</f>
         <v/>
       </c>
-      <c r="X73" s="126" t="str">
+      <c r="X73" s="59" t="str">
         <f>'[1]TERM 1'!X75</f>
         <v/>
       </c>
-      <c r="Y73" s="128" t="str">
+      <c r="Y73" s="63" t="str">
         <f>'[1]TERM 1'!Y75</f>
         <v/>
       </c>
-      <c r="Z73" s="125" t="str">
+      <c r="Z73" s="58" t="str">
         <f>'[1]TERM 1'!Z75</f>
         <v/>
       </c>
-      <c r="AA73" s="127" t="str">
+      <c r="AA73" s="61" t="str">
         <f>'[1]TERM 1'!AA75</f>
         <v/>
       </c>
@@ -11314,11 +11230,11 @@
         <f>'[1]TERM 1'!K76</f>
         <v/>
       </c>
-      <c r="L74" s="125" t="str">
+      <c r="L74" s="58" t="str">
         <f>'[1]TERM 1'!L76</f>
         <v/>
       </c>
-      <c r="M74" s="126" t="str">
+      <c r="M74" s="59" t="str">
         <f>'[1]TERM 1'!M76</f>
         <v/>
       </c>
@@ -11329,34 +11245,34 @@
         <f>'[1]TERM 1'!Q76</f>
         <v/>
       </c>
-      <c r="R74" s="125" t="str">
+      <c r="R74" s="58" t="str">
         <f>'[1]TERM 1'!R76</f>
         <v/>
       </c>
-      <c r="S74" s="127" t="str">
+      <c r="S74" s="61" t="str">
         <f>'[1]TERM 1'!S76</f>
         <v/>
       </c>
       <c r="T74" s="62"/>
       <c r="U74" s="55"/>
       <c r="V74" s="56"/>
-      <c r="W74" s="125" t="str">
+      <c r="W74" s="58" t="str">
         <f>'[1]TERM 1'!W76</f>
         <v/>
       </c>
-      <c r="X74" s="126" t="str">
+      <c r="X74" s="59" t="str">
         <f>'[1]TERM 1'!X76</f>
         <v/>
       </c>
-      <c r="Y74" s="128" t="str">
+      <c r="Y74" s="63" t="str">
         <f>'[1]TERM 1'!Y76</f>
         <v/>
       </c>
-      <c r="Z74" s="125" t="str">
+      <c r="Z74" s="58" t="str">
         <f>'[1]TERM 1'!Z76</f>
         <v/>
       </c>
-      <c r="AA74" s="127" t="str">
+      <c r="AA74" s="61" t="str">
         <f>'[1]TERM 1'!AA76</f>
         <v/>
       </c>
@@ -11390,11 +11306,11 @@
         <f>'[1]TERM 1'!K77</f>
         <v/>
       </c>
-      <c r="L75" s="125" t="str">
+      <c r="L75" s="58" t="str">
         <f>'[1]TERM 1'!L77</f>
         <v/>
       </c>
-      <c r="M75" s="126" t="str">
+      <c r="M75" s="59" t="str">
         <f>'[1]TERM 1'!M77</f>
         <v/>
       </c>
@@ -11405,34 +11321,34 @@
         <f>'[1]TERM 1'!Q77</f>
         <v/>
       </c>
-      <c r="R75" s="125" t="str">
+      <c r="R75" s="58" t="str">
         <f>'[1]TERM 1'!R77</f>
         <v/>
       </c>
-      <c r="S75" s="127" t="str">
+      <c r="S75" s="61" t="str">
         <f>'[1]TERM 1'!S77</f>
         <v/>
       </c>
       <c r="T75" s="62"/>
       <c r="U75" s="55"/>
       <c r="V75" s="56"/>
-      <c r="W75" s="125" t="str">
+      <c r="W75" s="58" t="str">
         <f>'[1]TERM 1'!W77</f>
         <v/>
       </c>
-      <c r="X75" s="126" t="str">
+      <c r="X75" s="59" t="str">
         <f>'[1]TERM 1'!X77</f>
         <v/>
       </c>
-      <c r="Y75" s="128" t="str">
+      <c r="Y75" s="63" t="str">
         <f>'[1]TERM 1'!Y77</f>
         <v/>
       </c>
-      <c r="Z75" s="125" t="str">
+      <c r="Z75" s="58" t="str">
         <f>'[1]TERM 1'!Z77</f>
         <v/>
       </c>
-      <c r="AA75" s="127" t="str">
+      <c r="AA75" s="61" t="str">
         <f>'[1]TERM 1'!AA77</f>
         <v/>
       </c>
@@ -11466,11 +11382,11 @@
         <f>'[1]TERM 1'!K78</f>
         <v/>
       </c>
-      <c r="L76" s="125" t="str">
+      <c r="L76" s="58" t="str">
         <f>'[1]TERM 1'!L78</f>
         <v/>
       </c>
-      <c r="M76" s="126" t="str">
+      <c r="M76" s="59" t="str">
         <f>'[1]TERM 1'!M78</f>
         <v/>
       </c>
@@ -11481,34 +11397,34 @@
         <f>'[1]TERM 1'!Q78</f>
         <v/>
       </c>
-      <c r="R76" s="125" t="str">
+      <c r="R76" s="58" t="str">
         <f>'[1]TERM 1'!R78</f>
         <v/>
       </c>
-      <c r="S76" s="127" t="str">
+      <c r="S76" s="61" t="str">
         <f>'[1]TERM 1'!S78</f>
         <v/>
       </c>
       <c r="T76" s="62"/>
       <c r="U76" s="55"/>
       <c r="V76" s="56"/>
-      <c r="W76" s="125" t="str">
+      <c r="W76" s="58" t="str">
         <f>'[1]TERM 1'!W78</f>
         <v/>
       </c>
-      <c r="X76" s="126" t="str">
+      <c r="X76" s="59" t="str">
         <f>'[1]TERM 1'!X78</f>
         <v/>
       </c>
-      <c r="Y76" s="128" t="str">
+      <c r="Y76" s="63" t="str">
         <f>'[1]TERM 1'!Y78</f>
         <v/>
       </c>
-      <c r="Z76" s="125" t="str">
+      <c r="Z76" s="58" t="str">
         <f>'[1]TERM 1'!Z78</f>
         <v/>
       </c>
-      <c r="AA76" s="127" t="str">
+      <c r="AA76" s="61" t="str">
         <f>'[1]TERM 1'!AA78</f>
         <v/>
       </c>
@@ -11542,11 +11458,11 @@
         <f>'[1]TERM 1'!K79</f>
         <v/>
       </c>
-      <c r="L77" s="125" t="str">
+      <c r="L77" s="58" t="str">
         <f>'[1]TERM 1'!L79</f>
         <v/>
       </c>
-      <c r="M77" s="126" t="str">
+      <c r="M77" s="59" t="str">
         <f>'[1]TERM 1'!M79</f>
         <v/>
       </c>
@@ -11557,34 +11473,34 @@
         <f>'[1]TERM 1'!Q79</f>
         <v/>
       </c>
-      <c r="R77" s="125" t="str">
+      <c r="R77" s="58" t="str">
         <f>'[1]TERM 1'!R79</f>
         <v/>
       </c>
-      <c r="S77" s="127" t="str">
+      <c r="S77" s="61" t="str">
         <f>'[1]TERM 1'!S79</f>
         <v/>
       </c>
       <c r="T77" s="62"/>
       <c r="U77" s="55"/>
       <c r="V77" s="56"/>
-      <c r="W77" s="125" t="str">
+      <c r="W77" s="58" t="str">
         <f>'[1]TERM 1'!W79</f>
         <v/>
       </c>
-      <c r="X77" s="126" t="str">
+      <c r="X77" s="59" t="str">
         <f>'[1]TERM 1'!X79</f>
         <v/>
       </c>
-      <c r="Y77" s="128" t="str">
+      <c r="Y77" s="63" t="str">
         <f>'[1]TERM 1'!Y79</f>
         <v/>
       </c>
-      <c r="Z77" s="125" t="str">
+      <c r="Z77" s="58" t="str">
         <f>'[1]TERM 1'!Z79</f>
         <v/>
       </c>
-      <c r="AA77" s="127" t="str">
+      <c r="AA77" s="61" t="str">
         <f>'[1]TERM 1'!AA79</f>
         <v/>
       </c>
@@ -11618,11 +11534,11 @@
         <f>'[1]TERM 1'!K80</f>
         <v/>
       </c>
-      <c r="L78" s="125" t="str">
+      <c r="L78" s="58" t="str">
         <f>'[1]TERM 1'!L80</f>
         <v/>
       </c>
-      <c r="M78" s="126" t="str">
+      <c r="M78" s="59" t="str">
         <f>'[1]TERM 1'!M80</f>
         <v/>
       </c>
@@ -11633,34 +11549,34 @@
         <f>'[1]TERM 1'!Q80</f>
         <v/>
       </c>
-      <c r="R78" s="125" t="str">
+      <c r="R78" s="58" t="str">
         <f>'[1]TERM 1'!R80</f>
         <v/>
       </c>
-      <c r="S78" s="127" t="str">
+      <c r="S78" s="61" t="str">
         <f>'[1]TERM 1'!S80</f>
         <v/>
       </c>
       <c r="T78" s="62"/>
       <c r="U78" s="55"/>
       <c r="V78" s="56"/>
-      <c r="W78" s="125" t="str">
+      <c r="W78" s="58" t="str">
         <f>'[1]TERM 1'!W80</f>
         <v/>
       </c>
-      <c r="X78" s="126" t="str">
+      <c r="X78" s="59" t="str">
         <f>'[1]TERM 1'!X80</f>
         <v/>
       </c>
-      <c r="Y78" s="128" t="str">
+      <c r="Y78" s="63" t="str">
         <f>'[1]TERM 1'!Y80</f>
         <v/>
       </c>
-      <c r="Z78" s="125" t="str">
+      <c r="Z78" s="58" t="str">
         <f>'[1]TERM 1'!Z80</f>
         <v/>
       </c>
-      <c r="AA78" s="127" t="str">
+      <c r="AA78" s="61" t="str">
         <f>'[1]TERM 1'!AA80</f>
         <v/>
       </c>
@@ -11694,11 +11610,11 @@
         <f>'[1]TERM 1'!K81</f>
         <v/>
       </c>
-      <c r="L79" s="125" t="str">
+      <c r="L79" s="58" t="str">
         <f>'[1]TERM 1'!L81</f>
         <v/>
       </c>
-      <c r="M79" s="126" t="str">
+      <c r="M79" s="59" t="str">
         <f>'[1]TERM 1'!M81</f>
         <v/>
       </c>
@@ -11709,34 +11625,34 @@
         <f>'[1]TERM 1'!Q81</f>
         <v/>
       </c>
-      <c r="R79" s="125" t="str">
+      <c r="R79" s="58" t="str">
         <f>'[1]TERM 1'!R81</f>
         <v/>
       </c>
-      <c r="S79" s="127" t="str">
+      <c r="S79" s="61" t="str">
         <f>'[1]TERM 1'!S81</f>
         <v/>
       </c>
       <c r="T79" s="62"/>
       <c r="U79" s="55"/>
       <c r="V79" s="56"/>
-      <c r="W79" s="125" t="str">
+      <c r="W79" s="58" t="str">
         <f>'[1]TERM 1'!W81</f>
         <v/>
       </c>
-      <c r="X79" s="126" t="str">
+      <c r="X79" s="59" t="str">
         <f>'[1]TERM 1'!X81</f>
         <v/>
       </c>
-      <c r="Y79" s="128" t="str">
+      <c r="Y79" s="63" t="str">
         <f>'[1]TERM 1'!Y81</f>
         <v/>
       </c>
-      <c r="Z79" s="125" t="str">
+      <c r="Z79" s="58" t="str">
         <f>'[1]TERM 1'!Z81</f>
         <v/>
       </c>
-      <c r="AA79" s="127" t="str">
+      <c r="AA79" s="61" t="str">
         <f>'[1]TERM 1'!AA81</f>
         <v/>
       </c>
@@ -11770,11 +11686,11 @@
         <f>'[1]TERM 1'!K82</f>
         <v/>
       </c>
-      <c r="L80" s="125" t="str">
+      <c r="L80" s="58" t="str">
         <f>'[1]TERM 1'!L82</f>
         <v/>
       </c>
-      <c r="M80" s="126" t="str">
+      <c r="M80" s="59" t="str">
         <f>'[1]TERM 1'!M82</f>
         <v/>
       </c>
@@ -11785,34 +11701,34 @@
         <f>'[1]TERM 1'!Q82</f>
         <v/>
       </c>
-      <c r="R80" s="125" t="str">
+      <c r="R80" s="58" t="str">
         <f>'[1]TERM 1'!R82</f>
         <v/>
       </c>
-      <c r="S80" s="127" t="str">
+      <c r="S80" s="61" t="str">
         <f>'[1]TERM 1'!S82</f>
         <v/>
       </c>
       <c r="T80" s="62"/>
       <c r="U80" s="55"/>
       <c r="V80" s="56"/>
-      <c r="W80" s="125" t="str">
+      <c r="W80" s="58" t="str">
         <f>'[1]TERM 1'!W82</f>
         <v/>
       </c>
-      <c r="X80" s="126" t="str">
+      <c r="X80" s="59" t="str">
         <f>'[1]TERM 1'!X82</f>
         <v/>
       </c>
-      <c r="Y80" s="128" t="str">
+      <c r="Y80" s="63" t="str">
         <f>'[1]TERM 1'!Y82</f>
         <v/>
       </c>
-      <c r="Z80" s="125" t="str">
+      <c r="Z80" s="58" t="str">
         <f>'[1]TERM 1'!Z82</f>
         <v/>
       </c>
-      <c r="AA80" s="127" t="str">
+      <c r="AA80" s="61" t="str">
         <f>'[1]TERM 1'!AA82</f>
         <v/>
       </c>
@@ -11846,11 +11762,11 @@
         <f>'[1]TERM 1'!K83</f>
         <v/>
       </c>
-      <c r="L81" s="125" t="str">
+      <c r="L81" s="58" t="str">
         <f>'[1]TERM 1'!L83</f>
         <v/>
       </c>
-      <c r="M81" s="126" t="str">
+      <c r="M81" s="59" t="str">
         <f>'[1]TERM 1'!M83</f>
         <v/>
       </c>
@@ -11861,34 +11777,34 @@
         <f>'[1]TERM 1'!Q83</f>
         <v/>
       </c>
-      <c r="R81" s="125" t="str">
+      <c r="R81" s="58" t="str">
         <f>'[1]TERM 1'!R83</f>
         <v/>
       </c>
-      <c r="S81" s="127" t="str">
+      <c r="S81" s="61" t="str">
         <f>'[1]TERM 1'!S83</f>
         <v/>
       </c>
       <c r="T81" s="62"/>
       <c r="U81" s="55"/>
       <c r="V81" s="56"/>
-      <c r="W81" s="125" t="str">
+      <c r="W81" s="58" t="str">
         <f>'[1]TERM 1'!W83</f>
         <v/>
       </c>
-      <c r="X81" s="126" t="str">
+      <c r="X81" s="59" t="str">
         <f>'[1]TERM 1'!X83</f>
         <v/>
       </c>
-      <c r="Y81" s="128" t="str">
+      <c r="Y81" s="63" t="str">
         <f>'[1]TERM 1'!Y83</f>
         <v/>
       </c>
-      <c r="Z81" s="125" t="str">
+      <c r="Z81" s="58" t="str">
         <f>'[1]TERM 1'!Z83</f>
         <v/>
       </c>
-      <c r="AA81" s="127" t="str">
+      <c r="AA81" s="61" t="str">
         <f>'[1]TERM 1'!AA83</f>
         <v/>
       </c>
@@ -11922,11 +11838,11 @@
         <f>'[1]TERM 1'!K84</f>
         <v/>
       </c>
-      <c r="L82" s="125" t="str">
+      <c r="L82" s="58" t="str">
         <f>'[1]TERM 1'!L84</f>
         <v/>
       </c>
-      <c r="M82" s="126" t="str">
+      <c r="M82" s="59" t="str">
         <f>'[1]TERM 1'!M84</f>
         <v/>
       </c>
@@ -11937,34 +11853,34 @@
         <f>'[1]TERM 1'!Q84</f>
         <v/>
       </c>
-      <c r="R82" s="125" t="str">
+      <c r="R82" s="58" t="str">
         <f>'[1]TERM 1'!R84</f>
         <v/>
       </c>
-      <c r="S82" s="127" t="str">
+      <c r="S82" s="61" t="str">
         <f>'[1]TERM 1'!S84</f>
         <v/>
       </c>
       <c r="T82" s="62"/>
       <c r="U82" s="55"/>
       <c r="V82" s="56"/>
-      <c r="W82" s="125" t="str">
+      <c r="W82" s="58" t="str">
         <f>'[1]TERM 1'!W84</f>
         <v/>
       </c>
-      <c r="X82" s="126" t="str">
+      <c r="X82" s="59" t="str">
         <f>'[1]TERM 1'!X84</f>
         <v/>
       </c>
-      <c r="Y82" s="128" t="str">
+      <c r="Y82" s="63" t="str">
         <f>'[1]TERM 1'!Y84</f>
         <v/>
       </c>
-      <c r="Z82" s="125" t="str">
+      <c r="Z82" s="58" t="str">
         <f>'[1]TERM 1'!Z84</f>
         <v/>
       </c>
-      <c r="AA82" s="127" t="str">
+      <c r="AA82" s="61" t="str">
         <f>'[1]TERM 1'!AA84</f>
         <v/>
       </c>
@@ -11998,11 +11914,11 @@
         <f>'[1]TERM 1'!K85</f>
         <v/>
       </c>
-      <c r="L83" s="125" t="str">
+      <c r="L83" s="58" t="str">
         <f>'[1]TERM 1'!L85</f>
         <v/>
       </c>
-      <c r="M83" s="126" t="str">
+      <c r="M83" s="59" t="str">
         <f>'[1]TERM 1'!M85</f>
         <v/>
       </c>
@@ -12013,34 +11929,34 @@
         <f>'[1]TERM 1'!Q85</f>
         <v/>
       </c>
-      <c r="R83" s="125" t="str">
+      <c r="R83" s="58" t="str">
         <f>'[1]TERM 1'!R85</f>
         <v/>
       </c>
-      <c r="S83" s="127" t="str">
+      <c r="S83" s="61" t="str">
         <f>'[1]TERM 1'!S85</f>
         <v/>
       </c>
       <c r="T83" s="62"/>
       <c r="U83" s="55"/>
       <c r="V83" s="56"/>
-      <c r="W83" s="125" t="str">
+      <c r="W83" s="58" t="str">
         <f>'[1]TERM 1'!W85</f>
         <v/>
       </c>
-      <c r="X83" s="126" t="str">
+      <c r="X83" s="59" t="str">
         <f>'[1]TERM 1'!X85</f>
         <v/>
       </c>
-      <c r="Y83" s="128" t="str">
+      <c r="Y83" s="63" t="str">
         <f>'[1]TERM 1'!Y85</f>
         <v/>
       </c>
-      <c r="Z83" s="125" t="str">
+      <c r="Z83" s="58" t="str">
         <f>'[1]TERM 1'!Z85</f>
         <v/>
       </c>
-      <c r="AA83" s="127" t="str">
+      <c r="AA83" s="61" t="str">
         <f>'[1]TERM 1'!AA85</f>
         <v/>
       </c>
@@ -12074,11 +11990,11 @@
         <f>'[1]TERM 1'!K86</f>
         <v/>
       </c>
-      <c r="L84" s="125" t="str">
+      <c r="L84" s="58" t="str">
         <f>'[1]TERM 1'!L86</f>
         <v/>
       </c>
-      <c r="M84" s="126" t="str">
+      <c r="M84" s="59" t="str">
         <f>'[1]TERM 1'!M86</f>
         <v/>
       </c>
@@ -12089,34 +12005,34 @@
         <f>'[1]TERM 1'!Q86</f>
         <v/>
       </c>
-      <c r="R84" s="125" t="str">
+      <c r="R84" s="58" t="str">
         <f>'[1]TERM 1'!R86</f>
         <v/>
       </c>
-      <c r="S84" s="127" t="str">
+      <c r="S84" s="61" t="str">
         <f>'[1]TERM 1'!S86</f>
         <v/>
       </c>
       <c r="T84" s="62"/>
       <c r="U84" s="55"/>
       <c r="V84" s="56"/>
-      <c r="W84" s="125" t="str">
+      <c r="W84" s="58" t="str">
         <f>'[1]TERM 1'!W86</f>
         <v/>
       </c>
-      <c r="X84" s="126" t="str">
+      <c r="X84" s="59" t="str">
         <f>'[1]TERM 1'!X86</f>
         <v/>
       </c>
-      <c r="Y84" s="128" t="str">
+      <c r="Y84" s="63" t="str">
         <f>'[1]TERM 1'!Y86</f>
         <v/>
       </c>
-      <c r="Z84" s="125" t="str">
+      <c r="Z84" s="58" t="str">
         <f>'[1]TERM 1'!Z86</f>
         <v/>
       </c>
-      <c r="AA84" s="127" t="str">
+      <c r="AA84" s="61" t="str">
         <f>'[1]TERM 1'!AA86</f>
         <v/>
       </c>
@@ -12150,11 +12066,11 @@
         <f>'[1]TERM 1'!K87</f>
         <v/>
       </c>
-      <c r="L85" s="125" t="str">
+      <c r="L85" s="58" t="str">
         <f>'[1]TERM 1'!L87</f>
         <v/>
       </c>
-      <c r="M85" s="126" t="str">
+      <c r="M85" s="59" t="str">
         <f>'[1]TERM 1'!M87</f>
         <v/>
       </c>
@@ -12165,34 +12081,34 @@
         <f>'[1]TERM 1'!Q87</f>
         <v/>
       </c>
-      <c r="R85" s="125" t="str">
+      <c r="R85" s="58" t="str">
         <f>'[1]TERM 1'!R87</f>
         <v/>
       </c>
-      <c r="S85" s="127" t="str">
+      <c r="S85" s="61" t="str">
         <f>'[1]TERM 1'!S87</f>
         <v/>
       </c>
       <c r="T85" s="62"/>
       <c r="U85" s="55"/>
       <c r="V85" s="56"/>
-      <c r="W85" s="125" t="str">
+      <c r="W85" s="58" t="str">
         <f>'[1]TERM 1'!W87</f>
         <v/>
       </c>
-      <c r="X85" s="126" t="str">
+      <c r="X85" s="59" t="str">
         <f>'[1]TERM 1'!X87</f>
         <v/>
       </c>
-      <c r="Y85" s="128" t="str">
+      <c r="Y85" s="63" t="str">
         <f>'[1]TERM 1'!Y87</f>
         <v/>
       </c>
-      <c r="Z85" s="125" t="str">
+      <c r="Z85" s="58" t="str">
         <f>'[1]TERM 1'!Z87</f>
         <v/>
       </c>
-      <c r="AA85" s="127" t="str">
+      <c r="AA85" s="61" t="str">
         <f>'[1]TERM 1'!AA87</f>
         <v/>
       </c>
@@ -12226,11 +12142,11 @@
         <f>'[1]TERM 1'!K88</f>
         <v/>
       </c>
-      <c r="L86" s="125" t="str">
+      <c r="L86" s="58" t="str">
         <f>'[1]TERM 1'!L88</f>
         <v/>
       </c>
-      <c r="M86" s="126" t="str">
+      <c r="M86" s="59" t="str">
         <f>'[1]TERM 1'!M88</f>
         <v/>
       </c>
@@ -12241,34 +12157,34 @@
         <f>'[1]TERM 1'!Q88</f>
         <v/>
       </c>
-      <c r="R86" s="125" t="str">
+      <c r="R86" s="58" t="str">
         <f>'[1]TERM 1'!R88</f>
         <v/>
       </c>
-      <c r="S86" s="127" t="str">
+      <c r="S86" s="61" t="str">
         <f>'[1]TERM 1'!S88</f>
         <v/>
       </c>
       <c r="T86" s="62"/>
       <c r="U86" s="55"/>
       <c r="V86" s="56"/>
-      <c r="W86" s="125" t="str">
+      <c r="W86" s="58" t="str">
         <f>'[1]TERM 1'!W88</f>
         <v/>
       </c>
-      <c r="X86" s="126" t="str">
+      <c r="X86" s="59" t="str">
         <f>'[1]TERM 1'!X88</f>
         <v/>
       </c>
-      <c r="Y86" s="128" t="str">
+      <c r="Y86" s="63" t="str">
         <f>'[1]TERM 1'!Y88</f>
         <v/>
       </c>
-      <c r="Z86" s="125" t="str">
+      <c r="Z86" s="58" t="str">
         <f>'[1]TERM 1'!Z88</f>
         <v/>
       </c>
-      <c r="AA86" s="127" t="str">
+      <c r="AA86" s="61" t="str">
         <f>'[1]TERM 1'!AA88</f>
         <v/>
       </c>
@@ -12302,11 +12218,11 @@
         <f>'[1]TERM 1'!K89</f>
         <v/>
       </c>
-      <c r="L87" s="125" t="str">
+      <c r="L87" s="58" t="str">
         <f>'[1]TERM 1'!L89</f>
         <v/>
       </c>
-      <c r="M87" s="126" t="str">
+      <c r="M87" s="59" t="str">
         <f>'[1]TERM 1'!M89</f>
         <v/>
       </c>
@@ -12317,34 +12233,34 @@
         <f>'[1]TERM 1'!Q89</f>
         <v/>
       </c>
-      <c r="R87" s="125" t="str">
+      <c r="R87" s="58" t="str">
         <f>'[1]TERM 1'!R89</f>
         <v/>
       </c>
-      <c r="S87" s="127" t="str">
+      <c r="S87" s="61" t="str">
         <f>'[1]TERM 1'!S89</f>
         <v/>
       </c>
       <c r="T87" s="62"/>
       <c r="U87" s="55"/>
       <c r="V87" s="56"/>
-      <c r="W87" s="125" t="str">
+      <c r="W87" s="58" t="str">
         <f>'[1]TERM 1'!W89</f>
         <v/>
       </c>
-      <c r="X87" s="126" t="str">
+      <c r="X87" s="59" t="str">
         <f>'[1]TERM 1'!X89</f>
         <v/>
       </c>
-      <c r="Y87" s="128" t="str">
+      <c r="Y87" s="63" t="str">
         <f>'[1]TERM 1'!Y89</f>
         <v/>
       </c>
-      <c r="Z87" s="125" t="str">
+      <c r="Z87" s="58" t="str">
         <f>'[1]TERM 1'!Z89</f>
         <v/>
       </c>
-      <c r="AA87" s="127" t="str">
+      <c r="AA87" s="61" t="str">
         <f>'[1]TERM 1'!AA89</f>
         <v/>
       </c>
@@ -12378,11 +12294,11 @@
         <f>'[1]TERM 1'!K90</f>
         <v/>
       </c>
-      <c r="L88" s="129" t="str">
+      <c r="L88" s="83" t="str">
         <f>'[1]TERM 1'!L90</f>
         <v/>
       </c>
-      <c r="M88" s="130" t="str">
+      <c r="M88" s="84" t="str">
         <f>'[1]TERM 1'!M90</f>
         <v/>
       </c>
@@ -12393,34 +12309,34 @@
         <f>'[1]TERM 1'!Q90</f>
         <v/>
       </c>
-      <c r="R88" s="129" t="str">
+      <c r="R88" s="83" t="str">
         <f>'[1]TERM 1'!R90</f>
         <v/>
       </c>
-      <c r="S88" s="131" t="str">
+      <c r="S88" s="86" t="str">
         <f>'[1]TERM 1'!S90</f>
         <v/>
       </c>
       <c r="T88" s="79"/>
       <c r="U88" s="80"/>
       <c r="V88" s="81"/>
-      <c r="W88" s="129" t="str">
+      <c r="W88" s="83" t="str">
         <f>'[1]TERM 1'!W90</f>
         <v/>
       </c>
-      <c r="X88" s="130" t="str">
+      <c r="X88" s="84" t="str">
         <f>'[1]TERM 1'!X90</f>
         <v/>
       </c>
-      <c r="Y88" s="120" t="str">
+      <c r="Y88" s="35" t="str">
         <f>'[1]TERM 1'!Y90</f>
         <v/>
       </c>
-      <c r="Z88" s="129" t="str">
+      <c r="Z88" s="83" t="str">
         <f>'[1]TERM 1'!Z90</f>
         <v/>
       </c>
-      <c r="AA88" s="131" t="str">
+      <c r="AA88" s="86" t="str">
         <f>'[1]TERM 1'!AA90</f>
         <v/>
       </c>
@@ -12454,11 +12370,11 @@
         <f>'[1]TERM 1'!K91</f>
         <v/>
       </c>
-      <c r="L89" s="133" t="str">
+      <c r="L89" s="95" t="str">
         <f>'[1]TERM 1'!L91</f>
         <v/>
       </c>
-      <c r="M89" s="134" t="str">
+      <c r="M89" s="96" t="str">
         <f>'[1]TERM 1'!M91</f>
         <v/>
       </c>
@@ -12469,34 +12385,34 @@
         <f>'[1]TERM 1'!Q91</f>
         <v/>
       </c>
-      <c r="R89" s="133" t="str">
+      <c r="R89" s="95" t="str">
         <f>'[1]TERM 1'!R91</f>
         <v/>
       </c>
-      <c r="S89" s="134" t="str">
+      <c r="S89" s="96" t="str">
         <f>'[1]TERM 1'!S91</f>
         <v/>
       </c>
       <c r="T89" s="91"/>
       <c r="U89" s="92"/>
       <c r="V89" s="93"/>
-      <c r="W89" s="133" t="str">
+      <c r="W89" s="95" t="str">
         <f>'[1]TERM 1'!W91</f>
         <v/>
       </c>
-      <c r="X89" s="133" t="str">
+      <c r="X89" s="95" t="str">
         <f>'[1]TERM 1'!X91</f>
         <v/>
       </c>
-      <c r="Y89" s="132" t="str">
+      <c r="Y89" s="94" t="str">
         <f>'[1]TERM 1'!Y91</f>
         <v/>
       </c>
-      <c r="Z89" s="133" t="str">
+      <c r="Z89" s="95" t="str">
         <f>'[1]TERM 1'!Z91</f>
         <v/>
       </c>
-      <c r="AA89" s="133" t="str">
+      <c r="AA89" s="95" t="str">
         <f>'[1]TERM 1'!AA91</f>
         <v/>
       </c>
@@ -12530,11 +12446,11 @@
         <f>'[1]TERM 1'!K92</f>
         <v/>
       </c>
-      <c r="L90" s="136" t="str">
+      <c r="L90" s="104" t="str">
         <f>'[1]TERM 1'!L92</f>
         <v/>
       </c>
-      <c r="M90" s="137" t="str">
+      <c r="M90" s="105" t="str">
         <f>'[1]TERM 1'!M92</f>
         <v/>
       </c>
@@ -12545,34 +12461,34 @@
         <f>'[1]TERM 1'!Q92</f>
         <v/>
       </c>
-      <c r="R90" s="136" t="str">
+      <c r="R90" s="104" t="str">
         <f>'[1]TERM 1'!R92</f>
         <v/>
       </c>
-      <c r="S90" s="137" t="str">
+      <c r="S90" s="105" t="str">
         <f>'[1]TERM 1'!S92</f>
         <v/>
       </c>
       <c r="T90" s="100"/>
       <c r="U90" s="101"/>
       <c r="V90" s="102"/>
-      <c r="W90" s="136" t="str">
+      <c r="W90" s="104" t="str">
         <f>'[1]TERM 1'!W92</f>
         <v/>
       </c>
-      <c r="X90" s="136" t="str">
+      <c r="X90" s="104" t="str">
         <f>'[1]TERM 1'!X92</f>
         <v/>
       </c>
-      <c r="Y90" s="135" t="str">
+      <c r="Y90" s="103" t="str">
         <f>'[1]TERM 1'!Y92</f>
         <v/>
       </c>
-      <c r="Z90" s="136" t="str">
+      <c r="Z90" s="104" t="str">
         <f>'[1]TERM 1'!Z92</f>
         <v/>
       </c>
-      <c r="AA90" s="136" t="str">
+      <c r="AA90" s="104" t="str">
         <f>'[1]TERM 1'!AA92</f>
         <v/>
       </c>
@@ -12606,11 +12522,11 @@
         <f>'[1]TERM 1'!K93</f>
         <v/>
       </c>
-      <c r="L91" s="136" t="str">
+      <c r="L91" s="104" t="str">
         <f>'[1]TERM 1'!L93</f>
         <v/>
       </c>
-      <c r="M91" s="137" t="str">
+      <c r="M91" s="105" t="str">
         <f>'[1]TERM 1'!M93</f>
         <v/>
       </c>
@@ -12621,34 +12537,34 @@
         <f>'[1]TERM 1'!Q93</f>
         <v/>
       </c>
-      <c r="R91" s="136" t="str">
+      <c r="R91" s="104" t="str">
         <f>'[1]TERM 1'!R93</f>
         <v/>
       </c>
-      <c r="S91" s="137" t="str">
+      <c r="S91" s="105" t="str">
         <f>'[1]TERM 1'!S93</f>
         <v/>
       </c>
       <c r="T91" s="100"/>
       <c r="U91" s="101"/>
       <c r="V91" s="102"/>
-      <c r="W91" s="136" t="str">
+      <c r="W91" s="104" t="str">
         <f>'[1]TERM 1'!W93</f>
         <v/>
       </c>
-      <c r="X91" s="136" t="str">
+      <c r="X91" s="104" t="str">
         <f>'[1]TERM 1'!X93</f>
         <v/>
       </c>
-      <c r="Y91" s="135" t="str">
+      <c r="Y91" s="103" t="str">
         <f>'[1]TERM 1'!Y93</f>
         <v/>
       </c>
-      <c r="Z91" s="136" t="str">
+      <c r="Z91" s="104" t="str">
         <f>'[1]TERM 1'!Z93</f>
         <v/>
       </c>
-      <c r="AA91" s="136" t="str">
+      <c r="AA91" s="104" t="str">
         <f>'[1]TERM 1'!AA93</f>
         <v/>
       </c>
@@ -12682,11 +12598,11 @@
         <f>'[1]TERM 1'!K94</f>
         <v/>
       </c>
-      <c r="L92" s="136" t="str">
+      <c r="L92" s="104" t="str">
         <f>'[1]TERM 1'!L94</f>
         <v/>
       </c>
-      <c r="M92" s="137" t="str">
+      <c r="M92" s="105" t="str">
         <f>'[1]TERM 1'!M94</f>
         <v/>
       </c>
@@ -12697,34 +12613,34 @@
         <f>'[1]TERM 1'!Q94</f>
         <v/>
       </c>
-      <c r="R92" s="136" t="str">
+      <c r="R92" s="104" t="str">
         <f>'[1]TERM 1'!R94</f>
         <v/>
       </c>
-      <c r="S92" s="137" t="str">
+      <c r="S92" s="105" t="str">
         <f>'[1]TERM 1'!S94</f>
         <v/>
       </c>
       <c r="T92" s="100"/>
       <c r="U92" s="101"/>
       <c r="V92" s="102"/>
-      <c r="W92" s="136" t="str">
+      <c r="W92" s="104" t="str">
         <f>'[1]TERM 1'!W94</f>
         <v/>
       </c>
-      <c r="X92" s="136" t="str">
+      <c r="X92" s="104" t="str">
         <f>'[1]TERM 1'!X94</f>
         <v/>
       </c>
-      <c r="Y92" s="135" t="str">
+      <c r="Y92" s="103" t="str">
         <f>'[1]TERM 1'!Y94</f>
         <v/>
       </c>
-      <c r="Z92" s="136" t="str">
+      <c r="Z92" s="104" t="str">
         <f>'[1]TERM 1'!Z94</f>
         <v/>
       </c>
-      <c r="AA92" s="136" t="str">
+      <c r="AA92" s="104" t="str">
         <f>'[1]TERM 1'!AA94</f>
         <v/>
       </c>
@@ -12758,11 +12674,11 @@
         <f>'[1]TERM 1'!K95</f>
         <v/>
       </c>
-      <c r="L93" s="136" t="str">
+      <c r="L93" s="104" t="str">
         <f>'[1]TERM 1'!L95</f>
         <v/>
       </c>
-      <c r="M93" s="137" t="str">
+      <c r="M93" s="105" t="str">
         <f>'[1]TERM 1'!M95</f>
         <v/>
       </c>
@@ -12773,34 +12689,34 @@
         <f>'[1]TERM 1'!Q95</f>
         <v/>
       </c>
-      <c r="R93" s="136" t="str">
+      <c r="R93" s="104" t="str">
         <f>'[1]TERM 1'!R95</f>
         <v/>
       </c>
-      <c r="S93" s="137" t="str">
+      <c r="S93" s="105" t="str">
         <f>'[1]TERM 1'!S95</f>
         <v/>
       </c>
       <c r="T93" s="100"/>
       <c r="U93" s="101"/>
       <c r="V93" s="102"/>
-      <c r="W93" s="136" t="str">
+      <c r="W93" s="104" t="str">
         <f>'[1]TERM 1'!W95</f>
         <v/>
       </c>
-      <c r="X93" s="136" t="str">
+      <c r="X93" s="104" t="str">
         <f>'[1]TERM 1'!X95</f>
         <v/>
       </c>
-      <c r="Y93" s="135" t="str">
+      <c r="Y93" s="103" t="str">
         <f>'[1]TERM 1'!Y95</f>
         <v/>
       </c>
-      <c r="Z93" s="136" t="str">
+      <c r="Z93" s="104" t="str">
         <f>'[1]TERM 1'!Z95</f>
         <v/>
       </c>
-      <c r="AA93" s="136" t="str">
+      <c r="AA93" s="104" t="str">
         <f>'[1]TERM 1'!AA95</f>
         <v/>
       </c>
@@ -12834,11 +12750,11 @@
         <f>'[1]TERM 1'!K96</f>
         <v/>
       </c>
-      <c r="L94" s="136" t="str">
+      <c r="L94" s="104" t="str">
         <f>'[1]TERM 1'!L96</f>
         <v/>
       </c>
-      <c r="M94" s="137" t="str">
+      <c r="M94" s="105" t="str">
         <f>'[1]TERM 1'!M96</f>
         <v/>
       </c>
@@ -12849,34 +12765,34 @@
         <f>'[1]TERM 1'!Q96</f>
         <v/>
       </c>
-      <c r="R94" s="136" t="str">
+      <c r="R94" s="104" t="str">
         <f>'[1]TERM 1'!R96</f>
         <v/>
       </c>
-      <c r="S94" s="137" t="str">
+      <c r="S94" s="105" t="str">
         <f>'[1]TERM 1'!S96</f>
         <v/>
       </c>
       <c r="T94" s="100"/>
       <c r="U94" s="101"/>
       <c r="V94" s="102"/>
-      <c r="W94" s="136" t="str">
+      <c r="W94" s="104" t="str">
         <f>'[1]TERM 1'!W96</f>
         <v/>
       </c>
-      <c r="X94" s="136" t="str">
+      <c r="X94" s="104" t="str">
         <f>'[1]TERM 1'!X96</f>
         <v/>
       </c>
-      <c r="Y94" s="135" t="str">
+      <c r="Y94" s="103" t="str">
         <f>'[1]TERM 1'!Y96</f>
         <v/>
       </c>
-      <c r="Z94" s="136" t="str">
+      <c r="Z94" s="104" t="str">
         <f>'[1]TERM 1'!Z96</f>
         <v/>
       </c>
-      <c r="AA94" s="136" t="str">
+      <c r="AA94" s="104" t="str">
         <f>'[1]TERM 1'!AA96</f>
         <v/>
       </c>
@@ -12910,11 +12826,11 @@
         <f>'[1]TERM 1'!K97</f>
         <v/>
       </c>
-      <c r="L95" s="136" t="str">
+      <c r="L95" s="104" t="str">
         <f>'[1]TERM 1'!L97</f>
         <v/>
       </c>
-      <c r="M95" s="137" t="str">
+      <c r="M95" s="105" t="str">
         <f>'[1]TERM 1'!M97</f>
         <v/>
       </c>
@@ -12925,34 +12841,34 @@
         <f>'[1]TERM 1'!Q97</f>
         <v/>
       </c>
-      <c r="R95" s="136" t="str">
+      <c r="R95" s="104" t="str">
         <f>'[1]TERM 1'!R97</f>
         <v/>
       </c>
-      <c r="S95" s="137" t="str">
+      <c r="S95" s="105" t="str">
         <f>'[1]TERM 1'!S97</f>
         <v/>
       </c>
       <c r="T95" s="100"/>
       <c r="U95" s="101"/>
       <c r="V95" s="102"/>
-      <c r="W95" s="136" t="str">
+      <c r="W95" s="104" t="str">
         <f>'[1]TERM 1'!W97</f>
         <v/>
       </c>
-      <c r="X95" s="136" t="str">
+      <c r="X95" s="104" t="str">
         <f>'[1]TERM 1'!X97</f>
         <v/>
       </c>
-      <c r="Y95" s="135" t="str">
+      <c r="Y95" s="103" t="str">
         <f>'[1]TERM 1'!Y97</f>
         <v/>
       </c>
-      <c r="Z95" s="136" t="str">
+      <c r="Z95" s="104" t="str">
         <f>'[1]TERM 1'!Z97</f>
         <v/>
       </c>
-      <c r="AA95" s="136" t="str">
+      <c r="AA95" s="104" t="str">
         <f>'[1]TERM 1'!AA97</f>
         <v/>
       </c>
@@ -12986,11 +12902,11 @@
         <f>'[1]TERM 1'!K98</f>
         <v/>
       </c>
-      <c r="L96" s="136" t="str">
+      <c r="L96" s="104" t="str">
         <f>'[1]TERM 1'!L98</f>
         <v/>
       </c>
-      <c r="M96" s="137" t="str">
+      <c r="M96" s="105" t="str">
         <f>'[1]TERM 1'!M98</f>
         <v/>
       </c>
@@ -13001,34 +12917,34 @@
         <f>'[1]TERM 1'!Q98</f>
         <v/>
       </c>
-      <c r="R96" s="136" t="str">
+      <c r="R96" s="104" t="str">
         <f>'[1]TERM 1'!R98</f>
         <v/>
       </c>
-      <c r="S96" s="137" t="str">
+      <c r="S96" s="105" t="str">
         <f>'[1]TERM 1'!S98</f>
         <v/>
       </c>
       <c r="T96" s="100"/>
       <c r="U96" s="101"/>
       <c r="V96" s="102"/>
-      <c r="W96" s="136" t="str">
+      <c r="W96" s="104" t="str">
         <f>'[1]TERM 1'!W98</f>
         <v/>
       </c>
-      <c r="X96" s="136" t="str">
+      <c r="X96" s="104" t="str">
         <f>'[1]TERM 1'!X98</f>
         <v/>
       </c>
-      <c r="Y96" s="135" t="str">
+      <c r="Y96" s="103" t="str">
         <f>'[1]TERM 1'!Y98</f>
         <v/>
       </c>
-      <c r="Z96" s="136" t="str">
+      <c r="Z96" s="104" t="str">
         <f>'[1]TERM 1'!Z98</f>
         <v/>
       </c>
-      <c r="AA96" s="136" t="str">
+      <c r="AA96" s="104" t="str">
         <f>'[1]TERM 1'!AA98</f>
         <v/>
       </c>
@@ -13062,11 +12978,11 @@
         <f>'[1]TERM 1'!K99</f>
         <v/>
       </c>
-      <c r="L97" s="136" t="str">
+      <c r="L97" s="104" t="str">
         <f>'[1]TERM 1'!L99</f>
         <v/>
       </c>
-      <c r="M97" s="137" t="str">
+      <c r="M97" s="105" t="str">
         <f>'[1]TERM 1'!M99</f>
         <v/>
       </c>
@@ -13077,34 +12993,34 @@
         <f>'[1]TERM 1'!Q99</f>
         <v/>
       </c>
-      <c r="R97" s="136" t="str">
+      <c r="R97" s="104" t="str">
         <f>'[1]TERM 1'!R99</f>
         <v/>
       </c>
-      <c r="S97" s="137" t="str">
+      <c r="S97" s="105" t="str">
         <f>'[1]TERM 1'!S99</f>
         <v/>
       </c>
       <c r="T97" s="100"/>
       <c r="U97" s="101"/>
       <c r="V97" s="102"/>
-      <c r="W97" s="136" t="str">
+      <c r="W97" s="104" t="str">
         <f>'[1]TERM 1'!W99</f>
         <v/>
       </c>
-      <c r="X97" s="136" t="str">
+      <c r="X97" s="104" t="str">
         <f>'[1]TERM 1'!X99</f>
         <v/>
       </c>
-      <c r="Y97" s="135" t="str">
+      <c r="Y97" s="103" t="str">
         <f>'[1]TERM 1'!Y99</f>
         <v/>
       </c>
-      <c r="Z97" s="136" t="str">
+      <c r="Z97" s="104" t="str">
         <f>'[1]TERM 1'!Z99</f>
         <v/>
       </c>
-      <c r="AA97" s="136" t="str">
+      <c r="AA97" s="104" t="str">
         <f>'[1]TERM 1'!AA99</f>
         <v/>
       </c>
@@ -13138,11 +13054,11 @@
         <f>'[1]TERM 1'!K100</f>
         <v/>
       </c>
-      <c r="L98" s="136" t="str">
+      <c r="L98" s="104" t="str">
         <f>'[1]TERM 1'!L100</f>
         <v/>
       </c>
-      <c r="M98" s="137" t="str">
+      <c r="M98" s="105" t="str">
         <f>'[1]TERM 1'!M100</f>
         <v/>
       </c>
@@ -13153,34 +13069,34 @@
         <f>'[1]TERM 1'!Q100</f>
         <v/>
       </c>
-      <c r="R98" s="136" t="str">
+      <c r="R98" s="104" t="str">
         <f>'[1]TERM 1'!R100</f>
         <v/>
       </c>
-      <c r="S98" s="137" t="str">
+      <c r="S98" s="105" t="str">
         <f>'[1]TERM 1'!S100</f>
         <v/>
       </c>
       <c r="T98" s="100"/>
       <c r="U98" s="101"/>
       <c r="V98" s="102"/>
-      <c r="W98" s="136" t="str">
+      <c r="W98" s="104" t="str">
         <f>'[1]TERM 1'!W100</f>
         <v/>
       </c>
-      <c r="X98" s="136" t="str">
+      <c r="X98" s="104" t="str">
         <f>'[1]TERM 1'!X100</f>
         <v/>
       </c>
-      <c r="Y98" s="135" t="str">
+      <c r="Y98" s="103" t="str">
         <f>'[1]TERM 1'!Y100</f>
         <v/>
       </c>
-      <c r="Z98" s="136" t="str">
+      <c r="Z98" s="104" t="str">
         <f>'[1]TERM 1'!Z100</f>
         <v/>
       </c>
-      <c r="AA98" s="136" t="str">
+      <c r="AA98" s="104" t="str">
         <f>'[1]TERM 1'!AA100</f>
         <v/>
       </c>
@@ -13214,11 +13130,11 @@
         <f>'[1]TERM 1'!K101</f>
         <v/>
       </c>
-      <c r="L99" s="136" t="str">
+      <c r="L99" s="104" t="str">
         <f>'[1]TERM 1'!L101</f>
         <v/>
       </c>
-      <c r="M99" s="137" t="str">
+      <c r="M99" s="105" t="str">
         <f>'[1]TERM 1'!M101</f>
         <v/>
       </c>
@@ -13229,34 +13145,34 @@
         <f>'[1]TERM 1'!Q101</f>
         <v/>
       </c>
-      <c r="R99" s="136" t="str">
+      <c r="R99" s="104" t="str">
         <f>'[1]TERM 1'!R101</f>
         <v/>
       </c>
-      <c r="S99" s="137" t="str">
+      <c r="S99" s="105" t="str">
         <f>'[1]TERM 1'!S101</f>
         <v/>
       </c>
       <c r="T99" s="100"/>
       <c r="U99" s="101"/>
       <c r="V99" s="102"/>
-      <c r="W99" s="136" t="str">
+      <c r="W99" s="104" t="str">
         <f>'[1]TERM 1'!W101</f>
         <v/>
       </c>
-      <c r="X99" s="136" t="str">
+      <c r="X99" s="104" t="str">
         <f>'[1]TERM 1'!X101</f>
         <v/>
       </c>
-      <c r="Y99" s="135" t="str">
+      <c r="Y99" s="103" t="str">
         <f>'[1]TERM 1'!Y101</f>
         <v/>
       </c>
-      <c r="Z99" s="136" t="str">
+      <c r="Z99" s="104" t="str">
         <f>'[1]TERM 1'!Z101</f>
         <v/>
       </c>
-      <c r="AA99" s="136" t="str">
+      <c r="AA99" s="104" t="str">
         <f>'[1]TERM 1'!AA101</f>
         <v/>
       </c>
@@ -13290,11 +13206,11 @@
         <f>'[1]TERM 1'!K102</f>
         <v/>
       </c>
-      <c r="L100" s="136" t="str">
+      <c r="L100" s="104" t="str">
         <f>'[1]TERM 1'!L102</f>
         <v/>
       </c>
-      <c r="M100" s="137" t="str">
+      <c r="M100" s="105" t="str">
         <f>'[1]TERM 1'!M102</f>
         <v/>
       </c>
@@ -13305,34 +13221,34 @@
         <f>'[1]TERM 1'!Q102</f>
         <v/>
       </c>
-      <c r="R100" s="136" t="str">
+      <c r="R100" s="104" t="str">
         <f>'[1]TERM 1'!R102</f>
         <v/>
       </c>
-      <c r="S100" s="137" t="str">
+      <c r="S100" s="105" t="str">
         <f>'[1]TERM 1'!S102</f>
         <v/>
       </c>
       <c r="T100" s="100"/>
       <c r="U100" s="101"/>
       <c r="V100" s="102"/>
-      <c r="W100" s="136" t="str">
+      <c r="W100" s="104" t="str">
         <f>'[1]TERM 1'!W102</f>
         <v/>
       </c>
-      <c r="X100" s="136" t="str">
+      <c r="X100" s="104" t="str">
         <f>'[1]TERM 1'!X102</f>
         <v/>
       </c>
-      <c r="Y100" s="135" t="str">
+      <c r="Y100" s="103" t="str">
         <f>'[1]TERM 1'!Y102</f>
         <v/>
       </c>
-      <c r="Z100" s="136" t="str">
+      <c r="Z100" s="104" t="str">
         <f>'[1]TERM 1'!Z102</f>
         <v/>
       </c>
-      <c r="AA100" s="136" t="str">
+      <c r="AA100" s="104" t="str">
         <f>'[1]TERM 1'!AA102</f>
         <v/>
       </c>
@@ -13366,11 +13282,11 @@
         <f>'[1]TERM 1'!K103</f>
         <v/>
       </c>
-      <c r="L101" s="136" t="str">
+      <c r="L101" s="104" t="str">
         <f>'[1]TERM 1'!L103</f>
         <v/>
       </c>
-      <c r="M101" s="137" t="str">
+      <c r="M101" s="105" t="str">
         <f>'[1]TERM 1'!M103</f>
         <v/>
       </c>
@@ -13381,34 +13297,34 @@
         <f>'[1]TERM 1'!Q103</f>
         <v/>
       </c>
-      <c r="R101" s="136" t="str">
+      <c r="R101" s="104" t="str">
         <f>'[1]TERM 1'!R103</f>
         <v/>
       </c>
-      <c r="S101" s="137" t="str">
+      <c r="S101" s="105" t="str">
         <f>'[1]TERM 1'!S103</f>
         <v/>
       </c>
       <c r="T101" s="100"/>
       <c r="U101" s="101"/>
       <c r="V101" s="102"/>
-      <c r="W101" s="136" t="str">
+      <c r="W101" s="104" t="str">
         <f>'[1]TERM 1'!W103</f>
         <v/>
       </c>
-      <c r="X101" s="136" t="str">
+      <c r="X101" s="104" t="str">
         <f>'[1]TERM 1'!X103</f>
         <v/>
       </c>
-      <c r="Y101" s="135" t="str">
+      <c r="Y101" s="103" t="str">
         <f>'[1]TERM 1'!Y103</f>
         <v/>
       </c>
-      <c r="Z101" s="136" t="str">
+      <c r="Z101" s="104" t="str">
         <f>'[1]TERM 1'!Z103</f>
         <v/>
       </c>
-      <c r="AA101" s="136" t="str">
+      <c r="AA101" s="104" t="str">
         <f>'[1]TERM 1'!AA103</f>
         <v/>
       </c>
@@ -13442,11 +13358,11 @@
         <f>'[1]TERM 1'!K104</f>
         <v/>
       </c>
-      <c r="L102" s="136" t="str">
+      <c r="L102" s="104" t="str">
         <f>'[1]TERM 1'!L104</f>
         <v/>
       </c>
-      <c r="M102" s="137" t="str">
+      <c r="M102" s="105" t="str">
         <f>'[1]TERM 1'!M104</f>
         <v/>
       </c>
@@ -13457,34 +13373,34 @@
         <f>'[1]TERM 1'!Q104</f>
         <v/>
       </c>
-      <c r="R102" s="136" t="str">
+      <c r="R102" s="104" t="str">
         <f>'[1]TERM 1'!R104</f>
         <v/>
       </c>
-      <c r="S102" s="137" t="str">
+      <c r="S102" s="105" t="str">
         <f>'[1]TERM 1'!S104</f>
         <v/>
       </c>
       <c r="T102" s="100"/>
       <c r="U102" s="101"/>
       <c r="V102" s="102"/>
-      <c r="W102" s="136" t="str">
+      <c r="W102" s="104" t="str">
         <f>'[1]TERM 1'!W104</f>
         <v/>
       </c>
-      <c r="X102" s="136" t="str">
+      <c r="X102" s="104" t="str">
         <f>'[1]TERM 1'!X104</f>
         <v/>
       </c>
-      <c r="Y102" s="135" t="str">
+      <c r="Y102" s="103" t="str">
         <f>'[1]TERM 1'!Y104</f>
         <v/>
       </c>
-      <c r="Z102" s="136" t="str">
+      <c r="Z102" s="104" t="str">
         <f>'[1]TERM 1'!Z104</f>
         <v/>
       </c>
-      <c r="AA102" s="136" t="str">
+      <c r="AA102" s="104" t="str">
         <f>'[1]TERM 1'!AA104</f>
         <v/>
       </c>
@@ -13518,11 +13434,11 @@
         <f>'[1]TERM 1'!K105</f>
         <v/>
       </c>
-      <c r="L103" s="136" t="str">
+      <c r="L103" s="104" t="str">
         <f>'[1]TERM 1'!L105</f>
         <v/>
       </c>
-      <c r="M103" s="137" t="str">
+      <c r="M103" s="105" t="str">
         <f>'[1]TERM 1'!M105</f>
         <v/>
       </c>
@@ -13533,34 +13449,34 @@
         <f>'[1]TERM 1'!Q105</f>
         <v/>
       </c>
-      <c r="R103" s="136" t="str">
+      <c r="R103" s="104" t="str">
         <f>'[1]TERM 1'!R105</f>
         <v/>
       </c>
-      <c r="S103" s="137" t="str">
+      <c r="S103" s="105" t="str">
         <f>'[1]TERM 1'!S105</f>
         <v/>
       </c>
       <c r="T103" s="100"/>
       <c r="U103" s="101"/>
       <c r="V103" s="102"/>
-      <c r="W103" s="136" t="str">
+      <c r="W103" s="104" t="str">
         <f>'[1]TERM 1'!W105</f>
         <v/>
       </c>
-      <c r="X103" s="136" t="str">
+      <c r="X103" s="104" t="str">
         <f>'[1]TERM 1'!X105</f>
         <v/>
       </c>
-      <c r="Y103" s="135" t="str">
+      <c r="Y103" s="103" t="str">
         <f>'[1]TERM 1'!Y105</f>
         <v/>
       </c>
-      <c r="Z103" s="136" t="str">
+      <c r="Z103" s="104" t="str">
         <f>'[1]TERM 1'!Z105</f>
         <v/>
       </c>
-      <c r="AA103" s="136" t="str">
+      <c r="AA103" s="104" t="str">
         <f>'[1]TERM 1'!AA105</f>
         <v/>
       </c>
@@ -13594,11 +13510,11 @@
         <f>'[1]TERM 1'!K106</f>
         <v/>
       </c>
-      <c r="L104" s="136" t="str">
+      <c r="L104" s="104" t="str">
         <f>'[1]TERM 1'!L106</f>
         <v/>
       </c>
-      <c r="M104" s="137" t="str">
+      <c r="M104" s="105" t="str">
         <f>'[1]TERM 1'!M106</f>
         <v/>
       </c>
@@ -13609,34 +13525,34 @@
         <f>'[1]TERM 1'!Q106</f>
         <v/>
       </c>
-      <c r="R104" s="136" t="str">
+      <c r="R104" s="104" t="str">
         <f>'[1]TERM 1'!R106</f>
         <v/>
       </c>
-      <c r="S104" s="137" t="str">
+      <c r="S104" s="105" t="str">
         <f>'[1]TERM 1'!S106</f>
         <v/>
       </c>
       <c r="T104" s="100"/>
       <c r="U104" s="101"/>
       <c r="V104" s="102"/>
-      <c r="W104" s="136" t="str">
+      <c r="W104" s="104" t="str">
         <f>'[1]TERM 1'!W106</f>
         <v/>
       </c>
-      <c r="X104" s="136" t="str">
+      <c r="X104" s="104" t="str">
         <f>'[1]TERM 1'!X106</f>
         <v/>
       </c>
-      <c r="Y104" s="135" t="str">
+      <c r="Y104" s="103" t="str">
         <f>'[1]TERM 1'!Y106</f>
         <v/>
       </c>
-      <c r="Z104" s="136" t="str">
+      <c r="Z104" s="104" t="str">
         <f>'[1]TERM 1'!Z106</f>
         <v/>
       </c>
-      <c r="AA104" s="136" t="str">
+      <c r="AA104" s="104" t="str">
         <f>'[1]TERM 1'!AA106</f>
         <v/>
       </c>
@@ -13670,11 +13586,11 @@
         <f>'[1]TERM 1'!K107</f>
         <v/>
       </c>
-      <c r="L105" s="136" t="str">
+      <c r="L105" s="104" t="str">
         <f>'[1]TERM 1'!L107</f>
         <v/>
       </c>
-      <c r="M105" s="137" t="str">
+      <c r="M105" s="105" t="str">
         <f>'[1]TERM 1'!M107</f>
         <v/>
       </c>
@@ -13685,34 +13601,34 @@
         <f>'[1]TERM 1'!Q107</f>
         <v/>
       </c>
-      <c r="R105" s="136" t="str">
+      <c r="R105" s="104" t="str">
         <f>'[1]TERM 1'!R107</f>
         <v/>
       </c>
-      <c r="S105" s="137" t="str">
+      <c r="S105" s="105" t="str">
         <f>'[1]TERM 1'!S107</f>
         <v/>
       </c>
       <c r="T105" s="100"/>
       <c r="U105" s="101"/>
       <c r="V105" s="102"/>
-      <c r="W105" s="136" t="str">
+      <c r="W105" s="104" t="str">
         <f>'[1]TERM 1'!W107</f>
         <v/>
       </c>
-      <c r="X105" s="136" t="str">
+      <c r="X105" s="104" t="str">
         <f>'[1]TERM 1'!X107</f>
         <v/>
       </c>
-      <c r="Y105" s="135" t="str">
+      <c r="Y105" s="103" t="str">
         <f>'[1]TERM 1'!Y107</f>
         <v/>
       </c>
-      <c r="Z105" s="136" t="str">
+      <c r="Z105" s="104" t="str">
         <f>'[1]TERM 1'!Z107</f>
         <v/>
       </c>
-      <c r="AA105" s="136" t="str">
+      <c r="AA105" s="104" t="str">
         <f>'[1]TERM 1'!AA107</f>
         <v/>
       </c>
@@ -13746,11 +13662,11 @@
         <f>'[1]TERM 1'!K108</f>
         <v/>
       </c>
-      <c r="L106" s="136" t="str">
+      <c r="L106" s="104" t="str">
         <f>'[1]TERM 1'!L108</f>
         <v/>
       </c>
-      <c r="M106" s="137" t="str">
+      <c r="M106" s="105" t="str">
         <f>'[1]TERM 1'!M108</f>
         <v/>
       </c>
@@ -13761,34 +13677,34 @@
         <f>'[1]TERM 1'!Q108</f>
         <v/>
       </c>
-      <c r="R106" s="136" t="str">
+      <c r="R106" s="104" t="str">
         <f>'[1]TERM 1'!R108</f>
         <v/>
       </c>
-      <c r="S106" s="137" t="str">
+      <c r="S106" s="105" t="str">
         <f>'[1]TERM 1'!S108</f>
         <v/>
       </c>
       <c r="T106" s="100"/>
       <c r="U106" s="101"/>
       <c r="V106" s="102"/>
-      <c r="W106" s="136" t="str">
+      <c r="W106" s="104" t="str">
         <f>'[1]TERM 1'!W108</f>
         <v/>
       </c>
-      <c r="X106" s="136" t="str">
+      <c r="X106" s="104" t="str">
         <f>'[1]TERM 1'!X108</f>
         <v/>
       </c>
-      <c r="Y106" s="135" t="str">
+      <c r="Y106" s="103" t="str">
         <f>'[1]TERM 1'!Y108</f>
         <v/>
       </c>
-      <c r="Z106" s="136" t="str">
+      <c r="Z106" s="104" t="str">
         <f>'[1]TERM 1'!Z108</f>
         <v/>
       </c>
-      <c r="AA106" s="136" t="str">
+      <c r="AA106" s="104" t="str">
         <f>'[1]TERM 1'!AA108</f>
         <v/>
       </c>
@@ -13822,11 +13738,11 @@
         <f>'[1]TERM 1'!K109</f>
         <v/>
       </c>
-      <c r="L107" s="136" t="str">
+      <c r="L107" s="104" t="str">
         <f>'[1]TERM 1'!L109</f>
         <v/>
       </c>
-      <c r="M107" s="137" t="str">
+      <c r="M107" s="105" t="str">
         <f>'[1]TERM 1'!M109</f>
         <v/>
       </c>
@@ -13837,34 +13753,34 @@
         <f>'[1]TERM 1'!Q109</f>
         <v/>
       </c>
-      <c r="R107" s="136" t="str">
+      <c r="R107" s="104" t="str">
         <f>'[1]TERM 1'!R109</f>
         <v/>
       </c>
-      <c r="S107" s="137" t="str">
+      <c r="S107" s="105" t="str">
         <f>'[1]TERM 1'!S109</f>
         <v/>
       </c>
       <c r="T107" s="100"/>
       <c r="U107" s="101"/>
       <c r="V107" s="102"/>
-      <c r="W107" s="136" t="str">
+      <c r="W107" s="104" t="str">
         <f>'[1]TERM 1'!W109</f>
         <v/>
       </c>
-      <c r="X107" s="136" t="str">
+      <c r="X107" s="104" t="str">
         <f>'[1]TERM 1'!X109</f>
         <v/>
       </c>
-      <c r="Y107" s="135" t="str">
+      <c r="Y107" s="103" t="str">
         <f>'[1]TERM 1'!Y109</f>
         <v/>
       </c>
-      <c r="Z107" s="136" t="str">
+      <c r="Z107" s="104" t="str">
         <f>'[1]TERM 1'!Z109</f>
         <v/>
       </c>
-      <c r="AA107" s="136" t="str">
+      <c r="AA107" s="104" t="str">
         <f>'[1]TERM 1'!AA109</f>
         <v/>
       </c>
@@ -13898,11 +13814,11 @@
         <f>'[1]TERM 1'!K110</f>
         <v/>
       </c>
-      <c r="L108" s="136" t="str">
+      <c r="L108" s="104" t="str">
         <f>'[1]TERM 1'!L110</f>
         <v/>
       </c>
-      <c r="M108" s="137" t="str">
+      <c r="M108" s="105" t="str">
         <f>'[1]TERM 1'!M110</f>
         <v/>
       </c>
@@ -13913,34 +13829,34 @@
         <f>'[1]TERM 1'!Q110</f>
         <v/>
       </c>
-      <c r="R108" s="136" t="str">
+      <c r="R108" s="104" t="str">
         <f>'[1]TERM 1'!R110</f>
         <v/>
       </c>
-      <c r="S108" s="137" t="str">
+      <c r="S108" s="105" t="str">
         <f>'[1]TERM 1'!S110</f>
         <v/>
       </c>
       <c r="T108" s="100"/>
       <c r="U108" s="101"/>
       <c r="V108" s="102"/>
-      <c r="W108" s="136" t="str">
+      <c r="W108" s="104" t="str">
         <f>'[1]TERM 1'!W110</f>
         <v/>
       </c>
-      <c r="X108" s="136" t="str">
+      <c r="X108" s="104" t="str">
         <f>'[1]TERM 1'!X110</f>
         <v/>
       </c>
-      <c r="Y108" s="135" t="str">
+      <c r="Y108" s="103" t="str">
         <f>'[1]TERM 1'!Y110</f>
         <v/>
       </c>
-      <c r="Z108" s="136" t="str">
+      <c r="Z108" s="104" t="str">
         <f>'[1]TERM 1'!Z110</f>
         <v/>
       </c>
-      <c r="AA108" s="136" t="str">
+      <c r="AA108" s="104" t="str">
         <f>'[1]TERM 1'!AA110</f>
         <v/>
       </c>
@@ -13974,11 +13890,11 @@
         <f>'[1]TERM 1'!K111</f>
         <v/>
       </c>
-      <c r="L109" s="136" t="str">
+      <c r="L109" s="104" t="str">
         <f>'[1]TERM 1'!L111</f>
         <v/>
       </c>
-      <c r="M109" s="137" t="str">
+      <c r="M109" s="105" t="str">
         <f>'[1]TERM 1'!M111</f>
         <v/>
       </c>
@@ -13989,34 +13905,34 @@
         <f>'[1]TERM 1'!Q111</f>
         <v/>
       </c>
-      <c r="R109" s="136" t="str">
+      <c r="R109" s="104" t="str">
         <f>'[1]TERM 1'!R111</f>
         <v/>
       </c>
-      <c r="S109" s="137" t="str">
+      <c r="S109" s="105" t="str">
         <f>'[1]TERM 1'!S111</f>
         <v/>
       </c>
       <c r="T109" s="100"/>
       <c r="U109" s="101"/>
       <c r="V109" s="102"/>
-      <c r="W109" s="136" t="str">
+      <c r="W109" s="104" t="str">
         <f>'[1]TERM 1'!W111</f>
         <v/>
       </c>
-      <c r="X109" s="136" t="str">
+      <c r="X109" s="104" t="str">
         <f>'[1]TERM 1'!X111</f>
         <v/>
       </c>
-      <c r="Y109" s="135" t="str">
+      <c r="Y109" s="103" t="str">
         <f>'[1]TERM 1'!Y111</f>
         <v/>
       </c>
-      <c r="Z109" s="136" t="str">
+      <c r="Z109" s="104" t="str">
         <f>'[1]TERM 1'!Z111</f>
         <v/>
       </c>
-      <c r="AA109" s="136" t="str">
+      <c r="AA109" s="104" t="str">
         <f>'[1]TERM 1'!AA111</f>
         <v/>
       </c>
@@ -14050,11 +13966,11 @@
         <f>'[1]TERM 1'!K112</f>
         <v/>
       </c>
-      <c r="L110" s="136" t="str">
+      <c r="L110" s="104" t="str">
         <f>'[1]TERM 1'!L112</f>
         <v/>
       </c>
-      <c r="M110" s="137" t="str">
+      <c r="M110" s="105" t="str">
         <f>'[1]TERM 1'!M112</f>
         <v/>
       </c>
@@ -14065,34 +13981,34 @@
         <f>'[1]TERM 1'!Q112</f>
         <v/>
       </c>
-      <c r="R110" s="136" t="str">
+      <c r="R110" s="104" t="str">
         <f>'[1]TERM 1'!R112</f>
         <v/>
       </c>
-      <c r="S110" s="137" t="str">
+      <c r="S110" s="105" t="str">
         <f>'[1]TERM 1'!S112</f>
         <v/>
       </c>
       <c r="T110" s="100"/>
       <c r="U110" s="101"/>
       <c r="V110" s="102"/>
-      <c r="W110" s="136" t="str">
+      <c r="W110" s="104" t="str">
         <f>'[1]TERM 1'!W112</f>
         <v/>
       </c>
-      <c r="X110" s="136" t="str">
+      <c r="X110" s="104" t="str">
         <f>'[1]TERM 1'!X112</f>
         <v/>
       </c>
-      <c r="Y110" s="135" t="str">
+      <c r="Y110" s="103" t="str">
         <f>'[1]TERM 1'!Y112</f>
         <v/>
       </c>
-      <c r="Z110" s="136" t="str">
+      <c r="Z110" s="104" t="str">
         <f>'[1]TERM 1'!Z112</f>
         <v/>
       </c>
-      <c r="AA110" s="136" t="str">
+      <c r="AA110" s="104" t="str">
         <f>'[1]TERM 1'!AA112</f>
         <v/>
       </c>
@@ -14126,11 +14042,11 @@
         <f>'[1]TERM 1'!K113</f>
         <v/>
       </c>
-      <c r="L111" s="136" t="str">
+      <c r="L111" s="104" t="str">
         <f>'[1]TERM 1'!L113</f>
         <v/>
       </c>
-      <c r="M111" s="137" t="str">
+      <c r="M111" s="105" t="str">
         <f>'[1]TERM 1'!M113</f>
         <v/>
       </c>
@@ -14141,34 +14057,34 @@
         <f>'[1]TERM 1'!Q113</f>
         <v/>
       </c>
-      <c r="R111" s="136" t="str">
+      <c r="R111" s="104" t="str">
         <f>'[1]TERM 1'!R113</f>
         <v/>
       </c>
-      <c r="S111" s="137" t="str">
+      <c r="S111" s="105" t="str">
         <f>'[1]TERM 1'!S113</f>
         <v/>
       </c>
       <c r="T111" s="100"/>
       <c r="U111" s="101"/>
       <c r="V111" s="102"/>
-      <c r="W111" s="136" t="str">
+      <c r="W111" s="104" t="str">
         <f>'[1]TERM 1'!W113</f>
         <v/>
       </c>
-      <c r="X111" s="136" t="str">
+      <c r="X111" s="104" t="str">
         <f>'[1]TERM 1'!X113</f>
         <v/>
       </c>
-      <c r="Y111" s="135" t="str">
+      <c r="Y111" s="103" t="str">
         <f>'[1]TERM 1'!Y113</f>
         <v/>
       </c>
-      <c r="Z111" s="136" t="str">
+      <c r="Z111" s="104" t="str">
         <f>'[1]TERM 1'!Z113</f>
         <v/>
       </c>
-      <c r="AA111" s="136" t="str">
+      <c r="AA111" s="104" t="str">
         <f>'[1]TERM 1'!AA113</f>
         <v/>
       </c>
@@ -14202,11 +14118,11 @@
         <f>'[1]TERM 1'!K114</f>
         <v/>
       </c>
-      <c r="L112" s="136" t="str">
+      <c r="L112" s="104" t="str">
         <f>'[1]TERM 1'!L114</f>
         <v/>
       </c>
-      <c r="M112" s="137" t="str">
+      <c r="M112" s="105" t="str">
         <f>'[1]TERM 1'!M114</f>
         <v/>
       </c>
@@ -14217,34 +14133,34 @@
         <f>'[1]TERM 1'!Q114</f>
         <v/>
       </c>
-      <c r="R112" s="136" t="str">
+      <c r="R112" s="104" t="str">
         <f>'[1]TERM 1'!R114</f>
         <v/>
       </c>
-      <c r="S112" s="137" t="str">
+      <c r="S112" s="105" t="str">
         <f>'[1]TERM 1'!S114</f>
         <v/>
       </c>
       <c r="T112" s="100"/>
       <c r="U112" s="101"/>
       <c r="V112" s="102"/>
-      <c r="W112" s="136" t="str">
+      <c r="W112" s="104" t="str">
         <f>'[1]TERM 1'!W114</f>
         <v/>
       </c>
-      <c r="X112" s="136" t="str">
+      <c r="X112" s="104" t="str">
         <f>'[1]TERM 1'!X114</f>
         <v/>
       </c>
-      <c r="Y112" s="135" t="str">
+      <c r="Y112" s="103" t="str">
         <f>'[1]TERM 1'!Y114</f>
         <v/>
       </c>
-      <c r="Z112" s="136" t="str">
+      <c r="Z112" s="104" t="str">
         <f>'[1]TERM 1'!Z114</f>
         <v/>
       </c>
-      <c r="AA112" s="136" t="str">
+      <c r="AA112" s="104" t="str">
         <f>'[1]TERM 1'!AA114</f>
         <v/>
       </c>
@@ -14278,11 +14194,11 @@
         <f>'[1]TERM 1'!K115</f>
         <v/>
       </c>
-      <c r="L113" s="136" t="str">
+      <c r="L113" s="104" t="str">
         <f>'[1]TERM 1'!L115</f>
         <v/>
       </c>
-      <c r="M113" s="137" t="str">
+      <c r="M113" s="105" t="str">
         <f>'[1]TERM 1'!M115</f>
         <v/>
       </c>
@@ -14293,34 +14209,34 @@
         <f>'[1]TERM 1'!Q115</f>
         <v/>
       </c>
-      <c r="R113" s="136" t="str">
+      <c r="R113" s="104" t="str">
         <f>'[1]TERM 1'!R115</f>
         <v/>
       </c>
-      <c r="S113" s="137" t="str">
+      <c r="S113" s="105" t="str">
         <f>'[1]TERM 1'!S115</f>
         <v/>
       </c>
       <c r="T113" s="100"/>
       <c r="U113" s="101"/>
       <c r="V113" s="102"/>
-      <c r="W113" s="136" t="str">
+      <c r="W113" s="104" t="str">
         <f>'[1]TERM 1'!W115</f>
         <v/>
       </c>
-      <c r="X113" s="136" t="str">
+      <c r="X113" s="104" t="str">
         <f>'[1]TERM 1'!X115</f>
         <v/>
       </c>
-      <c r="Y113" s="135" t="str">
+      <c r="Y113" s="103" t="str">
         <f>'[1]TERM 1'!Y115</f>
         <v/>
       </c>
-      <c r="Z113" s="136" t="str">
+      <c r="Z113" s="104" t="str">
         <f>'[1]TERM 1'!Z115</f>
         <v/>
       </c>
-      <c r="AA113" s="136" t="str">
+      <c r="AA113" s="104" t="str">
         <f>'[1]TERM 1'!AA115</f>
         <v/>
       </c>
@@ -14354,11 +14270,11 @@
         <f>'[1]TERM 1'!K116</f>
         <v/>
       </c>
-      <c r="L114" s="136" t="str">
+      <c r="L114" s="104" t="str">
         <f>'[1]TERM 1'!L116</f>
         <v/>
       </c>
-      <c r="M114" s="137" t="str">
+      <c r="M114" s="105" t="str">
         <f>'[1]TERM 1'!M116</f>
         <v/>
       </c>
@@ -14369,34 +14285,34 @@
         <f>'[1]TERM 1'!Q116</f>
         <v/>
       </c>
-      <c r="R114" s="136" t="str">
+      <c r="R114" s="104" t="str">
         <f>'[1]TERM 1'!R116</f>
         <v/>
       </c>
-      <c r="S114" s="137" t="str">
+      <c r="S114" s="105" t="str">
         <f>'[1]TERM 1'!S116</f>
         <v/>
       </c>
       <c r="T114" s="100"/>
       <c r="U114" s="101"/>
       <c r="V114" s="102"/>
-      <c r="W114" s="136" t="str">
+      <c r="W114" s="104" t="str">
         <f>'[1]TERM 1'!W116</f>
         <v/>
       </c>
-      <c r="X114" s="136" t="str">
+      <c r="X114" s="104" t="str">
         <f>'[1]TERM 1'!X116</f>
         <v/>
       </c>
-      <c r="Y114" s="135" t="str">
+      <c r="Y114" s="103" t="str">
         <f>'[1]TERM 1'!Y116</f>
         <v/>
       </c>
-      <c r="Z114" s="136" t="str">
+      <c r="Z114" s="104" t="str">
         <f>'[1]TERM 1'!Z116</f>
         <v/>
       </c>
-      <c r="AA114" s="136" t="str">
+      <c r="AA114" s="104" t="str">
         <f>'[1]TERM 1'!AA116</f>
         <v/>
       </c>
@@ -14430,11 +14346,11 @@
         <f>'[1]TERM 1'!K117</f>
         <v/>
       </c>
-      <c r="L115" s="136" t="str">
+      <c r="L115" s="104" t="str">
         <f>'[1]TERM 1'!L117</f>
         <v/>
       </c>
-      <c r="M115" s="137" t="str">
+      <c r="M115" s="105" t="str">
         <f>'[1]TERM 1'!M117</f>
         <v/>
       </c>
@@ -14445,34 +14361,34 @@
         <f>'[1]TERM 1'!Q117</f>
         <v/>
       </c>
-      <c r="R115" s="136" t="str">
+      <c r="R115" s="104" t="str">
         <f>'[1]TERM 1'!R117</f>
         <v/>
       </c>
-      <c r="S115" s="137" t="str">
+      <c r="S115" s="105" t="str">
         <f>'[1]TERM 1'!S117</f>
         <v/>
       </c>
       <c r="T115" s="100"/>
       <c r="U115" s="101"/>
       <c r="V115" s="102"/>
-      <c r="W115" s="136" t="str">
+      <c r="W115" s="104" t="str">
         <f>'[1]TERM 1'!W117</f>
         <v/>
       </c>
-      <c r="X115" s="136" t="str">
+      <c r="X115" s="104" t="str">
         <f>'[1]TERM 1'!X117</f>
         <v/>
       </c>
-      <c r="Y115" s="135" t="str">
+      <c r="Y115" s="103" t="str">
         <f>'[1]TERM 1'!Y117</f>
         <v/>
       </c>
-      <c r="Z115" s="136" t="str">
+      <c r="Z115" s="104" t="str">
         <f>'[1]TERM 1'!Z117</f>
         <v/>
       </c>
-      <c r="AA115" s="136" t="str">
+      <c r="AA115" s="104" t="str">
         <f>'[1]TERM 1'!AA117</f>
         <v/>
       </c>
@@ -14506,11 +14422,11 @@
         <f>'[1]TERM 1'!K118</f>
         <v/>
       </c>
-      <c r="L116" s="139" t="str">
+      <c r="L116" s="113" t="str">
         <f>'[1]TERM 1'!L118</f>
         <v/>
       </c>
-      <c r="M116" s="140" t="str">
+      <c r="M116" s="114" t="str">
         <f>'[1]TERM 1'!M118</f>
         <v/>
       </c>
@@ -14521,34 +14437,34 @@
         <f>'[1]TERM 1'!Q118</f>
         <v/>
       </c>
-      <c r="R116" s="139" t="str">
+      <c r="R116" s="113" t="str">
         <f>'[1]TERM 1'!R118</f>
         <v/>
       </c>
-      <c r="S116" s="140" t="str">
+      <c r="S116" s="114" t="str">
         <f>'[1]TERM 1'!S118</f>
         <v/>
       </c>
       <c r="T116" s="109"/>
       <c r="U116" s="110"/>
       <c r="V116" s="111"/>
-      <c r="W116" s="139" t="str">
+      <c r="W116" s="113" t="str">
         <f>'[1]TERM 1'!W118</f>
         <v/>
       </c>
-      <c r="X116" s="139" t="str">
+      <c r="X116" s="113" t="str">
         <f>'[1]TERM 1'!X118</f>
         <v/>
       </c>
-      <c r="Y116" s="138" t="str">
+      <c r="Y116" s="112" t="str">
         <f>'[1]TERM 1'!Y118</f>
         <v/>
       </c>
-      <c r="Z116" s="139" t="str">
+      <c r="Z116" s="113" t="str">
         <f>'[1]TERM 1'!Z118</f>
         <v/>
       </c>
-      <c r="AA116" s="139" t="str">
+      <c r="AA116" s="113" t="str">
         <f>'[1]TERM 1'!AA118</f>
         <v/>
       </c>
